--- a/bahan/Sheet Pengusul APS 4_0 20200131.xlsx
+++ b/bahan/Sheet Pengusul APS 4_0 20200131.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="22325"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29929"/>
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Akreditasi 140819\Dewan Eksekutif 2016-2021\2019\Kinerja Divisi\Penyempurnaan APS-APT-LH\Instrument Final\IAPS 4.0\Excel APS 4.0 terbaru pasca perban\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\laragon\www\akre\bahan\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{AB2A71D1-2B06-4545-BDDE-9006FAE965B3}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EEB17877-582D-4409-910F-2645090C1141}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12720" tabRatio="839" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="839" firstSheet="10" activeTab="20" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Menu" sheetId="68" r:id="rId1"/>
@@ -61,6 +61,7 @@
     <sheet name="8f4-2" sheetId="54" r:id="rId46"/>
     <sheet name="8f4-3" sheetId="55" r:id="rId47"/>
     <sheet name="8f4-4" sheetId="56" r:id="rId48"/>
+    <sheet name="Sheet1" sheetId="69" r:id="rId49"/>
   </sheets>
   <definedNames>
     <definedName name="diploma" localSheetId="12">#REF!</definedName>
@@ -2426,7 +2427,7 @@
     </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="167">
+  <cellXfs count="158">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -2615,9 +2616,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" indent="2"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="12" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="11" fillId="5" borderId="1" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
@@ -2669,23 +2667,11 @@
     <xf numFmtId="165" fontId="11" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="12" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="11" fillId="4" borderId="1" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="4" borderId="1" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="10" fillId="14" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2718,13 +2704,6 @@
     <xf numFmtId="0" fontId="10" fillId="14" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" xfId="5" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="16" fillId="12" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -2749,7 +2728,7 @@
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="5" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="29" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -2770,18 +2749,6 @@
     <xf numFmtId="0" fontId="11" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="15" fontId="5" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -2797,11 +2764,20 @@
     <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="14" fontId="5" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="15" fontId="5" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="12" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -3403,9 +3379,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -3443,9 +3419,9 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
-        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -3478,26 +3454,9 @@
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -3530,26 +3489,9 @@
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -3764,62 +3706,62 @@
       <c r="Y1" s="2"/>
     </row>
     <row r="2" spans="1:25" ht="27" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="123" t="s">
+      <c r="A2" s="111" t="s">
         <v>8</v>
       </c>
-      <c r="B2" s="123"/>
-      <c r="C2" s="123"/>
-      <c r="D2" s="123"/>
-      <c r="E2" s="123"/>
-      <c r="F2" s="123"/>
-      <c r="G2" s="123"/>
-      <c r="H2" s="123"/>
-      <c r="I2" s="123"/>
-      <c r="J2" s="123"/>
-      <c r="K2" s="123"/>
-      <c r="L2" s="123"/>
-      <c r="M2" s="123"/>
-      <c r="N2" s="123"/>
-      <c r="O2" s="123"/>
-      <c r="P2" s="123"/>
-      <c r="Q2" s="123"/>
-      <c r="R2" s="123"/>
-      <c r="S2" s="123"/>
-      <c r="T2" s="123"/>
-      <c r="U2" s="123"/>
-      <c r="V2" s="123"/>
-      <c r="W2" s="123"/>
-      <c r="X2" s="123"/>
-      <c r="Y2" s="123"/>
+      <c r="B2" s="111"/>
+      <c r="C2" s="111"/>
+      <c r="D2" s="111"/>
+      <c r="E2" s="111"/>
+      <c r="F2" s="111"/>
+      <c r="G2" s="111"/>
+      <c r="H2" s="111"/>
+      <c r="I2" s="111"/>
+      <c r="J2" s="111"/>
+      <c r="K2" s="111"/>
+      <c r="L2" s="111"/>
+      <c r="M2" s="111"/>
+      <c r="N2" s="111"/>
+      <c r="O2" s="111"/>
+      <c r="P2" s="111"/>
+      <c r="Q2" s="111"/>
+      <c r="R2" s="111"/>
+      <c r="S2" s="111"/>
+      <c r="T2" s="111"/>
+      <c r="U2" s="111"/>
+      <c r="V2" s="111"/>
+      <c r="W2" s="111"/>
+      <c r="X2" s="111"/>
+      <c r="Y2" s="111"/>
     </row>
     <row r="3" spans="1:25" ht="27" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="124" t="s">
+      <c r="A3" s="112" t="s">
         <v>3</v>
       </c>
-      <c r="B3" s="124"/>
-      <c r="C3" s="124"/>
-      <c r="D3" s="124"/>
-      <c r="E3" s="124"/>
-      <c r="F3" s="124"/>
-      <c r="G3" s="124"/>
-      <c r="H3" s="124"/>
-      <c r="I3" s="124"/>
-      <c r="J3" s="124"/>
-      <c r="K3" s="124"/>
-      <c r="L3" s="124"/>
-      <c r="M3" s="124"/>
-      <c r="N3" s="124"/>
-      <c r="O3" s="124"/>
-      <c r="P3" s="124"/>
-      <c r="Q3" s="124"/>
-      <c r="R3" s="124"/>
-      <c r="S3" s="124"/>
-      <c r="T3" s="124"/>
-      <c r="U3" s="124"/>
-      <c r="V3" s="124"/>
-      <c r="W3" s="124"/>
-      <c r="X3" s="124"/>
-      <c r="Y3" s="124"/>
+      <c r="B3" s="112"/>
+      <c r="C3" s="112"/>
+      <c r="D3" s="112"/>
+      <c r="E3" s="112"/>
+      <c r="F3" s="112"/>
+      <c r="G3" s="112"/>
+      <c r="H3" s="112"/>
+      <c r="I3" s="112"/>
+      <c r="J3" s="112"/>
+      <c r="K3" s="112"/>
+      <c r="L3" s="112"/>
+      <c r="M3" s="112"/>
+      <c r="N3" s="112"/>
+      <c r="O3" s="112"/>
+      <c r="P3" s="112"/>
+      <c r="Q3" s="112"/>
+      <c r="R3" s="112"/>
+      <c r="S3" s="112"/>
+      <c r="T3" s="112"/>
+      <c r="U3" s="112"/>
+      <c r="V3" s="112"/>
+      <c r="W3" s="112"/>
+      <c r="X3" s="112"/>
+      <c r="Y3" s="112"/>
     </row>
     <row r="4" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="2"/>
@@ -3860,23 +3802,23 @@
       <c r="G5" s="10" t="s">
         <v>0</v>
       </c>
-      <c r="H5" s="125"/>
-      <c r="I5" s="125"/>
-      <c r="J5" s="125"/>
-      <c r="K5" s="125"/>
-      <c r="L5" s="125"/>
-      <c r="M5" s="125"/>
-      <c r="N5" s="125"/>
-      <c r="O5" s="125"/>
-      <c r="P5" s="125"/>
-      <c r="Q5" s="125"/>
-      <c r="R5" s="125"/>
-      <c r="S5" s="125"/>
-      <c r="T5" s="125"/>
-      <c r="U5" s="125"/>
-      <c r="V5" s="125"/>
-      <c r="W5" s="125"/>
-      <c r="X5" s="125"/>
+      <c r="H5" s="113"/>
+      <c r="I5" s="113"/>
+      <c r="J5" s="113"/>
+      <c r="K5" s="113"/>
+      <c r="L5" s="113"/>
+      <c r="M5" s="113"/>
+      <c r="N5" s="113"/>
+      <c r="O5" s="113"/>
+      <c r="P5" s="113"/>
+      <c r="Q5" s="113"/>
+      <c r="R5" s="113"/>
+      <c r="S5" s="113"/>
+      <c r="T5" s="113"/>
+      <c r="U5" s="113"/>
+      <c r="V5" s="113"/>
+      <c r="W5" s="113"/>
+      <c r="X5" s="113"/>
       <c r="Y5" s="9"/>
     </row>
     <row r="6" spans="1:25" s="7" customFormat="1" ht="5.0999999999999996" customHeight="1" x14ac:dyDescent="0.3">
@@ -3918,13 +3860,13 @@
       <c r="G7" s="10" t="s">
         <v>0</v>
       </c>
-      <c r="H7" s="119"/>
-      <c r="I7" s="119"/>
-      <c r="J7" s="119"/>
-      <c r="K7" s="119"/>
-      <c r="L7" s="119"/>
-      <c r="M7" s="119"/>
-      <c r="N7" s="119"/>
+      <c r="H7" s="114"/>
+      <c r="I7" s="114"/>
+      <c r="J7" s="114"/>
+      <c r="K7" s="114"/>
+      <c r="L7" s="114"/>
+      <c r="M7" s="114"/>
+      <c r="N7" s="114"/>
       <c r="O7" s="11"/>
       <c r="P7" s="11"/>
       <c r="Q7" s="11"/>
@@ -3972,10 +3914,10 @@
       <c r="E9" s="9"/>
       <c r="F9" s="10"/>
       <c r="G9" s="10"/>
-      <c r="H9" s="112" t="s">
+      <c r="H9" s="104" t="s">
         <v>343</v>
       </c>
-      <c r="I9" s="112"/>
+      <c r="I9" s="104"/>
       <c r="J9" s="10"/>
       <c r="K9" s="10"/>
       <c r="L9" s="10"/>
@@ -4001,10 +3943,10 @@
       <c r="E10" s="9"/>
       <c r="F10" s="10"/>
       <c r="G10" s="10"/>
-      <c r="H10" s="112" t="s">
+      <c r="H10" s="104" t="s">
         <v>344</v>
       </c>
-      <c r="I10" s="112"/>
+      <c r="I10" s="104"/>
       <c r="J10" s="10"/>
       <c r="K10" s="10"/>
       <c r="L10" s="10"/>
@@ -4030,10 +3972,10 @@
       <c r="E11" s="9"/>
       <c r="F11" s="10"/>
       <c r="G11" s="10"/>
-      <c r="H11" s="112" t="s">
+      <c r="H11" s="104" t="s">
         <v>345</v>
       </c>
-      <c r="I11" s="112"/>
+      <c r="I11" s="104"/>
       <c r="J11" s="10"/>
       <c r="K11" s="10"/>
       <c r="L11" s="10"/>
@@ -4059,10 +4001,10 @@
       <c r="E12" s="9"/>
       <c r="F12" s="10"/>
       <c r="G12" s="10"/>
-      <c r="H12" s="112" t="s">
+      <c r="H12" s="104" t="s">
         <v>346</v>
       </c>
-      <c r="I12" s="112"/>
+      <c r="I12" s="104"/>
       <c r="J12" s="10"/>
       <c r="K12" s="10"/>
       <c r="L12" s="10"/>
@@ -4088,10 +4030,10 @@
       <c r="E13" s="9"/>
       <c r="F13" s="10"/>
       <c r="G13" s="10"/>
-      <c r="H13" s="112" t="s">
+      <c r="H13" s="104" t="s">
         <v>347</v>
       </c>
-      <c r="I13" s="112"/>
+      <c r="I13" s="104"/>
       <c r="J13" s="10"/>
       <c r="K13" s="10"/>
       <c r="L13" s="10"/>
@@ -4117,10 +4059,10 @@
       <c r="E14" s="9"/>
       <c r="F14" s="10"/>
       <c r="G14" s="10"/>
-      <c r="H14" s="112" t="s">
+      <c r="H14" s="104" t="s">
         <v>348</v>
       </c>
-      <c r="I14" s="112"/>
+      <c r="I14" s="104"/>
       <c r="J14" s="10"/>
       <c r="K14" s="10"/>
       <c r="L14" s="10"/>
@@ -4146,10 +4088,10 @@
       <c r="E15" s="9"/>
       <c r="F15" s="10"/>
       <c r="G15" s="10"/>
-      <c r="H15" s="112" t="s">
+      <c r="H15" s="104" t="s">
         <v>349</v>
       </c>
-      <c r="I15" s="112"/>
+      <c r="I15" s="104"/>
       <c r="J15" s="10"/>
       <c r="K15" s="10"/>
       <c r="L15" s="10"/>
@@ -4206,9 +4148,9 @@
       <c r="G17" s="10" t="s">
         <v>0</v>
       </c>
-      <c r="H17" s="119"/>
-      <c r="I17" s="119"/>
-      <c r="J17" s="119"/>
+      <c r="H17" s="114"/>
+      <c r="I17" s="114"/>
+      <c r="J17" s="114"/>
       <c r="K17" s="11" t="str">
         <f>IF(H17="Minimum","Studi telah mendapt ijin pembukaan program studi baru. Pengajuan usulan akreditasi pertama","")</f>
         <v/>
@@ -4263,7 +4205,7 @@
       <c r="E19" s="9"/>
       <c r="F19" s="10"/>
       <c r="G19" s="10"/>
-      <c r="H19" s="112" t="s">
+      <c r="H19" s="104" t="s">
         <v>387</v>
       </c>
       <c r="I19" s="10"/>
@@ -4292,7 +4234,7 @@
       <c r="E20" s="9"/>
       <c r="F20" s="10"/>
       <c r="G20" s="10"/>
-      <c r="H20" s="112" t="s">
+      <c r="H20" s="104" t="s">
         <v>6</v>
       </c>
       <c r="I20" s="10"/>
@@ -4321,7 +4263,7 @@
       <c r="E21" s="9"/>
       <c r="F21" s="10"/>
       <c r="G21" s="10"/>
-      <c r="H21" s="112" t="s">
+      <c r="H21" s="104" t="s">
         <v>388</v>
       </c>
       <c r="I21" s="10"/>
@@ -4350,7 +4292,7 @@
       <c r="E22" s="9"/>
       <c r="F22" s="10"/>
       <c r="G22" s="10"/>
-      <c r="H22" s="112" t="s">
+      <c r="H22" s="104" t="s">
         <v>7</v>
       </c>
       <c r="I22" s="10"/>
@@ -4379,7 +4321,7 @@
       <c r="E23" s="9"/>
       <c r="F23" s="10"/>
       <c r="G23" s="10"/>
-      <c r="H23" s="112" t="s">
+      <c r="H23" s="104" t="s">
         <v>169</v>
       </c>
       <c r="I23" s="10"/>
@@ -4408,7 +4350,7 @@
       <c r="E24" s="9"/>
       <c r="F24" s="10"/>
       <c r="G24" s="10"/>
-      <c r="H24" s="112" t="s">
+      <c r="H24" s="104" t="s">
         <v>56</v>
       </c>
       <c r="I24" s="10"/>
@@ -4437,7 +4379,7 @@
       <c r="E25" s="9"/>
       <c r="F25" s="10"/>
       <c r="G25" s="10"/>
-      <c r="H25" s="112" t="s">
+      <c r="H25" s="104" t="s">
         <v>389</v>
       </c>
       <c r="I25" s="10"/>
@@ -4497,13 +4439,13 @@
       <c r="G27" s="10" t="s">
         <v>0</v>
       </c>
-      <c r="H27" s="119"/>
-      <c r="I27" s="119"/>
-      <c r="J27" s="119"/>
-      <c r="K27" s="119"/>
-      <c r="L27" s="119"/>
-      <c r="M27" s="119"/>
-      <c r="N27" s="119"/>
+      <c r="H27" s="114"/>
+      <c r="I27" s="114"/>
+      <c r="J27" s="114"/>
+      <c r="K27" s="114"/>
+      <c r="L27" s="114"/>
+      <c r="M27" s="114"/>
+      <c r="N27" s="114"/>
       <c r="O27" s="11"/>
       <c r="P27" s="11"/>
       <c r="Q27" s="11"/>
@@ -4555,9 +4497,9 @@
       <c r="G29" s="10" t="s">
         <v>0</v>
       </c>
-      <c r="H29" s="126"/>
-      <c r="I29" s="126"/>
-      <c r="J29" s="126"/>
+      <c r="H29" s="115"/>
+      <c r="I29" s="115"/>
+      <c r="J29" s="115"/>
       <c r="K29" s="11"/>
       <c r="L29" s="11"/>
       <c r="M29" s="11"/>
@@ -4613,23 +4555,23 @@
       <c r="G31" s="10" t="s">
         <v>0</v>
       </c>
-      <c r="H31" s="125"/>
-      <c r="I31" s="125"/>
-      <c r="J31" s="125"/>
-      <c r="K31" s="125"/>
-      <c r="L31" s="125"/>
-      <c r="M31" s="125"/>
-      <c r="N31" s="125"/>
-      <c r="O31" s="125"/>
-      <c r="P31" s="125"/>
-      <c r="Q31" s="125"/>
-      <c r="R31" s="125"/>
-      <c r="S31" s="125"/>
-      <c r="T31" s="125"/>
-      <c r="U31" s="125"/>
-      <c r="V31" s="125"/>
-      <c r="W31" s="125"/>
-      <c r="X31" s="125"/>
+      <c r="H31" s="113"/>
+      <c r="I31" s="113"/>
+      <c r="J31" s="113"/>
+      <c r="K31" s="113"/>
+      <c r="L31" s="113"/>
+      <c r="M31" s="113"/>
+      <c r="N31" s="113"/>
+      <c r="O31" s="113"/>
+      <c r="P31" s="113"/>
+      <c r="Q31" s="113"/>
+      <c r="R31" s="113"/>
+      <c r="S31" s="113"/>
+      <c r="T31" s="113"/>
+      <c r="U31" s="113"/>
+      <c r="V31" s="113"/>
+      <c r="W31" s="113"/>
+      <c r="X31" s="113"/>
       <c r="Y31" s="9"/>
     </row>
     <row r="32" spans="1:25" s="7" customFormat="1" ht="5.4" customHeight="1" x14ac:dyDescent="0.3">
@@ -4671,23 +4613,23 @@
       <c r="G33" s="10" t="s">
         <v>0</v>
       </c>
-      <c r="H33" s="127"/>
-      <c r="I33" s="127"/>
-      <c r="J33" s="127"/>
-      <c r="K33" s="127"/>
-      <c r="L33" s="127"/>
-      <c r="M33" s="127"/>
-      <c r="N33" s="127"/>
-      <c r="O33" s="127"/>
-      <c r="P33" s="127"/>
-      <c r="Q33" s="127"/>
-      <c r="R33" s="127"/>
-      <c r="S33" s="127"/>
-      <c r="T33" s="127"/>
-      <c r="U33" s="127"/>
-      <c r="V33" s="127"/>
-      <c r="W33" s="127"/>
-      <c r="X33" s="127"/>
+      <c r="H33" s="116"/>
+      <c r="I33" s="116"/>
+      <c r="J33" s="116"/>
+      <c r="K33" s="116"/>
+      <c r="L33" s="116"/>
+      <c r="M33" s="116"/>
+      <c r="N33" s="116"/>
+      <c r="O33" s="116"/>
+      <c r="P33" s="116"/>
+      <c r="Q33" s="116"/>
+      <c r="R33" s="116"/>
+      <c r="S33" s="116"/>
+      <c r="T33" s="116"/>
+      <c r="U33" s="116"/>
+      <c r="V33" s="116"/>
+      <c r="W33" s="116"/>
+      <c r="X33" s="116"/>
       <c r="Y33" s="9"/>
     </row>
     <row r="34" spans="1:25" s="7" customFormat="1" ht="5.4" customHeight="1" x14ac:dyDescent="0.3">
@@ -4725,8 +4667,8 @@
       <c r="E35" s="9"/>
       <c r="F35" s="10"/>
       <c r="G35" s="10"/>
-      <c r="H35" s="112"/>
-      <c r="I35" s="112"/>
+      <c r="H35" s="104"/>
+      <c r="I35" s="104"/>
       <c r="J35" s="10"/>
       <c r="K35" s="10"/>
       <c r="L35" s="10"/>
@@ -4752,10 +4694,10 @@
       <c r="E36" s="9"/>
       <c r="F36" s="10"/>
       <c r="G36" s="10"/>
-      <c r="H36" s="112" t="s">
+      <c r="H36" s="104" t="s">
         <v>392</v>
       </c>
-      <c r="I36" s="112"/>
+      <c r="I36" s="104"/>
       <c r="J36" s="10"/>
       <c r="K36" s="10"/>
       <c r="L36" s="10"/>
@@ -4781,10 +4723,10 @@
       <c r="E37" s="9"/>
       <c r="F37" s="10"/>
       <c r="G37" s="10"/>
-      <c r="H37" s="112" t="s">
+      <c r="H37" s="104" t="s">
         <v>393</v>
       </c>
-      <c r="I37" s="112"/>
+      <c r="I37" s="104"/>
       <c r="J37" s="10"/>
       <c r="K37" s="10"/>
       <c r="L37" s="10"/>
@@ -4810,10 +4752,10 @@
       <c r="E38" s="9"/>
       <c r="F38" s="10"/>
       <c r="G38" s="10"/>
-      <c r="H38" s="112" t="s">
+      <c r="H38" s="104" t="s">
         <v>394</v>
       </c>
-      <c r="I38" s="112"/>
+      <c r="I38" s="104"/>
       <c r="J38" s="10"/>
       <c r="K38" s="10"/>
       <c r="L38" s="10"/>
@@ -4839,10 +4781,10 @@
       <c r="E39" s="9"/>
       <c r="F39" s="10"/>
       <c r="G39" s="10"/>
-      <c r="H39" s="112" t="s">
+      <c r="H39" s="104" t="s">
         <v>395</v>
       </c>
-      <c r="I39" s="112"/>
+      <c r="I39" s="104"/>
       <c r="J39" s="10"/>
       <c r="K39" s="10"/>
       <c r="L39" s="10"/>
@@ -4899,23 +4841,23 @@
       <c r="G41" s="10" t="s">
         <v>0</v>
       </c>
-      <c r="H41" s="119"/>
-      <c r="I41" s="119"/>
-      <c r="J41" s="119"/>
-      <c r="K41" s="119"/>
-      <c r="L41" s="119"/>
-      <c r="M41" s="119"/>
-      <c r="N41" s="119"/>
-      <c r="O41" s="119"/>
-      <c r="P41" s="119"/>
-      <c r="Q41" s="119"/>
-      <c r="R41" s="119"/>
-      <c r="S41" s="119"/>
-      <c r="T41" s="119"/>
-      <c r="U41" s="119"/>
-      <c r="V41" s="119"/>
-      <c r="W41" s="119"/>
-      <c r="X41" s="119"/>
+      <c r="H41" s="114"/>
+      <c r="I41" s="114"/>
+      <c r="J41" s="114"/>
+      <c r="K41" s="114"/>
+      <c r="L41" s="114"/>
+      <c r="M41" s="114"/>
+      <c r="N41" s="114"/>
+      <c r="O41" s="114"/>
+      <c r="P41" s="114"/>
+      <c r="Q41" s="114"/>
+      <c r="R41" s="114"/>
+      <c r="S41" s="114"/>
+      <c r="T41" s="114"/>
+      <c r="U41" s="114"/>
+      <c r="V41" s="114"/>
+      <c r="W41" s="114"/>
+      <c r="X41" s="114"/>
       <c r="Y41" s="9"/>
     </row>
     <row r="42" spans="1:25" s="7" customFormat="1" ht="5.4" customHeight="1" x14ac:dyDescent="0.3">
@@ -4953,23 +4895,23 @@
       <c r="E43" s="9"/>
       <c r="F43" s="10"/>
       <c r="G43" s="10"/>
-      <c r="H43" s="119"/>
-      <c r="I43" s="119"/>
-      <c r="J43" s="119"/>
-      <c r="K43" s="119"/>
-      <c r="L43" s="119"/>
-      <c r="M43" s="119"/>
-      <c r="N43" s="119"/>
-      <c r="O43" s="119"/>
-      <c r="P43" s="119"/>
-      <c r="Q43" s="119"/>
-      <c r="R43" s="119"/>
-      <c r="S43" s="119"/>
-      <c r="T43" s="119"/>
-      <c r="U43" s="119"/>
-      <c r="V43" s="119"/>
-      <c r="W43" s="119"/>
-      <c r="X43" s="119"/>
+      <c r="H43" s="114"/>
+      <c r="I43" s="114"/>
+      <c r="J43" s="114"/>
+      <c r="K43" s="114"/>
+      <c r="L43" s="114"/>
+      <c r="M43" s="114"/>
+      <c r="N43" s="114"/>
+      <c r="O43" s="114"/>
+      <c r="P43" s="114"/>
+      <c r="Q43" s="114"/>
+      <c r="R43" s="114"/>
+      <c r="S43" s="114"/>
+      <c r="T43" s="114"/>
+      <c r="U43" s="114"/>
+      <c r="V43" s="114"/>
+      <c r="W43" s="114"/>
+      <c r="X43" s="114"/>
       <c r="Y43" s="9"/>
     </row>
     <row r="44" spans="1:25" s="7" customFormat="1" ht="5.4" customHeight="1" x14ac:dyDescent="0.3">
@@ -5007,12 +4949,12 @@
       <c r="E45" s="9"/>
       <c r="F45" s="10"/>
       <c r="G45" s="10"/>
-      <c r="H45" s="121" t="s">
+      <c r="H45" s="109" t="s">
         <v>397</v>
       </c>
-      <c r="I45" s="121"/>
-      <c r="J45" s="121"/>
-      <c r="K45" s="121"/>
+      <c r="I45" s="109"/>
+      <c r="J45" s="109"/>
+      <c r="K45" s="109"/>
       <c r="L45" s="19"/>
       <c r="M45" s="19"/>
       <c r="N45" s="19"/>
@@ -5022,10 +4964,10 @@
       <c r="R45" s="19"/>
       <c r="S45" s="19"/>
       <c r="T45" s="19"/>
-      <c r="U45" s="122" t="s">
+      <c r="U45" s="110" t="s">
         <v>398</v>
       </c>
-      <c r="V45" s="122"/>
+      <c r="V45" s="110"/>
       <c r="W45" s="19"/>
       <c r="X45" s="19"/>
       <c r="Y45" s="9"/>
@@ -5069,13 +5011,13 @@
       <c r="G47" s="10" t="s">
         <v>0</v>
       </c>
-      <c r="H47" s="119"/>
-      <c r="I47" s="119"/>
-      <c r="J47" s="119"/>
-      <c r="K47" s="119"/>
-      <c r="L47" s="119"/>
-      <c r="M47" s="119"/>
-      <c r="N47" s="119"/>
+      <c r="H47" s="114"/>
+      <c r="I47" s="114"/>
+      <c r="J47" s="114"/>
+      <c r="K47" s="114"/>
+      <c r="L47" s="114"/>
+      <c r="M47" s="114"/>
+      <c r="N47" s="114"/>
       <c r="O47" s="11"/>
       <c r="P47" s="11"/>
       <c r="Q47" s="11"/>
@@ -5127,16 +5069,16 @@
       <c r="G49" s="10" t="s">
         <v>0</v>
       </c>
-      <c r="H49" s="119"/>
-      <c r="I49" s="119"/>
-      <c r="J49" s="119"/>
-      <c r="K49" s="119"/>
-      <c r="L49" s="119"/>
-      <c r="M49" s="119"/>
-      <c r="N49" s="119"/>
-      <c r="O49" s="119"/>
-      <c r="P49" s="119"/>
-      <c r="Q49" s="119"/>
+      <c r="H49" s="114"/>
+      <c r="I49" s="114"/>
+      <c r="J49" s="114"/>
+      <c r="K49" s="114"/>
+      <c r="L49" s="114"/>
+      <c r="M49" s="114"/>
+      <c r="N49" s="114"/>
+      <c r="O49" s="114"/>
+      <c r="P49" s="114"/>
+      <c r="Q49" s="114"/>
       <c r="R49" s="11"/>
       <c r="S49" s="11"/>
       <c r="T49" s="11"/>
@@ -5185,15 +5127,15 @@
       <c r="G51" s="10" t="s">
         <v>0</v>
       </c>
-      <c r="H51" s="119"/>
-      <c r="I51" s="119"/>
-      <c r="J51" s="119"/>
-      <c r="K51" s="119"/>
-      <c r="L51" s="119"/>
-      <c r="M51" s="119"/>
-      <c r="N51" s="119"/>
-      <c r="O51" s="119"/>
-      <c r="P51" s="119"/>
+      <c r="H51" s="114"/>
+      <c r="I51" s="114"/>
+      <c r="J51" s="114"/>
+      <c r="K51" s="114"/>
+      <c r="L51" s="114"/>
+      <c r="M51" s="114"/>
+      <c r="N51" s="114"/>
+      <c r="O51" s="114"/>
+      <c r="P51" s="114"/>
       <c r="Q51" s="11"/>
       <c r="R51" s="11"/>
       <c r="S51" s="11"/>
@@ -5244,7 +5186,7 @@
         <v>0</v>
       </c>
       <c r="H53" s="17"/>
-      <c r="I53" s="113" t="s">
+      <c r="I53" s="105" t="s">
         <v>11</v>
       </c>
       <c r="J53" s="17"/>
@@ -5331,7 +5273,7 @@
       <c r="J56" s="2"/>
       <c r="K56" s="2"/>
       <c r="L56" s="2"/>
-      <c r="M56" s="114"/>
+      <c r="M56" s="106"/>
       <c r="N56" s="11"/>
       <c r="O56" s="9"/>
       <c r="P56" s="10"/>
@@ -5358,7 +5300,7 @@
       <c r="J57" s="2"/>
       <c r="K57" s="2"/>
       <c r="L57" s="2"/>
-      <c r="M57" s="114"/>
+      <c r="M57" s="106"/>
       <c r="N57" s="11"/>
       <c r="O57" s="12" t="s">
         <v>403</v>
@@ -5368,12 +5310,12 @@
       <c r="R57" s="10" t="s">
         <v>0</v>
       </c>
-      <c r="S57" s="119"/>
-      <c r="T57" s="119"/>
-      <c r="U57" s="119"/>
-      <c r="V57" s="119"/>
-      <c r="W57" s="119"/>
-      <c r="X57" s="119"/>
+      <c r="S57" s="114"/>
+      <c r="T57" s="114"/>
+      <c r="U57" s="114"/>
+      <c r="V57" s="114"/>
+      <c r="W57" s="114"/>
+      <c r="X57" s="114"/>
       <c r="Y57" s="9"/>
     </row>
     <row r="58" spans="1:25" ht="4.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -5389,7 +5331,7 @@
       <c r="J58" s="2"/>
       <c r="K58" s="2"/>
       <c r="L58" s="2"/>
-      <c r="M58" s="114"/>
+      <c r="M58" s="106"/>
       <c r="N58" s="2"/>
       <c r="O58" s="9"/>
       <c r="P58" s="10"/>
@@ -5418,7 +5360,7 @@
       <c r="J59" s="2"/>
       <c r="K59" s="2"/>
       <c r="L59" s="2"/>
-      <c r="M59" s="114"/>
+      <c r="M59" s="106"/>
       <c r="N59" s="2"/>
       <c r="O59" s="12" t="s">
         <v>405</v>
@@ -5428,9 +5370,9 @@
       <c r="R59" s="10" t="s">
         <v>0</v>
       </c>
-      <c r="S59" s="120"/>
-      <c r="T59" s="120"/>
-      <c r="U59" s="120"/>
+      <c r="S59" s="118"/>
+      <c r="T59" s="118"/>
+      <c r="U59" s="118"/>
       <c r="V59" s="2"/>
       <c r="W59" s="2"/>
       <c r="X59" s="2"/>
@@ -5444,10 +5386,10 @@
       <c r="C60" s="15" t="s">
         <v>406</v>
       </c>
-      <c r="D60" s="118">
+      <c r="D60" s="117">
         <v>20200131</v>
       </c>
-      <c r="E60" s="118"/>
+      <c r="E60" s="117"/>
       <c r="F60" s="2"/>
       <c r="G60" s="2"/>
       <c r="H60" s="2"/>
@@ -5455,7 +5397,7 @@
       <c r="J60" s="2"/>
       <c r="K60" s="2"/>
       <c r="L60" s="2"/>
-      <c r="M60" s="114"/>
+      <c r="M60" s="106"/>
       <c r="N60" s="2"/>
       <c r="O60" s="2"/>
       <c r="P60" s="2"/>
@@ -5504,6 +5446,12 @@
     <protectedRange sqref="H5:I5 H31:I31" name="Nama PT"/>
   </protectedRanges>
   <mergeCells count="19">
+    <mergeCell ref="D60:E60"/>
+    <mergeCell ref="H47:N47"/>
+    <mergeCell ref="H49:Q49"/>
+    <mergeCell ref="H51:P51"/>
+    <mergeCell ref="S57:X57"/>
+    <mergeCell ref="S59:U59"/>
     <mergeCell ref="H45:K45"/>
     <mergeCell ref="U45:V45"/>
     <mergeCell ref="A2:Y2"/>
@@ -5517,12 +5465,6 @@
     <mergeCell ref="H33:X33"/>
     <mergeCell ref="H41:X41"/>
     <mergeCell ref="H43:X43"/>
-    <mergeCell ref="D60:E60"/>
-    <mergeCell ref="H47:N47"/>
-    <mergeCell ref="H49:Q49"/>
-    <mergeCell ref="H51:P51"/>
-    <mergeCell ref="S57:X57"/>
-    <mergeCell ref="S59:U59"/>
   </mergeCells>
   <dataValidations count="4">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H17:J17" xr:uid="{00000000-0002-0000-0000-000000000000}">
@@ -5569,46 +5511,46 @@
       <c r="A2" s="38"/>
     </row>
     <row r="3" spans="1:12" ht="21.9" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="146" t="s">
+      <c r="A3" s="137" t="s">
         <v>17</v>
       </c>
-      <c r="B3" s="146" t="s">
+      <c r="B3" s="137" t="s">
         <v>46</v>
       </c>
-      <c r="C3" s="146" t="s">
+      <c r="C3" s="137" t="s">
         <v>60</v>
       </c>
-      <c r="D3" s="146"/>
-      <c r="E3" s="146"/>
-      <c r="F3" s="146"/>
-      <c r="G3" s="146"/>
-      <c r="H3" s="146"/>
-      <c r="I3" s="146"/>
-      <c r="J3" s="146"/>
-      <c r="K3" s="146" t="s">
+      <c r="D3" s="137"/>
+      <c r="E3" s="137"/>
+      <c r="F3" s="137"/>
+      <c r="G3" s="137"/>
+      <c r="H3" s="137"/>
+      <c r="I3" s="137"/>
+      <c r="J3" s="137"/>
+      <c r="K3" s="137" t="s">
         <v>273</v>
       </c>
     </row>
     <row r="4" spans="1:12" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="146"/>
-      <c r="B4" s="146"/>
-      <c r="C4" s="146" t="s">
+      <c r="A4" s="137"/>
+      <c r="B4" s="137"/>
+      <c r="C4" s="137" t="s">
         <v>61</v>
       </c>
-      <c r="D4" s="146"/>
-      <c r="E4" s="146"/>
-      <c r="F4" s="146"/>
-      <c r="G4" s="146" t="s">
+      <c r="D4" s="137"/>
+      <c r="E4" s="137"/>
+      <c r="F4" s="137"/>
+      <c r="G4" s="137" t="s">
         <v>427</v>
       </c>
-      <c r="H4" s="146"/>
-      <c r="I4" s="146"/>
-      <c r="J4" s="146"/>
-      <c r="K4" s="146"/>
+      <c r="H4" s="137"/>
+      <c r="I4" s="137"/>
+      <c r="J4" s="137"/>
+      <c r="K4" s="137"/>
     </row>
     <row r="5" spans="1:12" ht="27.6" x14ac:dyDescent="0.3">
-      <c r="A5" s="146"/>
-      <c r="B5" s="146"/>
+      <c r="A5" s="137"/>
+      <c r="B5" s="137"/>
       <c r="C5" s="39" t="s">
         <v>40</v>
       </c>
@@ -5633,7 +5575,7 @@
       <c r="J5" s="39" t="s">
         <v>136</v>
       </c>
-      <c r="K5" s="146"/>
+      <c r="K5" s="137"/>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A6" s="29">
@@ -5678,12 +5620,12 @@
       <c r="C7" s="25"/>
       <c r="D7" s="25"/>
       <c r="E7" s="25"/>
-      <c r="F7" s="81"/>
+      <c r="F7" s="80"/>
       <c r="G7" s="25"/>
       <c r="H7" s="25"/>
       <c r="I7" s="25"/>
-      <c r="J7" s="81"/>
-      <c r="K7" s="81"/>
+      <c r="J7" s="80"/>
+      <c r="K7" s="80"/>
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A8" s="31">
@@ -5693,12 +5635,12 @@
       <c r="C8" s="25"/>
       <c r="D8" s="25"/>
       <c r="E8" s="25"/>
-      <c r="F8" s="81"/>
+      <c r="F8" s="80"/>
       <c r="G8" s="25"/>
       <c r="H8" s="25"/>
       <c r="I8" s="25"/>
-      <c r="J8" s="81"/>
-      <c r="K8" s="81"/>
+      <c r="J8" s="80"/>
+      <c r="K8" s="80"/>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A9" s="31">
@@ -5708,12 +5650,12 @@
       <c r="C9" s="25"/>
       <c r="D9" s="25"/>
       <c r="E9" s="25"/>
-      <c r="F9" s="81"/>
+      <c r="F9" s="80"/>
       <c r="G9" s="25"/>
       <c r="H9" s="25"/>
       <c r="I9" s="25"/>
-      <c r="J9" s="81"/>
-      <c r="K9" s="81"/>
+      <c r="J9" s="80"/>
+      <c r="K9" s="80"/>
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A10" s="31">
@@ -5723,12 +5665,12 @@
       <c r="C10" s="25"/>
       <c r="D10" s="25"/>
       <c r="E10" s="25"/>
-      <c r="F10" s="81"/>
+      <c r="F10" s="80"/>
       <c r="G10" s="25"/>
       <c r="H10" s="25"/>
       <c r="I10" s="25"/>
-      <c r="J10" s="81"/>
-      <c r="K10" s="81"/>
+      <c r="J10" s="80"/>
+      <c r="K10" s="80"/>
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A11" s="31">
@@ -5738,12 +5680,12 @@
       <c r="C11" s="25"/>
       <c r="D11" s="25"/>
       <c r="E11" s="25"/>
-      <c r="F11" s="81"/>
+      <c r="F11" s="80"/>
       <c r="G11" s="25"/>
       <c r="H11" s="25"/>
       <c r="I11" s="25"/>
-      <c r="J11" s="81"/>
-      <c r="K11" s="81"/>
+      <c r="J11" s="80"/>
+      <c r="K11" s="80"/>
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A12" s="31" t="s">
@@ -5753,7 +5695,7 @@
       <c r="C12" s="25"/>
       <c r="D12" s="25"/>
       <c r="E12" s="25"/>
-      <c r="F12" s="81"/>
+      <c r="F12" s="80"/>
       <c r="G12" s="25"/>
       <c r="H12" s="25"/>
       <c r="I12" s="25"/>
@@ -5812,55 +5754,55 @@
     </row>
     <row r="6" spans="1:12" hidden="1" x14ac:dyDescent="0.3"/>
     <row r="7" spans="1:12" ht="29.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="128" t="s">
+      <c r="A7" s="119" t="s">
         <v>17</v>
       </c>
-      <c r="B7" s="128" t="s">
+      <c r="B7" s="119" t="s">
         <v>64</v>
       </c>
-      <c r="C7" s="128" t="s">
+      <c r="C7" s="119" t="s">
         <v>65</v>
       </c>
-      <c r="D7" s="130" t="s">
+      <c r="D7" s="121" t="s">
         <v>66</v>
       </c>
-      <c r="E7" s="131"/>
-      <c r="F7" s="131"/>
-      <c r="G7" s="131"/>
-      <c r="H7" s="131"/>
-      <c r="I7" s="132"/>
-      <c r="J7" s="128" t="s">
+      <c r="E7" s="122"/>
+      <c r="F7" s="122"/>
+      <c r="G7" s="122"/>
+      <c r="H7" s="122"/>
+      <c r="I7" s="123"/>
+      <c r="J7" s="119" t="s">
         <v>67</v>
       </c>
-      <c r="K7" s="128" t="s">
+      <c r="K7" s="119" t="s">
         <v>68</v>
       </c>
     </row>
     <row r="8" spans="1:12" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="147"/>
-      <c r="B8" s="147"/>
-      <c r="C8" s="147"/>
-      <c r="D8" s="130" t="s">
+      <c r="A8" s="138"/>
+      <c r="B8" s="138"/>
+      <c r="C8" s="138"/>
+      <c r="D8" s="121" t="s">
         <v>69</v>
       </c>
-      <c r="E8" s="131"/>
-      <c r="F8" s="132"/>
-      <c r="G8" s="128" t="s">
+      <c r="E8" s="122"/>
+      <c r="F8" s="123"/>
+      <c r="G8" s="119" t="s">
         <v>43</v>
       </c>
-      <c r="H8" s="128" t="s">
+      <c r="H8" s="119" t="s">
         <v>44</v>
       </c>
-      <c r="I8" s="128" t="s">
+      <c r="I8" s="119" t="s">
         <v>70</v>
       </c>
-      <c r="J8" s="147"/>
-      <c r="K8" s="147"/>
+      <c r="J8" s="138"/>
+      <c r="K8" s="138"/>
     </row>
     <row r="9" spans="1:12" ht="32.1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="129"/>
-      <c r="B9" s="129"/>
-      <c r="C9" s="129"/>
+      <c r="A9" s="120"/>
+      <c r="B9" s="120"/>
+      <c r="C9" s="120"/>
       <c r="D9" s="27" t="s">
         <v>71</v>
       </c>
@@ -5870,11 +5812,11 @@
       <c r="F9" s="27" t="s">
         <v>73</v>
       </c>
-      <c r="G9" s="129"/>
-      <c r="H9" s="129"/>
-      <c r="I9" s="129"/>
-      <c r="J9" s="129"/>
-      <c r="K9" s="129"/>
+      <c r="G9" s="120"/>
+      <c r="H9" s="120"/>
+      <c r="I9" s="120"/>
+      <c r="J9" s="120"/>
+      <c r="K9" s="120"/>
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A10" s="29">
@@ -6228,16 +6170,16 @@
     </row>
   </sheetData>
   <mergeCells count="10">
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="B7:B9"/>
+    <mergeCell ref="C7:C9"/>
+    <mergeCell ref="D7:I7"/>
+    <mergeCell ref="J7:J9"/>
     <mergeCell ref="K7:K9"/>
     <mergeCell ref="D8:F8"/>
     <mergeCell ref="G8:G9"/>
     <mergeCell ref="H8:H9"/>
     <mergeCell ref="I8:I9"/>
-    <mergeCell ref="A7:A9"/>
-    <mergeCell ref="B7:B9"/>
-    <mergeCell ref="C7:C9"/>
-    <mergeCell ref="D7:I7"/>
-    <mergeCell ref="J7:J9"/>
   </mergeCells>
   <dataValidations count="1">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C11:C31" xr:uid="{00000000-0002-0000-0A00-000000000000}">
@@ -6330,7 +6272,7 @@
       <c r="G11" s="27" t="s">
         <v>51</v>
       </c>
-      <c r="H11" s="84" t="s">
+      <c r="H11" s="27" t="s">
         <v>52</v>
       </c>
       <c r="I11" s="27" t="s">
@@ -6694,32 +6636,32 @@
       <c r="A6" s="41"/>
     </row>
     <row r="7" spans="1:9" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="128" t="s">
+      <c r="A7" s="119" t="s">
         <v>17</v>
       </c>
-      <c r="B7" s="128" t="s">
+      <c r="B7" s="119" t="s">
         <v>46</v>
       </c>
-      <c r="C7" s="128" t="s">
+      <c r="C7" s="119" t="s">
         <v>48</v>
       </c>
-      <c r="D7" s="128" t="s">
+      <c r="D7" s="119" t="s">
         <v>85</v>
       </c>
-      <c r="E7" s="130" t="s">
+      <c r="E7" s="121" t="s">
         <v>86</v>
       </c>
-      <c r="F7" s="131"/>
-      <c r="G7" s="132"/>
-      <c r="H7" s="128" t="s">
+      <c r="F7" s="122"/>
+      <c r="G7" s="123"/>
+      <c r="H7" s="119" t="s">
         <v>87</v>
       </c>
     </row>
     <row r="8" spans="1:9" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="129"/>
-      <c r="B8" s="129"/>
-      <c r="C8" s="129"/>
-      <c r="D8" s="129"/>
+      <c r="A8" s="120"/>
+      <c r="B8" s="120"/>
+      <c r="C8" s="120"/>
+      <c r="D8" s="120"/>
       <c r="E8" s="27" t="s">
         <v>88</v>
       </c>
@@ -6729,7 +6671,7 @@
       <c r="G8" s="27" t="s">
         <v>25</v>
       </c>
-      <c r="H8" s="129"/>
+      <c r="H8" s="120"/>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A9" s="42">
@@ -6884,24 +6826,24 @@
       <c r="A2" s="38"/>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A3" s="148" t="s">
+      <c r="A3" s="139" t="s">
         <v>17</v>
       </c>
-      <c r="B3" s="149" t="s">
+      <c r="B3" s="140" t="s">
         <v>91</v>
       </c>
-      <c r="C3" s="148" t="s">
+      <c r="C3" s="139" t="s">
         <v>92</v>
       </c>
-      <c r="D3" s="148"/>
-      <c r="E3" s="148"/>
-      <c r="F3" s="148" t="s">
+      <c r="D3" s="139"/>
+      <c r="E3" s="139"/>
+      <c r="F3" s="139" t="s">
         <v>42</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A4" s="148"/>
-      <c r="B4" s="150"/>
+      <c r="A4" s="139"/>
+      <c r="B4" s="141"/>
       <c r="C4" s="48" t="s">
         <v>40</v>
       </c>
@@ -6911,7 +6853,7 @@
       <c r="E4" s="48" t="s">
         <v>12</v>
       </c>
-      <c r="F4" s="148"/>
+      <c r="F4" s="139"/>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A5" s="22">
@@ -6979,10 +6921,10 @@
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A9" s="151" t="s">
+      <c r="A9" s="142" t="s">
         <v>42</v>
       </c>
-      <c r="B9" s="151"/>
+      <c r="B9" s="142"/>
       <c r="C9" s="33">
         <f>SUM(C6:C8)</f>
         <v>0</v>
@@ -7039,24 +6981,24 @@
       <c r="A2" s="38"/>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A3" s="148" t="s">
+      <c r="A3" s="139" t="s">
         <v>17</v>
       </c>
-      <c r="B3" s="149" t="s">
+      <c r="B3" s="140" t="s">
         <v>91</v>
       </c>
-      <c r="C3" s="148" t="s">
+      <c r="C3" s="139" t="s">
         <v>97</v>
       </c>
-      <c r="D3" s="148"/>
-      <c r="E3" s="148"/>
-      <c r="F3" s="148" t="s">
+      <c r="D3" s="139"/>
+      <c r="E3" s="139"/>
+      <c r="F3" s="139" t="s">
         <v>42</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A4" s="148"/>
-      <c r="B4" s="150"/>
+      <c r="A4" s="139"/>
+      <c r="B4" s="141"/>
       <c r="C4" s="48" t="s">
         <v>40</v>
       </c>
@@ -7066,7 +7008,7 @@
       <c r="E4" s="48" t="s">
         <v>12</v>
       </c>
-      <c r="F4" s="148"/>
+      <c r="F4" s="139"/>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A5" s="22">
@@ -7134,10 +7076,10 @@
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A9" s="151" t="s">
+      <c r="A9" s="142" t="s">
         <v>42</v>
       </c>
-      <c r="B9" s="151"/>
+      <c r="B9" s="142"/>
       <c r="C9" s="33">
         <f>SUM(C6:C8)</f>
         <v>0</v>
@@ -7199,34 +7141,34 @@
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A4" s="148" t="s">
+      <c r="A4" s="139" t="s">
         <v>17</v>
       </c>
-      <c r="B4" s="148" t="s">
+      <c r="B4" s="139" t="s">
         <v>100</v>
       </c>
-      <c r="C4" s="148" t="s">
+      <c r="C4" s="139" t="s">
         <v>101</v>
       </c>
-      <c r="D4" s="148"/>
-      <c r="E4" s="148"/>
-      <c r="F4" s="148" t="s">
+      <c r="D4" s="139"/>
+      <c r="E4" s="139"/>
+      <c r="F4" s="139" t="s">
         <v>42</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A5" s="148"/>
-      <c r="B5" s="148"/>
-      <c r="C5" s="82" t="s">
+      <c r="A5" s="139"/>
+      <c r="B5" s="139"/>
+      <c r="C5" s="48" t="s">
         <v>40</v>
       </c>
-      <c r="D5" s="82" t="s">
+      <c r="D5" s="48" t="s">
         <v>41</v>
       </c>
-      <c r="E5" s="82" t="s">
+      <c r="E5" s="48" t="s">
         <v>12</v>
       </c>
-      <c r="F5" s="148"/>
+      <c r="F5" s="139"/>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A6" s="22">
@@ -7399,23 +7341,23 @@
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A17" s="151" t="s">
+      <c r="A17" s="142" t="s">
         <v>42</v>
       </c>
-      <c r="B17" s="152"/>
-      <c r="C17" s="83">
+      <c r="B17" s="143"/>
+      <c r="C17" s="33">
         <f>SUM(C7:C16)</f>
         <v>0</v>
       </c>
-      <c r="D17" s="83">
+      <c r="D17" s="33">
         <f>SUM(D7:D16)</f>
         <v>0</v>
       </c>
-      <c r="E17" s="83">
+      <c r="E17" s="33">
         <f>SUM(E7:E16)</f>
         <v>0</v>
       </c>
-      <c r="F17" s="83">
+      <c r="F17" s="33">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
@@ -7464,24 +7406,24 @@
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A4" s="148" t="s">
+      <c r="A4" s="139" t="s">
         <v>17</v>
       </c>
-      <c r="B4" s="148" t="s">
+      <c r="B4" s="139" t="s">
         <v>100</v>
       </c>
-      <c r="C4" s="148" t="s">
+      <c r="C4" s="139" t="s">
         <v>101</v>
       </c>
-      <c r="D4" s="148"/>
-      <c r="E4" s="148"/>
-      <c r="F4" s="148" t="s">
+      <c r="D4" s="139"/>
+      <c r="E4" s="139"/>
+      <c r="F4" s="139" t="s">
         <v>42</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A5" s="148"/>
-      <c r="B5" s="148"/>
+      <c r="A5" s="139"/>
+      <c r="B5" s="139"/>
       <c r="C5" s="48" t="s">
         <v>40</v>
       </c>
@@ -7491,7 +7433,7 @@
       <c r="E5" s="48" t="s">
         <v>12</v>
       </c>
-      <c r="F5" s="148"/>
+      <c r="F5" s="139"/>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A6" s="22">
@@ -7664,10 +7606,10 @@
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A17" s="151" t="s">
+      <c r="A17" s="142" t="s">
         <v>42</v>
       </c>
-      <c r="B17" s="152"/>
+      <c r="B17" s="143"/>
       <c r="C17" s="33">
         <f>SUM(C7:C16)</f>
         <v>0</v>
@@ -7826,54 +7768,54 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A1" s="88" t="s">
+      <c r="A1" s="83" t="s">
         <v>291</v>
       </c>
     </row>
     <row r="3" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="89" t="s">
+      <c r="A3" s="84" t="s">
         <v>116</v>
       </c>
-      <c r="B3" s="89" t="s">
+      <c r="B3" s="84" t="s">
         <v>292</v>
       </c>
-      <c r="C3" s="89" t="s">
+      <c r="C3" s="84" t="s">
         <v>293</v>
       </c>
-      <c r="E3" s="98" t="s">
+      <c r="E3" s="93" t="s">
         <v>378</v>
       </c>
-      <c r="F3" s="98" t="s">
+      <c r="F3" s="93" t="s">
         <v>359</v>
       </c>
-      <c r="G3" s="98" t="s">
+      <c r="G3" s="93" t="s">
         <v>379</v>
       </c>
-      <c r="H3" s="98" t="s">
+      <c r="H3" s="93" t="s">
         <v>380</v>
       </c>
-      <c r="I3" s="98" t="s">
+      <c r="I3" s="93" t="s">
         <v>381</v>
       </c>
-      <c r="J3" s="98" t="s">
+      <c r="J3" s="93" t="s">
         <v>57</v>
       </c>
-      <c r="K3" s="98" t="s">
+      <c r="K3" s="93" t="s">
         <v>382</v>
       </c>
-      <c r="M3" s="110" t="s">
+      <c r="M3" s="102" t="s">
         <v>375</v>
       </c>
     </row>
     <row r="4" spans="1:14" s="3" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A4" s="73"/>
-      <c r="B4" s="90" t="s">
+      <c r="A4" s="72"/>
+      <c r="B4" s="85" t="s">
         <v>294</v>
       </c>
-      <c r="C4" s="91" t="s">
+      <c r="C4" s="86" t="s">
         <v>295</v>
       </c>
-      <c r="M4" s="105" t="s">
+      <c r="M4" s="97" t="s">
         <v>350</v>
       </c>
       <c r="N4" s="3" t="s">
@@ -7881,1353 +7823,1353 @@
       </c>
     </row>
     <row r="5" spans="1:14" s="3" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A5" s="73">
+      <c r="A5" s="72">
         <v>1</v>
       </c>
-      <c r="B5" s="90" t="s">
+      <c r="B5" s="85" t="s">
         <v>337</v>
       </c>
-      <c r="C5" s="97" t="s">
+      <c r="C5" s="92" t="s">
         <v>340</v>
       </c>
-      <c r="E5" s="105" t="s">
-        <v>350</v>
-      </c>
-      <c r="F5" s="105" t="s">
-        <v>350</v>
-      </c>
-      <c r="G5" s="105" t="s">
-        <v>350</v>
-      </c>
-      <c r="H5" s="105" t="s">
-        <v>350</v>
-      </c>
-      <c r="I5" s="105" t="s">
-        <v>350</v>
-      </c>
-      <c r="J5" s="105" t="s">
-        <v>350</v>
-      </c>
-      <c r="K5" s="105" t="s">
-        <v>350</v>
-      </c>
-      <c r="M5" s="104"/>
+      <c r="E5" s="97" t="s">
+        <v>350</v>
+      </c>
+      <c r="F5" s="97" t="s">
+        <v>350</v>
+      </c>
+      <c r="G5" s="97" t="s">
+        <v>350</v>
+      </c>
+      <c r="H5" s="97" t="s">
+        <v>350</v>
+      </c>
+      <c r="I5" s="97" t="s">
+        <v>350</v>
+      </c>
+      <c r="J5" s="97" t="s">
+        <v>350</v>
+      </c>
+      <c r="K5" s="97" t="s">
+        <v>350</v>
+      </c>
+      <c r="M5" s="96"/>
       <c r="N5" s="3" t="s">
         <v>377</v>
       </c>
     </row>
     <row r="6" spans="1:14" s="3" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A6" s="73">
+      <c r="A6" s="72">
         <v>2</v>
       </c>
-      <c r="B6" s="90" t="s">
+      <c r="B6" s="85" t="s">
         <v>338</v>
       </c>
-      <c r="C6" s="97" t="s">
+      <c r="C6" s="92" t="s">
         <v>341</v>
       </c>
-      <c r="E6" s="105" t="s">
-        <v>350</v>
-      </c>
-      <c r="F6" s="105" t="s">
-        <v>350</v>
-      </c>
-      <c r="G6" s="105" t="s">
-        <v>350</v>
-      </c>
-      <c r="H6" s="105" t="s">
-        <v>350</v>
-      </c>
-      <c r="I6" s="105" t="s">
-        <v>350</v>
-      </c>
-      <c r="J6" s="105" t="s">
-        <v>350</v>
-      </c>
-      <c r="K6" s="105" t="s">
+      <c r="E6" s="97" t="s">
+        <v>350</v>
+      </c>
+      <c r="F6" s="97" t="s">
+        <v>350</v>
+      </c>
+      <c r="G6" s="97" t="s">
+        <v>350</v>
+      </c>
+      <c r="H6" s="97" t="s">
+        <v>350</v>
+      </c>
+      <c r="I6" s="97" t="s">
+        <v>350</v>
+      </c>
+      <c r="J6" s="97" t="s">
+        <v>350</v>
+      </c>
+      <c r="K6" s="97" t="s">
         <v>350</v>
       </c>
     </row>
     <row r="7" spans="1:14" s="3" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A7" s="73">
+      <c r="A7" s="72">
         <v>3</v>
       </c>
-      <c r="B7" s="90" t="s">
+      <c r="B7" s="85" t="s">
         <v>339</v>
       </c>
-      <c r="C7" s="97" t="s">
+      <c r="C7" s="92" t="s">
         <v>342</v>
       </c>
-      <c r="E7" s="105" t="s">
-        <v>350</v>
-      </c>
-      <c r="F7" s="105" t="s">
-        <v>350</v>
-      </c>
-      <c r="G7" s="105" t="s">
-        <v>350</v>
-      </c>
-      <c r="H7" s="105" t="s">
-        <v>350</v>
-      </c>
-      <c r="I7" s="105" t="s">
-        <v>350</v>
-      </c>
-      <c r="J7" s="105" t="s">
-        <v>350</v>
-      </c>
-      <c r="K7" s="105" t="s">
+      <c r="E7" s="97" t="s">
+        <v>350</v>
+      </c>
+      <c r="F7" s="97" t="s">
+        <v>350</v>
+      </c>
+      <c r="G7" s="97" t="s">
+        <v>350</v>
+      </c>
+      <c r="H7" s="97" t="s">
+        <v>350</v>
+      </c>
+      <c r="I7" s="97" t="s">
+        <v>350</v>
+      </c>
+      <c r="J7" s="97" t="s">
+        <v>350</v>
+      </c>
+      <c r="K7" s="97" t="s">
         <v>350</v>
       </c>
     </row>
     <row r="8" spans="1:14" s="3" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A8" s="73">
+      <c r="A8" s="72">
         <v>4</v>
       </c>
-      <c r="B8" s="90" t="s">
+      <c r="B8" s="85" t="s">
         <v>296</v>
       </c>
-      <c r="C8" s="93" t="s">
+      <c r="C8" s="88" t="s">
         <v>297</v>
       </c>
-      <c r="E8" s="105" t="s">
-        <v>350</v>
-      </c>
-      <c r="F8" s="105" t="s">
-        <v>350</v>
-      </c>
-      <c r="G8" s="105" t="s">
-        <v>350</v>
-      </c>
-      <c r="H8" s="105" t="s">
-        <v>350</v>
-      </c>
-      <c r="I8" s="105" t="s">
-        <v>350</v>
-      </c>
-      <c r="J8" s="105" t="s">
-        <v>350</v>
-      </c>
-      <c r="K8" s="105" t="s">
+      <c r="E8" s="97" t="s">
+        <v>350</v>
+      </c>
+      <c r="F8" s="97" t="s">
+        <v>350</v>
+      </c>
+      <c r="G8" s="97" t="s">
+        <v>350</v>
+      </c>
+      <c r="H8" s="97" t="s">
+        <v>350</v>
+      </c>
+      <c r="I8" s="97" t="s">
+        <v>350</v>
+      </c>
+      <c r="J8" s="97" t="s">
+        <v>350</v>
+      </c>
+      <c r="K8" s="97" t="s">
         <v>350</v>
       </c>
     </row>
     <row r="9" spans="1:14" s="3" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A9" s="73">
+      <c r="A9" s="72">
         <v>5</v>
       </c>
-      <c r="B9" s="90" t="s">
+      <c r="B9" s="85" t="s">
         <v>298</v>
       </c>
-      <c r="C9" s="93" t="s">
+      <c r="C9" s="88" t="s">
         <v>299</v>
       </c>
-      <c r="E9" s="104"/>
-      <c r="F9" s="105" t="s">
-        <v>350</v>
-      </c>
-      <c r="G9" s="105" t="s">
-        <v>350</v>
-      </c>
-      <c r="H9" s="105" t="s">
-        <v>350</v>
-      </c>
-      <c r="I9" s="105" t="s">
-        <v>350</v>
-      </c>
-      <c r="J9" s="105" t="s">
-        <v>350</v>
-      </c>
-      <c r="K9" s="105" t="s">
+      <c r="E9" s="96"/>
+      <c r="F9" s="97" t="s">
+        <v>350</v>
+      </c>
+      <c r="G9" s="97" t="s">
+        <v>350</v>
+      </c>
+      <c r="H9" s="97" t="s">
+        <v>350</v>
+      </c>
+      <c r="I9" s="97" t="s">
+        <v>350</v>
+      </c>
+      <c r="J9" s="97" t="s">
+        <v>350</v>
+      </c>
+      <c r="K9" s="97" t="s">
         <v>350</v>
       </c>
     </row>
     <row r="10" spans="1:14" s="3" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A10" s="73">
+      <c r="A10" s="72">
         <v>6</v>
       </c>
-      <c r="B10" s="90" t="s">
+      <c r="B10" s="85" t="s">
         <v>45</v>
       </c>
-      <c r="C10" s="106" t="s">
+      <c r="C10" s="98" t="s">
         <v>300</v>
       </c>
-      <c r="E10" s="105" t="s">
-        <v>350</v>
-      </c>
-      <c r="F10" s="105" t="s">
-        <v>350</v>
-      </c>
-      <c r="G10" s="105" t="s">
-        <v>350</v>
-      </c>
-      <c r="H10" s="105" t="s">
-        <v>350</v>
-      </c>
-      <c r="I10" s="105" t="s">
-        <v>350</v>
-      </c>
-      <c r="J10" s="105" t="s">
-        <v>350</v>
-      </c>
-      <c r="K10" s="105" t="s">
+      <c r="E10" s="97" t="s">
+        <v>350</v>
+      </c>
+      <c r="F10" s="97" t="s">
+        <v>350</v>
+      </c>
+      <c r="G10" s="97" t="s">
+        <v>350</v>
+      </c>
+      <c r="H10" s="97" t="s">
+        <v>350</v>
+      </c>
+      <c r="I10" s="97" t="s">
+        <v>350</v>
+      </c>
+      <c r="J10" s="97" t="s">
+        <v>350</v>
+      </c>
+      <c r="K10" s="97" t="s">
         <v>350</v>
       </c>
     </row>
     <row r="11" spans="1:14" s="3" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A11" s="73">
+      <c r="A11" s="72">
         <v>7</v>
       </c>
-      <c r="B11" s="94" t="s">
+      <c r="B11" s="89" t="s">
         <v>59</v>
       </c>
-      <c r="C11" s="92" t="s">
+      <c r="C11" s="87" t="s">
         <v>301</v>
       </c>
-      <c r="E11" s="105" t="s">
-        <v>350</v>
-      </c>
-      <c r="F11" s="105" t="s">
-        <v>350</v>
-      </c>
-      <c r="G11" s="105" t="s">
-        <v>350</v>
-      </c>
-      <c r="H11" s="105" t="s">
-        <v>350</v>
-      </c>
-      <c r="I11" s="105" t="s">
-        <v>350</v>
-      </c>
-      <c r="J11" s="105" t="s">
-        <v>350</v>
-      </c>
-      <c r="K11" s="105" t="s">
+      <c r="E11" s="97" t="s">
+        <v>350</v>
+      </c>
+      <c r="F11" s="97" t="s">
+        <v>350</v>
+      </c>
+      <c r="G11" s="97" t="s">
+        <v>350</v>
+      </c>
+      <c r="H11" s="97" t="s">
+        <v>350</v>
+      </c>
+      <c r="I11" s="97" t="s">
+        <v>350</v>
+      </c>
+      <c r="J11" s="97" t="s">
+        <v>350</v>
+      </c>
+      <c r="K11" s="97" t="s">
         <v>350</v>
       </c>
     </row>
     <row r="12" spans="1:14" s="3" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A12" s="73">
+      <c r="A12" s="72">
         <v>8</v>
       </c>
-      <c r="B12" s="90" t="s">
+      <c r="B12" s="85" t="s">
         <v>63</v>
       </c>
-      <c r="C12" s="92" t="s">
+      <c r="C12" s="87" t="s">
         <v>302</v>
       </c>
-      <c r="E12" s="105" t="s">
-        <v>350</v>
-      </c>
-      <c r="F12" s="105" t="s">
-        <v>350</v>
-      </c>
-      <c r="G12" s="105" t="s">
-        <v>350</v>
-      </c>
-      <c r="H12" s="105" t="s">
-        <v>350</v>
-      </c>
-      <c r="I12" s="105" t="s">
-        <v>350</v>
-      </c>
-      <c r="J12" s="105" t="s">
-        <v>350</v>
-      </c>
-      <c r="K12" s="105" t="s">
+      <c r="E12" s="97" t="s">
+        <v>350</v>
+      </c>
+      <c r="F12" s="97" t="s">
+        <v>350</v>
+      </c>
+      <c r="G12" s="97" t="s">
+        <v>350</v>
+      </c>
+      <c r="H12" s="97" t="s">
+        <v>350</v>
+      </c>
+      <c r="I12" s="97" t="s">
+        <v>350</v>
+      </c>
+      <c r="J12" s="97" t="s">
+        <v>350</v>
+      </c>
+      <c r="K12" s="97" t="s">
         <v>350</v>
       </c>
     </row>
     <row r="13" spans="1:14" s="3" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A13" s="73">
+      <c r="A13" s="72">
         <v>9</v>
       </c>
-      <c r="B13" s="90" t="s">
+      <c r="B13" s="85" t="s">
         <v>74</v>
       </c>
-      <c r="C13" s="92" t="s">
+      <c r="C13" s="87" t="s">
         <v>303</v>
       </c>
-      <c r="E13" s="105" t="s">
-        <v>350</v>
-      </c>
-      <c r="F13" s="105" t="s">
-        <v>350</v>
-      </c>
-      <c r="G13" s="105" t="s">
-        <v>350</v>
-      </c>
-      <c r="H13" s="105" t="s">
-        <v>350</v>
-      </c>
-      <c r="I13" s="105" t="s">
-        <v>350</v>
-      </c>
-      <c r="J13" s="105" t="s">
-        <v>350</v>
-      </c>
-      <c r="K13" s="105" t="s">
+      <c r="E13" s="97" t="s">
+        <v>350</v>
+      </c>
+      <c r="F13" s="97" t="s">
+        <v>350</v>
+      </c>
+      <c r="G13" s="97" t="s">
+        <v>350</v>
+      </c>
+      <c r="H13" s="97" t="s">
+        <v>350</v>
+      </c>
+      <c r="I13" s="97" t="s">
+        <v>350</v>
+      </c>
+      <c r="J13" s="97" t="s">
+        <v>350</v>
+      </c>
+      <c r="K13" s="97" t="s">
         <v>350</v>
       </c>
     </row>
     <row r="14" spans="1:14" s="3" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A14" s="73">
+      <c r="A14" s="72">
         <v>10</v>
       </c>
-      <c r="B14" s="94" t="s">
+      <c r="B14" s="89" t="s">
         <v>304</v>
       </c>
-      <c r="C14" s="92" t="s">
+      <c r="C14" s="87" t="s">
         <v>305</v>
       </c>
-      <c r="E14" s="105" t="s">
-        <v>350</v>
-      </c>
-      <c r="F14" s="104"/>
-      <c r="G14" s="105" t="s">
-        <v>350</v>
-      </c>
-      <c r="H14" s="104"/>
-      <c r="I14" s="104"/>
-      <c r="J14" s="104"/>
-      <c r="K14" s="104"/>
+      <c r="E14" s="97" t="s">
+        <v>350</v>
+      </c>
+      <c r="F14" s="96"/>
+      <c r="G14" s="97" t="s">
+        <v>350</v>
+      </c>
+      <c r="H14" s="96"/>
+      <c r="I14" s="96"/>
+      <c r="J14" s="96"/>
+      <c r="K14" s="96"/>
     </row>
     <row r="15" spans="1:14" s="3" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A15" s="73">
+      <c r="A15" s="72">
         <v>11</v>
       </c>
-      <c r="B15" s="94" t="s">
+      <c r="B15" s="89" t="s">
         <v>84</v>
       </c>
-      <c r="C15" s="92" t="s">
+      <c r="C15" s="87" t="s">
         <v>306</v>
       </c>
-      <c r="E15" s="105" t="s">
-        <v>350</v>
-      </c>
-      <c r="F15" s="105" t="s">
-        <v>350</v>
-      </c>
-      <c r="G15" s="105" t="s">
-        <v>350</v>
-      </c>
-      <c r="H15" s="105" t="s">
-        <v>350</v>
-      </c>
-      <c r="I15" s="105" t="s">
-        <v>350</v>
-      </c>
-      <c r="J15" s="105" t="s">
-        <v>350</v>
-      </c>
-      <c r="K15" s="105" t="s">
+      <c r="E15" s="97" t="s">
+        <v>350</v>
+      </c>
+      <c r="F15" s="97" t="s">
+        <v>350</v>
+      </c>
+      <c r="G15" s="97" t="s">
+        <v>350</v>
+      </c>
+      <c r="H15" s="97" t="s">
+        <v>350</v>
+      </c>
+      <c r="I15" s="97" t="s">
+        <v>350</v>
+      </c>
+      <c r="J15" s="97" t="s">
+        <v>350</v>
+      </c>
+      <c r="K15" s="97" t="s">
         <v>350</v>
       </c>
     </row>
     <row r="16" spans="1:14" s="3" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A16" s="73">
+      <c r="A16" s="72">
         <v>12</v>
       </c>
-      <c r="B16" s="94" t="s">
+      <c r="B16" s="89" t="s">
         <v>90</v>
       </c>
-      <c r="C16" s="92" t="s">
+      <c r="C16" s="87" t="s">
         <v>307</v>
       </c>
-      <c r="E16" s="105" t="s">
-        <v>350</v>
-      </c>
-      <c r="F16" s="105" t="s">
-        <v>350</v>
-      </c>
-      <c r="G16" s="105" t="s">
-        <v>350</v>
-      </c>
-      <c r="H16" s="105" t="s">
-        <v>350</v>
-      </c>
-      <c r="I16" s="105" t="s">
-        <v>350</v>
-      </c>
-      <c r="J16" s="105" t="s">
-        <v>350</v>
-      </c>
-      <c r="K16" s="105" t="s">
+      <c r="E16" s="97" t="s">
+        <v>350</v>
+      </c>
+      <c r="F16" s="97" t="s">
+        <v>350</v>
+      </c>
+      <c r="G16" s="97" t="s">
+        <v>350</v>
+      </c>
+      <c r="H16" s="97" t="s">
+        <v>350</v>
+      </c>
+      <c r="I16" s="97" t="s">
+        <v>350</v>
+      </c>
+      <c r="J16" s="97" t="s">
+        <v>350</v>
+      </c>
+      <c r="K16" s="97" t="s">
         <v>350</v>
       </c>
     </row>
     <row r="17" spans="1:11" s="3" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A17" s="73">
+      <c r="A17" s="72">
         <v>13</v>
       </c>
-      <c r="B17" s="94" t="s">
+      <c r="B17" s="89" t="s">
         <v>96</v>
       </c>
-      <c r="C17" s="92" t="s">
+      <c r="C17" s="87" t="s">
         <v>308</v>
       </c>
-      <c r="E17" s="105" t="s">
-        <v>350</v>
-      </c>
-      <c r="F17" s="105" t="s">
-        <v>350</v>
-      </c>
-      <c r="G17" s="105" t="s">
-        <v>350</v>
-      </c>
-      <c r="H17" s="105" t="s">
-        <v>350</v>
-      </c>
-      <c r="I17" s="105" t="s">
-        <v>350</v>
-      </c>
-      <c r="J17" s="105" t="s">
-        <v>350</v>
-      </c>
-      <c r="K17" s="105" t="s">
+      <c r="E17" s="97" t="s">
+        <v>350</v>
+      </c>
+      <c r="F17" s="97" t="s">
+        <v>350</v>
+      </c>
+      <c r="G17" s="97" t="s">
+        <v>350</v>
+      </c>
+      <c r="H17" s="97" t="s">
+        <v>350</v>
+      </c>
+      <c r="I17" s="97" t="s">
+        <v>350</v>
+      </c>
+      <c r="J17" s="97" t="s">
+        <v>350</v>
+      </c>
+      <c r="K17" s="97" t="s">
         <v>350</v>
       </c>
     </row>
     <row r="18" spans="1:11" s="3" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A18" s="73">
+      <c r="A18" s="72">
         <v>14</v>
       </c>
-      <c r="B18" s="94" t="s">
+      <c r="B18" s="89" t="s">
         <v>98</v>
       </c>
-      <c r="C18" s="92" t="s">
+      <c r="C18" s="87" t="s">
         <v>360</v>
       </c>
-      <c r="E18" s="104"/>
-      <c r="F18" s="105" t="s">
-        <v>350</v>
-      </c>
-      <c r="G18" s="104"/>
-      <c r="H18" s="105" t="s">
-        <v>350</v>
-      </c>
-      <c r="I18" s="104"/>
-      <c r="J18" s="105" t="s">
-        <v>350</v>
-      </c>
-      <c r="K18" s="104"/>
+      <c r="E18" s="96"/>
+      <c r="F18" s="97" t="s">
+        <v>350</v>
+      </c>
+      <c r="G18" s="96"/>
+      <c r="H18" s="97" t="s">
+        <v>350</v>
+      </c>
+      <c r="I18" s="96"/>
+      <c r="J18" s="97" t="s">
+        <v>350</v>
+      </c>
+      <c r="K18" s="96"/>
     </row>
     <row r="19" spans="1:11" s="3" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A19" s="73">
+      <c r="A19" s="72">
         <v>15</v>
       </c>
-      <c r="B19" s="94" t="s">
+      <c r="B19" s="89" t="s">
         <v>309</v>
       </c>
-      <c r="C19" s="92" t="s">
+      <c r="C19" s="87" t="s">
         <v>361</v>
       </c>
-      <c r="E19" s="105" t="s">
-        <v>350</v>
-      </c>
-      <c r="F19" s="104"/>
-      <c r="G19" s="105" t="s">
-        <v>350</v>
-      </c>
-      <c r="H19" s="104"/>
-      <c r="I19" s="105" t="s">
-        <v>350</v>
-      </c>
-      <c r="J19" s="104"/>
-      <c r="K19" s="105" t="s">
+      <c r="E19" s="97" t="s">
+        <v>350</v>
+      </c>
+      <c r="F19" s="96"/>
+      <c r="G19" s="97" t="s">
+        <v>350</v>
+      </c>
+      <c r="H19" s="96"/>
+      <c r="I19" s="97" t="s">
+        <v>350</v>
+      </c>
+      <c r="J19" s="96"/>
+      <c r="K19" s="97" t="s">
         <v>350</v>
       </c>
     </row>
     <row r="20" spans="1:11" s="3" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A20" s="73">
+      <c r="A20" s="72">
         <v>16</v>
       </c>
-      <c r="B20" s="94" t="s">
+      <c r="B20" s="89" t="s">
         <v>407</v>
       </c>
-      <c r="C20" s="92" t="s">
+      <c r="C20" s="87" t="s">
         <v>418</v>
       </c>
-      <c r="E20" s="104"/>
-      <c r="F20" s="105" t="s">
-        <v>350</v>
-      </c>
-      <c r="G20" s="105" t="s">
-        <v>350</v>
-      </c>
-      <c r="H20" s="105" t="s">
-        <v>350</v>
-      </c>
-      <c r="I20" s="105" t="s">
-        <v>350</v>
-      </c>
-      <c r="J20" s="105" t="s">
-        <v>350</v>
-      </c>
-      <c r="K20" s="105" t="s">
+      <c r="E20" s="96"/>
+      <c r="F20" s="97" t="s">
+        <v>350</v>
+      </c>
+      <c r="G20" s="97" t="s">
+        <v>350</v>
+      </c>
+      <c r="H20" s="97" t="s">
+        <v>350</v>
+      </c>
+      <c r="I20" s="97" t="s">
+        <v>350</v>
+      </c>
+      <c r="J20" s="97" t="s">
+        <v>350</v>
+      </c>
+      <c r="K20" s="97" t="s">
         <v>350</v>
       </c>
     </row>
     <row r="21" spans="1:11" s="3" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A21" s="73">
+      <c r="A21" s="72">
         <v>17</v>
       </c>
-      <c r="B21" s="94" t="s">
+      <c r="B21" s="89" t="s">
         <v>408</v>
       </c>
-      <c r="C21" s="92" t="s">
+      <c r="C21" s="87" t="s">
         <v>310</v>
       </c>
-      <c r="E21" s="105" t="s">
-        <v>350</v>
-      </c>
-      <c r="F21" s="104"/>
-      <c r="G21" s="105" t="s">
-        <v>350</v>
-      </c>
-      <c r="H21" s="104"/>
-      <c r="I21" s="105" t="s">
-        <v>350</v>
-      </c>
-      <c r="J21" s="104"/>
-      <c r="K21" s="105" t="s">
+      <c r="E21" s="97" t="s">
+        <v>350</v>
+      </c>
+      <c r="F21" s="96"/>
+      <c r="G21" s="97" t="s">
+        <v>350</v>
+      </c>
+      <c r="H21" s="96"/>
+      <c r="I21" s="97" t="s">
+        <v>350</v>
+      </c>
+      <c r="J21" s="96"/>
+      <c r="K21" s="97" t="s">
         <v>350</v>
       </c>
     </row>
     <row r="22" spans="1:11" s="3" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A22" s="73">
+      <c r="A22" s="72">
         <v>18</v>
       </c>
-      <c r="B22" s="94" t="s">
+      <c r="B22" s="89" t="s">
         <v>414</v>
       </c>
-      <c r="C22" s="92" t="s">
+      <c r="C22" s="87" t="s">
         <v>419</v>
       </c>
-      <c r="E22" s="105" t="s">
-        <v>350</v>
-      </c>
-      <c r="F22" s="105" t="s">
-        <v>350</v>
-      </c>
-      <c r="G22" s="105" t="s">
-        <v>350</v>
-      </c>
-      <c r="H22" s="105" t="s">
-        <v>350</v>
-      </c>
-      <c r="I22" s="105" t="s">
-        <v>350</v>
-      </c>
-      <c r="J22" s="105" t="s">
-        <v>350</v>
-      </c>
-      <c r="K22" s="105" t="s">
+      <c r="E22" s="97" t="s">
+        <v>350</v>
+      </c>
+      <c r="F22" s="97" t="s">
+        <v>350</v>
+      </c>
+      <c r="G22" s="97" t="s">
+        <v>350</v>
+      </c>
+      <c r="H22" s="97" t="s">
+        <v>350</v>
+      </c>
+      <c r="I22" s="97" t="s">
+        <v>350</v>
+      </c>
+      <c r="J22" s="97" t="s">
+        <v>350</v>
+      </c>
+      <c r="K22" s="97" t="s">
         <v>350</v>
       </c>
     </row>
     <row r="23" spans="1:11" s="3" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A23" s="73">
+      <c r="A23" s="72">
         <v>19</v>
       </c>
-      <c r="B23" s="94" t="s">
+      <c r="B23" s="89" t="s">
         <v>415</v>
       </c>
-      <c r="C23" s="92" t="s">
+      <c r="C23" s="87" t="s">
         <v>420</v>
       </c>
-      <c r="E23" s="105" t="s">
-        <v>350</v>
-      </c>
-      <c r="F23" s="105" t="s">
-        <v>350</v>
-      </c>
-      <c r="G23" s="105" t="s">
-        <v>350</v>
-      </c>
-      <c r="H23" s="105" t="s">
-        <v>350</v>
-      </c>
-      <c r="I23" s="105" t="s">
-        <v>350</v>
-      </c>
-      <c r="J23" s="105" t="s">
-        <v>350</v>
-      </c>
-      <c r="K23" s="105" t="s">
+      <c r="E23" s="97" t="s">
+        <v>350</v>
+      </c>
+      <c r="F23" s="97" t="s">
+        <v>350</v>
+      </c>
+      <c r="G23" s="97" t="s">
+        <v>350</v>
+      </c>
+      <c r="H23" s="97" t="s">
+        <v>350</v>
+      </c>
+      <c r="I23" s="97" t="s">
+        <v>350</v>
+      </c>
+      <c r="J23" s="97" t="s">
+        <v>350</v>
+      </c>
+      <c r="K23" s="97" t="s">
         <v>350</v>
       </c>
     </row>
     <row r="24" spans="1:11" s="3" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A24" s="73">
+      <c r="A24" s="72">
         <v>20</v>
       </c>
-      <c r="B24" s="94" t="s">
+      <c r="B24" s="89" t="s">
         <v>416</v>
       </c>
-      <c r="C24" s="92" t="s">
+      <c r="C24" s="87" t="s">
         <v>421</v>
       </c>
-      <c r="E24" s="105" t="s">
-        <v>350</v>
-      </c>
-      <c r="F24" s="105" t="s">
-        <v>350</v>
-      </c>
-      <c r="G24" s="105" t="s">
-        <v>350</v>
-      </c>
-      <c r="H24" s="105" t="s">
-        <v>350</v>
-      </c>
-      <c r="I24" s="105" t="s">
-        <v>350</v>
-      </c>
-      <c r="J24" s="105" t="s">
-        <v>350</v>
-      </c>
-      <c r="K24" s="105" t="s">
+      <c r="E24" s="97" t="s">
+        <v>350</v>
+      </c>
+      <c r="F24" s="97" t="s">
+        <v>350</v>
+      </c>
+      <c r="G24" s="97" t="s">
+        <v>350</v>
+      </c>
+      <c r="H24" s="97" t="s">
+        <v>350</v>
+      </c>
+      <c r="I24" s="97" t="s">
+        <v>350</v>
+      </c>
+      <c r="J24" s="97" t="s">
+        <v>350</v>
+      </c>
+      <c r="K24" s="97" t="s">
         <v>350</v>
       </c>
     </row>
     <row r="25" spans="1:11" s="3" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A25" s="73">
+      <c r="A25" s="72">
         <v>21</v>
       </c>
-      <c r="B25" s="94" t="s">
+      <c r="B25" s="89" t="s">
         <v>417</v>
       </c>
-      <c r="C25" s="92" t="s">
+      <c r="C25" s="87" t="s">
         <v>422</v>
       </c>
-      <c r="E25" s="105" t="s">
-        <v>350</v>
-      </c>
-      <c r="F25" s="105" t="s">
-        <v>350</v>
-      </c>
-      <c r="G25" s="105" t="s">
-        <v>350</v>
-      </c>
-      <c r="H25" s="105" t="s">
-        <v>350</v>
-      </c>
-      <c r="I25" s="105" t="s">
-        <v>350</v>
-      </c>
-      <c r="J25" s="105" t="s">
-        <v>350</v>
-      </c>
-      <c r="K25" s="105" t="s">
+      <c r="E25" s="97" t="s">
+        <v>350</v>
+      </c>
+      <c r="F25" s="97" t="s">
+        <v>350</v>
+      </c>
+      <c r="G25" s="97" t="s">
+        <v>350</v>
+      </c>
+      <c r="H25" s="97" t="s">
+        <v>350</v>
+      </c>
+      <c r="I25" s="97" t="s">
+        <v>350</v>
+      </c>
+      <c r="J25" s="97" t="s">
+        <v>350</v>
+      </c>
+      <c r="K25" s="97" t="s">
         <v>350</v>
       </c>
     </row>
     <row r="26" spans="1:11" s="3" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A26" s="73">
+      <c r="A26" s="72">
         <v>22</v>
       </c>
-      <c r="B26" s="94" t="s">
+      <c r="B26" s="89" t="s">
         <v>132</v>
       </c>
-      <c r="C26" s="97">
+      <c r="C26" s="92">
         <v>4</v>
       </c>
-      <c r="E26" s="105" t="s">
-        <v>350</v>
-      </c>
-      <c r="F26" s="105" t="s">
-        <v>350</v>
-      </c>
-      <c r="G26" s="105" t="s">
-        <v>350</v>
-      </c>
-      <c r="H26" s="105" t="s">
-        <v>350</v>
-      </c>
-      <c r="I26" s="105" t="s">
-        <v>350</v>
-      </c>
-      <c r="J26" s="105" t="s">
-        <v>350</v>
-      </c>
-      <c r="K26" s="105" t="s">
+      <c r="E26" s="97" t="s">
+        <v>350</v>
+      </c>
+      <c r="F26" s="97" t="s">
+        <v>350</v>
+      </c>
+      <c r="G26" s="97" t="s">
+        <v>350</v>
+      </c>
+      <c r="H26" s="97" t="s">
+        <v>350</v>
+      </c>
+      <c r="I26" s="97" t="s">
+        <v>350</v>
+      </c>
+      <c r="J26" s="97" t="s">
+        <v>350</v>
+      </c>
+      <c r="K26" s="97" t="s">
         <v>350</v>
       </c>
     </row>
     <row r="27" spans="1:11" s="3" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A27" s="73">
+      <c r="A27" s="72">
         <v>23</v>
       </c>
-      <c r="B27" s="94" t="s">
+      <c r="B27" s="89" t="s">
         <v>144</v>
       </c>
-      <c r="C27" s="92" t="s">
+      <c r="C27" s="87" t="s">
         <v>311</v>
       </c>
-      <c r="E27" s="105" t="s">
-        <v>350</v>
-      </c>
-      <c r="F27" s="105" t="s">
-        <v>350</v>
-      </c>
-      <c r="G27" s="105" t="s">
-        <v>350</v>
-      </c>
-      <c r="H27" s="105" t="s">
-        <v>350</v>
-      </c>
-      <c r="I27" s="105" t="s">
-        <v>350</v>
-      </c>
-      <c r="J27" s="105" t="s">
-        <v>350</v>
-      </c>
-      <c r="K27" s="105" t="s">
+      <c r="E27" s="97" t="s">
+        <v>350</v>
+      </c>
+      <c r="F27" s="97" t="s">
+        <v>350</v>
+      </c>
+      <c r="G27" s="97" t="s">
+        <v>350</v>
+      </c>
+      <c r="H27" s="97" t="s">
+        <v>350</v>
+      </c>
+      <c r="I27" s="97" t="s">
+        <v>350</v>
+      </c>
+      <c r="J27" s="97" t="s">
+        <v>350</v>
+      </c>
+      <c r="K27" s="97" t="s">
         <v>350</v>
       </c>
     </row>
     <row r="28" spans="1:11" s="3" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A28" s="73">
+      <c r="A28" s="72">
         <v>24</v>
       </c>
-      <c r="B28" s="94" t="s">
+      <c r="B28" s="89" t="s">
         <v>312</v>
       </c>
-      <c r="C28" s="92" t="s">
+      <c r="C28" s="87" t="s">
         <v>313</v>
       </c>
-      <c r="E28" s="105" t="s">
-        <v>350</v>
-      </c>
-      <c r="F28" s="105" t="s">
-        <v>350</v>
-      </c>
-      <c r="G28" s="105" t="s">
-        <v>350</v>
-      </c>
-      <c r="H28" s="105" t="s">
-        <v>350</v>
-      </c>
-      <c r="I28" s="105" t="s">
-        <v>350</v>
-      </c>
-      <c r="J28" s="105" t="s">
-        <v>350</v>
-      </c>
-      <c r="K28" s="105" t="s">
+      <c r="E28" s="97" t="s">
+        <v>350</v>
+      </c>
+      <c r="F28" s="97" t="s">
+        <v>350</v>
+      </c>
+      <c r="G28" s="97" t="s">
+        <v>350</v>
+      </c>
+      <c r="H28" s="97" t="s">
+        <v>350</v>
+      </c>
+      <c r="I28" s="97" t="s">
+        <v>350</v>
+      </c>
+      <c r="J28" s="97" t="s">
+        <v>350</v>
+      </c>
+      <c r="K28" s="97" t="s">
         <v>350</v>
       </c>
     </row>
     <row r="29" spans="1:11" s="3" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A29" s="73">
+      <c r="A29" s="72">
         <v>25</v>
       </c>
-      <c r="B29" s="94" t="s">
+      <c r="B29" s="89" t="s">
         <v>164</v>
       </c>
-      <c r="C29" s="92" t="s">
+      <c r="C29" s="87" t="s">
         <v>314</v>
       </c>
-      <c r="E29" s="105" t="s">
-        <v>350</v>
-      </c>
-      <c r="F29" s="105" t="s">
-        <v>350</v>
-      </c>
-      <c r="G29" s="105" t="s">
-        <v>350</v>
-      </c>
-      <c r="H29" s="105" t="s">
-        <v>350</v>
-      </c>
-      <c r="I29" s="105" t="s">
-        <v>350</v>
-      </c>
-      <c r="J29" s="105" t="s">
-        <v>350</v>
-      </c>
-      <c r="K29" s="105" t="s">
+      <c r="E29" s="97" t="s">
+        <v>350</v>
+      </c>
+      <c r="F29" s="97" t="s">
+        <v>350</v>
+      </c>
+      <c r="G29" s="97" t="s">
+        <v>350</v>
+      </c>
+      <c r="H29" s="97" t="s">
+        <v>350</v>
+      </c>
+      <c r="I29" s="97" t="s">
+        <v>350</v>
+      </c>
+      <c r="J29" s="97" t="s">
+        <v>350</v>
+      </c>
+      <c r="K29" s="97" t="s">
         <v>350</v>
       </c>
     </row>
     <row r="30" spans="1:11" s="3" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A30" s="73">
+      <c r="A30" s="72">
         <v>26</v>
       </c>
-      <c r="B30" s="94" t="s">
+      <c r="B30" s="89" t="s">
         <v>177</v>
       </c>
-      <c r="C30" s="92" t="s">
+      <c r="C30" s="87" t="s">
         <v>315</v>
       </c>
-      <c r="E30" s="104"/>
-      <c r="F30" s="105" t="s">
-        <v>350</v>
-      </c>
-      <c r="G30" s="105" t="s">
-        <v>350</v>
-      </c>
-      <c r="H30" s="105" t="s">
-        <v>350</v>
-      </c>
-      <c r="I30" s="105" t="s">
-        <v>350</v>
-      </c>
-      <c r="J30" s="105" t="s">
-        <v>350</v>
-      </c>
-      <c r="K30" s="105" t="s">
+      <c r="E30" s="96"/>
+      <c r="F30" s="97" t="s">
+        <v>350</v>
+      </c>
+      <c r="G30" s="97" t="s">
+        <v>350</v>
+      </c>
+      <c r="H30" s="97" t="s">
+        <v>350</v>
+      </c>
+      <c r="I30" s="97" t="s">
+        <v>350</v>
+      </c>
+      <c r="J30" s="97" t="s">
+        <v>350</v>
+      </c>
+      <c r="K30" s="97" t="s">
         <v>350</v>
       </c>
     </row>
     <row r="31" spans="1:11" s="3" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A31" s="73">
+      <c r="A31" s="72">
         <v>27</v>
       </c>
-      <c r="B31" s="94" t="s">
+      <c r="B31" s="89" t="s">
         <v>182</v>
       </c>
-      <c r="C31" s="92" t="s">
+      <c r="C31" s="87" t="s">
         <v>316</v>
       </c>
-      <c r="E31" s="104"/>
-      <c r="F31" s="104"/>
-      <c r="G31" s="104"/>
-      <c r="H31" s="105" t="s">
-        <v>350</v>
-      </c>
-      <c r="I31" s="105" t="s">
-        <v>350</v>
-      </c>
-      <c r="J31" s="105" t="s">
-        <v>350</v>
-      </c>
-      <c r="K31" s="105" t="s">
+      <c r="E31" s="96"/>
+      <c r="F31" s="96"/>
+      <c r="G31" s="96"/>
+      <c r="H31" s="97" t="s">
+        <v>350</v>
+      </c>
+      <c r="I31" s="97" t="s">
+        <v>350</v>
+      </c>
+      <c r="J31" s="97" t="s">
+        <v>350</v>
+      </c>
+      <c r="K31" s="97" t="s">
         <v>350</v>
       </c>
     </row>
     <row r="32" spans="1:11" s="3" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A32" s="73">
+      <c r="A32" s="72">
         <v>28</v>
       </c>
-      <c r="B32" s="94" t="s">
+      <c r="B32" s="89" t="s">
         <v>185</v>
       </c>
-      <c r="C32" s="92">
+      <c r="C32" s="87">
         <v>7</v>
       </c>
-      <c r="E32" s="105" t="s">
-        <v>350</v>
-      </c>
-      <c r="F32" s="105" t="s">
-        <v>350</v>
-      </c>
-      <c r="G32" s="105" t="s">
-        <v>350</v>
-      </c>
-      <c r="H32" s="104"/>
-      <c r="I32" s="104"/>
-      <c r="J32" s="104"/>
-      <c r="K32" s="104"/>
+      <c r="E32" s="97" t="s">
+        <v>350</v>
+      </c>
+      <c r="F32" s="97" t="s">
+        <v>350</v>
+      </c>
+      <c r="G32" s="97" t="s">
+        <v>350</v>
+      </c>
+      <c r="H32" s="96"/>
+      <c r="I32" s="96"/>
+      <c r="J32" s="96"/>
+      <c r="K32" s="96"/>
     </row>
     <row r="33" spans="1:11" s="3" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A33" s="73">
+      <c r="A33" s="72">
         <v>29</v>
       </c>
-      <c r="B33" s="94" t="s">
+      <c r="B33" s="89" t="s">
         <v>188</v>
       </c>
-      <c r="C33" s="92" t="s">
+      <c r="C33" s="87" t="s">
         <v>317</v>
       </c>
-      <c r="E33" s="105" t="s">
-        <v>350</v>
-      </c>
-      <c r="F33" s="105" t="s">
-        <v>350</v>
-      </c>
-      <c r="G33" s="105" t="s">
-        <v>350</v>
-      </c>
-      <c r="H33" s="105" t="s">
-        <v>350</v>
-      </c>
-      <c r="I33" s="105" t="s">
-        <v>350</v>
-      </c>
-      <c r="J33" s="105" t="s">
-        <v>350</v>
-      </c>
-      <c r="K33" s="105" t="s">
+      <c r="E33" s="97" t="s">
+        <v>350</v>
+      </c>
+      <c r="F33" s="97" t="s">
+        <v>350</v>
+      </c>
+      <c r="G33" s="97" t="s">
+        <v>350</v>
+      </c>
+      <c r="H33" s="97" t="s">
+        <v>350</v>
+      </c>
+      <c r="I33" s="97" t="s">
+        <v>350</v>
+      </c>
+      <c r="J33" s="97" t="s">
+        <v>350</v>
+      </c>
+      <c r="K33" s="97" t="s">
         <v>350</v>
       </c>
     </row>
     <row r="34" spans="1:11" s="3" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A34" s="73">
+      <c r="A34" s="72">
         <v>30</v>
       </c>
-      <c r="B34" s="94" t="s">
+      <c r="B34" s="89" t="s">
         <v>194</v>
       </c>
-      <c r="C34" s="92" t="s">
+      <c r="C34" s="87" t="s">
         <v>318</v>
       </c>
-      <c r="E34" s="105" t="s">
-        <v>350</v>
-      </c>
-      <c r="F34" s="105" t="s">
-        <v>350</v>
-      </c>
-      <c r="G34" s="105" t="s">
-        <v>350</v>
-      </c>
-      <c r="H34" s="105" t="s">
-        <v>350</v>
-      </c>
-      <c r="I34" s="105" t="s">
-        <v>350</v>
-      </c>
-      <c r="J34" s="105" t="s">
-        <v>350</v>
-      </c>
-      <c r="K34" s="105" t="s">
+      <c r="E34" s="97" t="s">
+        <v>350</v>
+      </c>
+      <c r="F34" s="97" t="s">
+        <v>350</v>
+      </c>
+      <c r="G34" s="97" t="s">
+        <v>350</v>
+      </c>
+      <c r="H34" s="97" t="s">
+        <v>350</v>
+      </c>
+      <c r="I34" s="97" t="s">
+        <v>350</v>
+      </c>
+      <c r="J34" s="97" t="s">
+        <v>350</v>
+      </c>
+      <c r="K34" s="97" t="s">
         <v>350</v>
       </c>
     </row>
     <row r="35" spans="1:11" s="3" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A35" s="73">
+      <c r="A35" s="72">
         <v>31</v>
       </c>
-      <c r="B35" s="94" t="s">
+      <c r="B35" s="89" t="s">
         <v>200</v>
       </c>
-      <c r="C35" s="92" t="s">
+      <c r="C35" s="87" t="s">
         <v>319</v>
       </c>
-      <c r="E35" s="105" t="s">
-        <v>350</v>
-      </c>
-      <c r="F35" s="105" t="s">
-        <v>350</v>
-      </c>
-      <c r="G35" s="105" t="s">
-        <v>350</v>
-      </c>
-      <c r="H35" s="104"/>
-      <c r="I35" s="104"/>
-      <c r="J35" s="104"/>
-      <c r="K35" s="104"/>
+      <c r="E35" s="97" t="s">
+        <v>350</v>
+      </c>
+      <c r="F35" s="97" t="s">
+        <v>350</v>
+      </c>
+      <c r="G35" s="97" t="s">
+        <v>350</v>
+      </c>
+      <c r="H35" s="96"/>
+      <c r="I35" s="96"/>
+      <c r="J35" s="96"/>
+      <c r="K35" s="96"/>
     </row>
     <row r="36" spans="1:11" s="3" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A36" s="73">
+      <c r="A36" s="72">
         <v>32</v>
       </c>
-      <c r="B36" s="94" t="s">
+      <c r="B36" s="89" t="s">
         <v>320</v>
       </c>
-      <c r="C36" s="92" t="s">
+      <c r="C36" s="87" t="s">
         <v>321</v>
       </c>
-      <c r="E36" s="105" t="s">
-        <v>350</v>
-      </c>
-      <c r="F36" s="105" t="s">
-        <v>350</v>
-      </c>
-      <c r="G36" s="105" t="s">
-        <v>350</v>
-      </c>
-      <c r="H36" s="105" t="s">
-        <v>350</v>
-      </c>
-      <c r="I36" s="105" t="s">
-        <v>350</v>
-      </c>
-      <c r="J36" s="105" t="s">
-        <v>350</v>
-      </c>
-      <c r="K36" s="105" t="s">
+      <c r="E36" s="97" t="s">
+        <v>350</v>
+      </c>
+      <c r="F36" s="97" t="s">
+        <v>350</v>
+      </c>
+      <c r="G36" s="97" t="s">
+        <v>350</v>
+      </c>
+      <c r="H36" s="97" t="s">
+        <v>350</v>
+      </c>
+      <c r="I36" s="97" t="s">
+        <v>350</v>
+      </c>
+      <c r="J36" s="97" t="s">
+        <v>350</v>
+      </c>
+      <c r="K36" s="97" t="s">
         <v>350</v>
       </c>
     </row>
     <row r="37" spans="1:11" s="3" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A37" s="73">
+      <c r="A37" s="72">
         <v>33</v>
       </c>
-      <c r="B37" s="94" t="s">
+      <c r="B37" s="89" t="s">
         <v>227</v>
       </c>
-      <c r="C37" s="92" t="s">
+      <c r="C37" s="87" t="s">
         <v>322</v>
       </c>
-      <c r="E37" s="105" t="s">
-        <v>350</v>
-      </c>
-      <c r="F37" s="105" t="s">
-        <v>350</v>
-      </c>
-      <c r="G37" s="105" t="s">
-        <v>350</v>
-      </c>
-      <c r="H37" s="104"/>
-      <c r="I37" s="104"/>
-      <c r="J37" s="104"/>
-      <c r="K37" s="104"/>
+      <c r="E37" s="97" t="s">
+        <v>350</v>
+      </c>
+      <c r="F37" s="97" t="s">
+        <v>350</v>
+      </c>
+      <c r="G37" s="97" t="s">
+        <v>350</v>
+      </c>
+      <c r="H37" s="96"/>
+      <c r="I37" s="96"/>
+      <c r="J37" s="96"/>
+      <c r="K37" s="96"/>
     </row>
     <row r="38" spans="1:11" s="3" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A38" s="73">
+      <c r="A38" s="72">
         <v>34</v>
       </c>
-      <c r="B38" s="94" t="s">
+      <c r="B38" s="89" t="s">
         <v>238</v>
       </c>
-      <c r="C38" s="92" t="s">
+      <c r="C38" s="87" t="s">
         <v>323</v>
       </c>
-      <c r="E38" s="105" t="s">
-        <v>350</v>
-      </c>
-      <c r="F38" s="105" t="s">
-        <v>350</v>
-      </c>
-      <c r="G38" s="105" t="s">
-        <v>350</v>
-      </c>
-      <c r="H38" s="105" t="s">
-        <v>350</v>
-      </c>
-      <c r="I38" s="105" t="s">
-        <v>350</v>
-      </c>
-      <c r="J38" s="104"/>
-      <c r="K38" s="104"/>
+      <c r="E38" s="97" t="s">
+        <v>350</v>
+      </c>
+      <c r="F38" s="97" t="s">
+        <v>350</v>
+      </c>
+      <c r="G38" s="97" t="s">
+        <v>350</v>
+      </c>
+      <c r="H38" s="97" t="s">
+        <v>350</v>
+      </c>
+      <c r="I38" s="97" t="s">
+        <v>350</v>
+      </c>
+      <c r="J38" s="96"/>
+      <c r="K38" s="96"/>
     </row>
     <row r="39" spans="1:11" s="3" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A39" s="73">
+      <c r="A39" s="72">
         <v>35</v>
       </c>
-      <c r="B39" s="94" t="s">
+      <c r="B39" s="89" t="s">
         <v>243</v>
       </c>
-      <c r="C39" s="95" t="s">
+      <c r="C39" s="90" t="s">
         <v>368</v>
       </c>
-      <c r="E39" s="105" t="s">
-        <v>350</v>
-      </c>
-      <c r="F39" s="105" t="s">
-        <v>350</v>
-      </c>
-      <c r="G39" s="105" t="s">
-        <v>350</v>
-      </c>
-      <c r="H39" s="104"/>
-      <c r="I39" s="104"/>
-      <c r="J39" s="104"/>
-      <c r="K39" s="104"/>
+      <c r="E39" s="97" t="s">
+        <v>350</v>
+      </c>
+      <c r="F39" s="97" t="s">
+        <v>350</v>
+      </c>
+      <c r="G39" s="97" t="s">
+        <v>350</v>
+      </c>
+      <c r="H39" s="96"/>
+      <c r="I39" s="96"/>
+      <c r="J39" s="96"/>
+      <c r="K39" s="96"/>
     </row>
     <row r="40" spans="1:11" s="3" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A40" s="73">
+      <c r="A40" s="72">
         <v>36</v>
       </c>
-      <c r="B40" s="94" t="s">
+      <c r="B40" s="89" t="s">
         <v>324</v>
       </c>
-      <c r="C40" s="96" t="s">
+      <c r="C40" s="91" t="s">
         <v>325</v>
       </c>
-      <c r="E40" s="105" t="s">
-        <v>350</v>
-      </c>
-      <c r="F40" s="105" t="s">
-        <v>350</v>
-      </c>
-      <c r="G40" s="105" t="s">
-        <v>350</v>
-      </c>
-      <c r="H40" s="105" t="s">
-        <v>350</v>
-      </c>
-      <c r="I40" s="105" t="s">
-        <v>350</v>
-      </c>
-      <c r="J40" s="104"/>
-      <c r="K40" s="104"/>
+      <c r="E40" s="97" t="s">
+        <v>350</v>
+      </c>
+      <c r="F40" s="97" t="s">
+        <v>350</v>
+      </c>
+      <c r="G40" s="97" t="s">
+        <v>350</v>
+      </c>
+      <c r="H40" s="97" t="s">
+        <v>350</v>
+      </c>
+      <c r="I40" s="97" t="s">
+        <v>350</v>
+      </c>
+      <c r="J40" s="96"/>
+      <c r="K40" s="96"/>
     </row>
     <row r="41" spans="1:11" s="3" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A41" s="73">
+      <c r="A41" s="72">
         <v>37</v>
       </c>
-      <c r="B41" s="94" t="s">
+      <c r="B41" s="89" t="s">
         <v>249</v>
       </c>
-      <c r="C41" s="95" t="s">
+      <c r="C41" s="90" t="s">
         <v>372</v>
       </c>
-      <c r="E41" s="105" t="s">
-        <v>350</v>
-      </c>
-      <c r="F41" s="105" t="s">
-        <v>350</v>
-      </c>
-      <c r="G41" s="105" t="s">
-        <v>350</v>
-      </c>
-      <c r="H41" s="105" t="s">
-        <v>350</v>
-      </c>
-      <c r="I41" s="105" t="s">
-        <v>350</v>
-      </c>
-      <c r="J41" s="104"/>
-      <c r="K41" s="104"/>
+      <c r="E41" s="97" t="s">
+        <v>350</v>
+      </c>
+      <c r="F41" s="97" t="s">
+        <v>350</v>
+      </c>
+      <c r="G41" s="97" t="s">
+        <v>350</v>
+      </c>
+      <c r="H41" s="97" t="s">
+        <v>350</v>
+      </c>
+      <c r="I41" s="97" t="s">
+        <v>350</v>
+      </c>
+      <c r="J41" s="96"/>
+      <c r="K41" s="96"/>
     </row>
     <row r="42" spans="1:11" s="3" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A42" s="73">
+      <c r="A42" s="72">
         <v>38</v>
       </c>
-      <c r="B42" s="94" t="s">
+      <c r="B42" s="89" t="s">
         <v>383</v>
       </c>
-      <c r="C42" s="92" t="s">
+      <c r="C42" s="87" t="s">
         <v>384</v>
       </c>
-      <c r="E42" s="104"/>
-      <c r="F42" s="105" t="s">
-        <v>350</v>
-      </c>
-      <c r="G42" s="104"/>
-      <c r="H42" s="105" t="s">
-        <v>350</v>
-      </c>
-      <c r="I42" s="104"/>
-      <c r="J42" s="105" t="s">
-        <v>350</v>
-      </c>
-      <c r="K42" s="104"/>
+      <c r="E42" s="96"/>
+      <c r="F42" s="97" t="s">
+        <v>350</v>
+      </c>
+      <c r="G42" s="96"/>
+      <c r="H42" s="97" t="s">
+        <v>350</v>
+      </c>
+      <c r="I42" s="96"/>
+      <c r="J42" s="97" t="s">
+        <v>350</v>
+      </c>
+      <c r="K42" s="96"/>
     </row>
     <row r="43" spans="1:11" s="3" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A43" s="73">
+      <c r="A43" s="72">
         <v>39</v>
       </c>
-      <c r="B43" s="94" t="s">
+      <c r="B43" s="89" t="s">
         <v>257</v>
       </c>
-      <c r="C43" s="92" t="s">
+      <c r="C43" s="87" t="s">
         <v>385</v>
       </c>
-      <c r="E43" s="104"/>
-      <c r="F43" s="104"/>
-      <c r="G43" s="105" t="s">
-        <v>350</v>
-      </c>
-      <c r="H43" s="104"/>
-      <c r="I43" s="105" t="s">
-        <v>350</v>
-      </c>
-      <c r="J43" s="104"/>
-      <c r="K43" s="105" t="s">
+      <c r="E43" s="96"/>
+      <c r="F43" s="96"/>
+      <c r="G43" s="97" t="s">
+        <v>350</v>
+      </c>
+      <c r="H43" s="96"/>
+      <c r="I43" s="97" t="s">
+        <v>350</v>
+      </c>
+      <c r="J43" s="96"/>
+      <c r="K43" s="97" t="s">
         <v>350</v>
       </c>
     </row>
     <row r="44" spans="1:11" s="3" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A44" s="73">
+      <c r="A44" s="72">
         <v>40</v>
       </c>
-      <c r="B44" s="94" t="s">
+      <c r="B44" s="89" t="s">
         <v>258</v>
       </c>
-      <c r="C44" s="92" t="s">
+      <c r="C44" s="87" t="s">
         <v>326</v>
       </c>
-      <c r="E44" s="104"/>
-      <c r="F44" s="104"/>
-      <c r="G44" s="104"/>
-      <c r="H44" s="105" t="s">
-        <v>350</v>
-      </c>
-      <c r="I44" s="105" t="s">
-        <v>350</v>
-      </c>
-      <c r="J44" s="105" t="s">
-        <v>350</v>
-      </c>
-      <c r="K44" s="105" t="s">
+      <c r="E44" s="96"/>
+      <c r="F44" s="96"/>
+      <c r="G44" s="96"/>
+      <c r="H44" s="97" t="s">
+        <v>350</v>
+      </c>
+      <c r="I44" s="97" t="s">
+        <v>350</v>
+      </c>
+      <c r="J44" s="97" t="s">
+        <v>350</v>
+      </c>
+      <c r="K44" s="97" t="s">
         <v>350</v>
       </c>
     </row>
     <row r="45" spans="1:11" s="3" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A45" s="73">
+      <c r="A45" s="72">
         <v>41</v>
       </c>
-      <c r="B45" s="94" t="s">
+      <c r="B45" s="89" t="s">
         <v>327</v>
       </c>
-      <c r="C45" s="92" t="s">
+      <c r="C45" s="87" t="s">
         <v>328</v>
       </c>
-      <c r="E45" s="105" t="s">
-        <v>350</v>
-      </c>
-      <c r="F45" s="104"/>
-      <c r="G45" s="105" t="s">
-        <v>350</v>
-      </c>
-      <c r="H45" s="104"/>
-      <c r="I45" s="105" t="s">
-        <v>350</v>
-      </c>
-      <c r="J45" s="104"/>
-      <c r="K45" s="105" t="s">
+      <c r="E45" s="97" t="s">
+        <v>350</v>
+      </c>
+      <c r="F45" s="96"/>
+      <c r="G45" s="97" t="s">
+        <v>350</v>
+      </c>
+      <c r="H45" s="96"/>
+      <c r="I45" s="97" t="s">
+        <v>350</v>
+      </c>
+      <c r="J45" s="96"/>
+      <c r="K45" s="97" t="s">
         <v>350</v>
       </c>
     </row>
     <row r="46" spans="1:11" s="3" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A46" s="73">
+      <c r="A46" s="72">
         <v>42</v>
       </c>
-      <c r="B46" s="94" t="s">
+      <c r="B46" s="89" t="s">
         <v>329</v>
       </c>
-      <c r="C46" s="92" t="s">
+      <c r="C46" s="87" t="s">
         <v>330</v>
       </c>
-      <c r="E46" s="104"/>
-      <c r="F46" s="105" t="s">
-        <v>350</v>
-      </c>
-      <c r="G46" s="105" t="s">
-        <v>350</v>
-      </c>
-      <c r="H46" s="105" t="s">
-        <v>350</v>
-      </c>
-      <c r="I46" s="105" t="s">
-        <v>350</v>
-      </c>
-      <c r="J46" s="105" t="s">
-        <v>350</v>
-      </c>
-      <c r="K46" s="105" t="s">
+      <c r="E46" s="96"/>
+      <c r="F46" s="97" t="s">
+        <v>350</v>
+      </c>
+      <c r="G46" s="97" t="s">
+        <v>350</v>
+      </c>
+      <c r="H46" s="97" t="s">
+        <v>350</v>
+      </c>
+      <c r="I46" s="97" t="s">
+        <v>350</v>
+      </c>
+      <c r="J46" s="97" t="s">
+        <v>350</v>
+      </c>
+      <c r="K46" s="97" t="s">
         <v>350</v>
       </c>
     </row>
     <row r="47" spans="1:11" s="3" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A47" s="73">
+      <c r="A47" s="72">
         <v>43</v>
       </c>
-      <c r="B47" s="94" t="s">
+      <c r="B47" s="89" t="s">
         <v>331</v>
       </c>
-      <c r="C47" s="92" t="s">
+      <c r="C47" s="87" t="s">
         <v>332</v>
       </c>
-      <c r="E47" s="104"/>
-      <c r="F47" s="105" t="s">
-        <v>350</v>
-      </c>
-      <c r="G47" s="105" t="s">
-        <v>350</v>
-      </c>
-      <c r="H47" s="105" t="s">
-        <v>350</v>
-      </c>
-      <c r="I47" s="105" t="s">
-        <v>350</v>
-      </c>
-      <c r="J47" s="105" t="s">
-        <v>350</v>
-      </c>
-      <c r="K47" s="105" t="s">
+      <c r="E47" s="96"/>
+      <c r="F47" s="97" t="s">
+        <v>350</v>
+      </c>
+      <c r="G47" s="97" t="s">
+        <v>350</v>
+      </c>
+      <c r="H47" s="97" t="s">
+        <v>350</v>
+      </c>
+      <c r="I47" s="97" t="s">
+        <v>350</v>
+      </c>
+      <c r="J47" s="97" t="s">
+        <v>350</v>
+      </c>
+      <c r="K47" s="97" t="s">
         <v>350</v>
       </c>
     </row>
     <row r="48" spans="1:11" s="3" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A48" s="73">
+      <c r="A48" s="72">
         <v>44</v>
       </c>
-      <c r="B48" s="94" t="s">
+      <c r="B48" s="89" t="s">
         <v>333</v>
       </c>
-      <c r="C48" s="92" t="s">
+      <c r="C48" s="87" t="s">
         <v>334</v>
       </c>
-      <c r="E48" s="104"/>
-      <c r="F48" s="105" t="s">
-        <v>350</v>
-      </c>
-      <c r="G48" s="105" t="s">
-        <v>350</v>
-      </c>
-      <c r="H48" s="105" t="s">
-        <v>350</v>
-      </c>
-      <c r="I48" s="105" t="s">
-        <v>350</v>
-      </c>
-      <c r="J48" s="105" t="s">
-        <v>350</v>
-      </c>
-      <c r="K48" s="105" t="s">
+      <c r="E48" s="96"/>
+      <c r="F48" s="97" t="s">
+        <v>350</v>
+      </c>
+      <c r="G48" s="97" t="s">
+        <v>350</v>
+      </c>
+      <c r="H48" s="97" t="s">
+        <v>350</v>
+      </c>
+      <c r="I48" s="97" t="s">
+        <v>350</v>
+      </c>
+      <c r="J48" s="97" t="s">
+        <v>350</v>
+      </c>
+      <c r="K48" s="97" t="s">
         <v>350</v>
       </c>
     </row>
     <row r="49" spans="1:11" s="3" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A49" s="73">
+      <c r="A49" s="72">
         <v>45</v>
       </c>
-      <c r="B49" s="94" t="s">
+      <c r="B49" s="89" t="s">
         <v>335</v>
       </c>
-      <c r="C49" s="92" t="s">
+      <c r="C49" s="87" t="s">
         <v>336</v>
       </c>
-      <c r="E49" s="104"/>
-      <c r="F49" s="105" t="s">
-        <v>350</v>
-      </c>
-      <c r="G49" s="105" t="s">
-        <v>350</v>
-      </c>
-      <c r="H49" s="105" t="s">
-        <v>350</v>
-      </c>
-      <c r="I49" s="105" t="s">
-        <v>350</v>
-      </c>
-      <c r="J49" s="105" t="s">
-        <v>350</v>
-      </c>
-      <c r="K49" s="105" t="s">
+      <c r="E49" s="96"/>
+      <c r="F49" s="97" t="s">
+        <v>350</v>
+      </c>
+      <c r="G49" s="97" t="s">
+        <v>350</v>
+      </c>
+      <c r="H49" s="97" t="s">
+        <v>350</v>
+      </c>
+      <c r="I49" s="97" t="s">
+        <v>350</v>
+      </c>
+      <c r="J49" s="97" t="s">
+        <v>350</v>
+      </c>
+      <c r="K49" s="97" t="s">
         <v>350</v>
       </c>
     </row>
     <row r="51" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="E51" s="111">
+      <c r="E51" s="103">
         <f>COUNTA(E4:E49)</f>
         <v>33</v>
       </c>
-      <c r="F51" s="111">
+      <c r="F51" s="103">
         <f t="shared" ref="F51:K51" si="0">COUNTA(F4:F49)</f>
         <v>38</v>
       </c>
-      <c r="G51" s="111">
+      <c r="G51" s="103">
         <f t="shared" si="0"/>
         <v>41</v>
       </c>
-      <c r="H51" s="111">
+      <c r="H51" s="103">
         <f t="shared" si="0"/>
         <v>36</v>
       </c>
-      <c r="I51" s="111">
+      <c r="I51" s="103">
         <f t="shared" si="0"/>
         <v>38</v>
       </c>
-      <c r="J51" s="111">
+      <c r="J51" s="103">
         <f t="shared" si="0"/>
         <v>33</v>
       </c>
-      <c r="K51" s="111">
+      <c r="K51" s="103">
         <f t="shared" si="0"/>
         <v>35</v>
       </c>
@@ -9331,7 +9273,7 @@
       <c r="E4" s="48" t="s">
         <v>131</v>
       </c>
-      <c r="F4" s="87" t="s">
+      <c r="F4" s="48" t="s">
         <v>423</v>
       </c>
     </row>
@@ -9363,7 +9305,7 @@
       <c r="C6" s="60"/>
       <c r="D6" s="25"/>
       <c r="E6" s="25"/>
-      <c r="F6" s="116"/>
+      <c r="F6" s="108"/>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A7" s="31">
@@ -9373,7 +9315,7 @@
       <c r="C7" s="60"/>
       <c r="D7" s="25"/>
       <c r="E7" s="25"/>
-      <c r="F7" s="116"/>
+      <c r="F7" s="108"/>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A8" s="31">
@@ -9383,7 +9325,7 @@
       <c r="C8" s="60"/>
       <c r="D8" s="25"/>
       <c r="E8" s="25"/>
-      <c r="F8" s="116"/>
+      <c r="F8" s="108"/>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A9" s="31">
@@ -9393,7 +9335,7 @@
       <c r="C9" s="60"/>
       <c r="D9" s="25"/>
       <c r="E9" s="25"/>
-      <c r="F9" s="116"/>
+      <c r="F9" s="108"/>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A10" s="31">
@@ -9403,7 +9345,7 @@
       <c r="C10" s="60"/>
       <c r="D10" s="25"/>
       <c r="E10" s="25"/>
-      <c r="F10" s="116"/>
+      <c r="F10" s="108"/>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A11" s="31" t="s">
@@ -9413,7 +9355,7 @@
       <c r="C11" s="60"/>
       <c r="D11" s="25"/>
       <c r="E11" s="25"/>
-      <c r="F11" s="116"/>
+      <c r="F11" s="108"/>
     </row>
   </sheetData>
   <hyperlinks>
@@ -9485,11 +9427,11 @@
       <c r="A6" s="58" t="s">
         <v>58</v>
       </c>
-      <c r="B6" s="153" t="s">
+      <c r="B6" s="144" t="s">
         <v>119</v>
       </c>
-      <c r="C6" s="154"/>
-      <c r="D6" s="155"/>
+      <c r="C6" s="145"/>
+      <c r="D6" s="146"/>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A7" s="59">
@@ -9611,11 +9553,11 @@
       <c r="A6" s="58" t="s">
         <v>120</v>
       </c>
-      <c r="B6" s="153" t="s">
+      <c r="B6" s="144" t="s">
         <v>121</v>
       </c>
-      <c r="C6" s="154"/>
-      <c r="D6" s="155"/>
+      <c r="C6" s="145"/>
+      <c r="D6" s="146"/>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A7" s="59">
@@ -9746,11 +9688,11 @@
       <c r="A6" s="58" t="s">
         <v>122</v>
       </c>
-      <c r="B6" s="153" t="s">
+      <c r="B6" s="144" t="s">
         <v>123</v>
       </c>
-      <c r="C6" s="154"/>
-      <c r="D6" s="155"/>
+      <c r="C6" s="145"/>
+      <c r="D6" s="146"/>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A7" s="59">
@@ -9881,11 +9823,11 @@
       <c r="A6" s="58" t="s">
         <v>124</v>
       </c>
-      <c r="B6" s="153" t="s">
+      <c r="B6" s="144" t="s">
         <v>125</v>
       </c>
-      <c r="C6" s="154"/>
-      <c r="D6" s="155"/>
+      <c r="C6" s="145"/>
+      <c r="D6" s="146"/>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A7" s="59">
@@ -9973,47 +9915,47 @@
       <c r="A2" s="38"/>
     </row>
     <row r="3" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="157" t="s">
+      <c r="A3" s="148" t="s">
         <v>17</v>
       </c>
-      <c r="B3" s="157" t="s">
+      <c r="B3" s="148" t="s">
         <v>133</v>
       </c>
-      <c r="C3" s="130" t="s">
+      <c r="C3" s="121" t="s">
         <v>134</v>
       </c>
-      <c r="D3" s="131"/>
-      <c r="E3" s="131"/>
-      <c r="F3" s="132"/>
-      <c r="G3" s="130" t="s">
+      <c r="D3" s="122"/>
+      <c r="E3" s="122"/>
+      <c r="F3" s="123"/>
+      <c r="G3" s="121" t="s">
         <v>135</v>
       </c>
-      <c r="H3" s="131"/>
-      <c r="I3" s="131"/>
-      <c r="J3" s="132"/>
+      <c r="H3" s="122"/>
+      <c r="I3" s="122"/>
+      <c r="J3" s="123"/>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A4" s="157"/>
-      <c r="B4" s="157"/>
-      <c r="C4" s="64" t="s">
+      <c r="A4" s="148"/>
+      <c r="B4" s="148"/>
+      <c r="C4" s="27" t="s">
         <v>40</v>
       </c>
-      <c r="D4" s="64" t="s">
+      <c r="D4" s="27" t="s">
         <v>41</v>
       </c>
-      <c r="E4" s="64" t="s">
+      <c r="E4" s="27" t="s">
         <v>12</v>
       </c>
       <c r="F4" s="37" t="s">
         <v>136</v>
       </c>
-      <c r="G4" s="64" t="s">
+      <c r="G4" s="27" t="s">
         <v>40</v>
       </c>
-      <c r="H4" s="64" t="s">
+      <c r="H4" s="27" t="s">
         <v>41</v>
       </c>
-      <c r="I4" s="64" t="s">
+      <c r="I4" s="27" t="s">
         <v>12</v>
       </c>
       <c r="J4" s="37" t="s">
@@ -10059,31 +10001,31 @@
       <c r="B6" s="49" t="s">
         <v>137</v>
       </c>
-      <c r="C6" s="85"/>
-      <c r="D6" s="85"/>
-      <c r="E6" s="85"/>
-      <c r="F6" s="86"/>
-      <c r="G6" s="85"/>
-      <c r="H6" s="85"/>
-      <c r="I6" s="85"/>
-      <c r="J6" s="86"/>
+      <c r="C6" s="81"/>
+      <c r="D6" s="81"/>
+      <c r="E6" s="81"/>
+      <c r="F6" s="82"/>
+      <c r="G6" s="81"/>
+      <c r="H6" s="81"/>
+      <c r="I6" s="81"/>
+      <c r="J6" s="82"/>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A7" s="31"/>
       <c r="B7" s="49" t="s">
         <v>363</v>
       </c>
-      <c r="C7" s="65"/>
-      <c r="D7" s="65"/>
-      <c r="E7" s="65"/>
-      <c r="F7" s="66" t="e">
+      <c r="C7" s="64"/>
+      <c r="D7" s="64"/>
+      <c r="E7" s="64"/>
+      <c r="F7" s="65" t="e">
         <f>AVERAGE(C7:E7)</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="G7" s="65"/>
-      <c r="H7" s="65"/>
-      <c r="I7" s="65"/>
-      <c r="J7" s="66" t="e">
+      <c r="G7" s="64"/>
+      <c r="H7" s="64"/>
+      <c r="I7" s="64"/>
+      <c r="J7" s="65" t="e">
         <f>AVERAGE(G7:I7)</f>
         <v>#DIV/0!</v>
       </c>
@@ -10093,17 +10035,17 @@
       <c r="B8" s="49" t="s">
         <v>364</v>
       </c>
-      <c r="C8" s="65"/>
-      <c r="D8" s="65"/>
-      <c r="E8" s="65"/>
-      <c r="F8" s="66" t="e">
+      <c r="C8" s="64"/>
+      <c r="D8" s="64"/>
+      <c r="E8" s="64"/>
+      <c r="F8" s="65" t="e">
         <f t="shared" ref="F8:F19" si="0">AVERAGE(C8:E8)</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="G8" s="65"/>
-      <c r="H8" s="65"/>
-      <c r="I8" s="65"/>
-      <c r="J8" s="66" t="e">
+      <c r="G8" s="64"/>
+      <c r="H8" s="64"/>
+      <c r="I8" s="64"/>
+      <c r="J8" s="65" t="e">
         <f t="shared" ref="J8:J19" si="1">AVERAGE(G8:I8)</f>
         <v>#DIV/0!</v>
       </c>
@@ -10113,17 +10055,17 @@
       <c r="B9" s="49" t="s">
         <v>365</v>
       </c>
-      <c r="C9" s="65"/>
-      <c r="D9" s="65"/>
-      <c r="E9" s="65"/>
-      <c r="F9" s="66" t="e">
+      <c r="C9" s="64"/>
+      <c r="D9" s="64"/>
+      <c r="E9" s="64"/>
+      <c r="F9" s="65" t="e">
         <f t="shared" si="0"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="G9" s="65"/>
-      <c r="H9" s="65"/>
-      <c r="I9" s="65"/>
-      <c r="J9" s="66" t="e">
+      <c r="G9" s="64"/>
+      <c r="H9" s="64"/>
+      <c r="I9" s="64"/>
+      <c r="J9" s="65" t="e">
         <f t="shared" si="1"/>
         <v>#DIV/0!</v>
       </c>
@@ -10133,17 +10075,17 @@
       <c r="B10" s="49" t="s">
         <v>366</v>
       </c>
-      <c r="C10" s="65"/>
-      <c r="D10" s="65"/>
-      <c r="E10" s="65"/>
-      <c r="F10" s="66" t="e">
+      <c r="C10" s="64"/>
+      <c r="D10" s="64"/>
+      <c r="E10" s="64"/>
+      <c r="F10" s="65" t="e">
         <f t="shared" si="0"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="G10" s="65"/>
-      <c r="H10" s="65"/>
-      <c r="I10" s="65"/>
-      <c r="J10" s="66" t="e">
+      <c r="G10" s="64"/>
+      <c r="H10" s="64"/>
+      <c r="I10" s="64"/>
+      <c r="J10" s="65" t="e">
         <f t="shared" si="1"/>
         <v>#DIV/0!</v>
       </c>
@@ -10155,55 +10097,55 @@
       <c r="B11" s="49" t="s">
         <v>138</v>
       </c>
-      <c r="C11" s="65"/>
-      <c r="D11" s="65"/>
-      <c r="E11" s="65"/>
-      <c r="F11" s="66" t="e">
+      <c r="C11" s="64"/>
+      <c r="D11" s="64"/>
+      <c r="E11" s="64"/>
+      <c r="F11" s="65" t="e">
         <f t="shared" si="0"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="G11" s="65"/>
-      <c r="H11" s="65"/>
-      <c r="I11" s="65"/>
-      <c r="J11" s="66" t="e">
+      <c r="G11" s="64"/>
+      <c r="H11" s="64"/>
+      <c r="I11" s="64"/>
+      <c r="J11" s="65" t="e">
         <f t="shared" si="1"/>
         <v>#DIV/0!</v>
       </c>
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A12" s="156" t="s">
+      <c r="A12" s="147" t="s">
         <v>42</v>
       </c>
-      <c r="B12" s="156"/>
-      <c r="C12" s="107">
+      <c r="B12" s="147"/>
+      <c r="C12" s="99">
         <f>SUM(C6:C11)</f>
         <v>0</v>
       </c>
-      <c r="D12" s="107">
+      <c r="D12" s="99">
         <f>SUM(D6:D11)</f>
         <v>0</v>
       </c>
-      <c r="E12" s="107">
+      <c r="E12" s="99">
         <f>SUM(E6:E11)</f>
         <v>0</v>
       </c>
-      <c r="F12" s="107">
+      <c r="F12" s="99">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="G12" s="107">
+      <c r="G12" s="99">
         <f>SUM(G6:G11)</f>
         <v>0</v>
       </c>
-      <c r="H12" s="107">
+      <c r="H12" s="99">
         <f>SUM(H6:H11)</f>
         <v>0</v>
       </c>
-      <c r="I12" s="107">
+      <c r="I12" s="99">
         <f>SUM(I6:I11)</f>
         <v>0</v>
       </c>
-      <c r="J12" s="107">
+      <c r="J12" s="99">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -10215,17 +10157,17 @@
       <c r="B13" s="49" t="s">
         <v>139</v>
       </c>
-      <c r="C13" s="65"/>
-      <c r="D13" s="65"/>
-      <c r="E13" s="65"/>
-      <c r="F13" s="66" t="e">
+      <c r="C13" s="64"/>
+      <c r="D13" s="64"/>
+      <c r="E13" s="64"/>
+      <c r="F13" s="65" t="e">
         <f t="shared" si="0"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="G13" s="65"/>
-      <c r="H13" s="65"/>
-      <c r="I13" s="65"/>
-      <c r="J13" s="66" t="e">
+      <c r="G13" s="64"/>
+      <c r="H13" s="64"/>
+      <c r="I13" s="64"/>
+      <c r="J13" s="65" t="e">
         <f t="shared" si="1"/>
         <v>#DIV/0!</v>
       </c>
@@ -10237,55 +10179,55 @@
       <c r="B14" s="49" t="s">
         <v>140</v>
       </c>
-      <c r="C14" s="65"/>
-      <c r="D14" s="65"/>
-      <c r="E14" s="65"/>
-      <c r="F14" s="66" t="e">
+      <c r="C14" s="64"/>
+      <c r="D14" s="64"/>
+      <c r="E14" s="64"/>
+      <c r="F14" s="65" t="e">
         <f t="shared" si="0"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="G14" s="65"/>
-      <c r="H14" s="65"/>
-      <c r="I14" s="65"/>
-      <c r="J14" s="66" t="e">
+      <c r="G14" s="64"/>
+      <c r="H14" s="64"/>
+      <c r="I14" s="64"/>
+      <c r="J14" s="65" t="e">
         <f t="shared" si="1"/>
         <v>#DIV/0!</v>
       </c>
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A15" s="156" t="s">
+      <c r="A15" s="147" t="s">
         <v>42</v>
       </c>
-      <c r="B15" s="156"/>
-      <c r="C15" s="107">
+      <c r="B15" s="147"/>
+      <c r="C15" s="99">
         <f>SUM(C13:C14)</f>
         <v>0</v>
       </c>
-      <c r="D15" s="107">
+      <c r="D15" s="99">
         <f>SUM(D13:D14)</f>
         <v>0</v>
       </c>
-      <c r="E15" s="107">
+      <c r="E15" s="99">
         <f>SUM(E13:E14)</f>
         <v>0</v>
       </c>
-      <c r="F15" s="107">
+      <c r="F15" s="99">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="G15" s="107">
+      <c r="G15" s="99">
         <f>SUM(G13:G14)</f>
         <v>0</v>
       </c>
-      <c r="H15" s="107">
+      <c r="H15" s="99">
         <f>SUM(H13:H14)</f>
         <v>0</v>
       </c>
-      <c r="I15" s="107">
+      <c r="I15" s="99">
         <f>SUM(I13:I14)</f>
         <v>0</v>
       </c>
-      <c r="J15" s="107">
+      <c r="J15" s="99">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -10297,17 +10239,17 @@
       <c r="B16" s="49" t="s">
         <v>141</v>
       </c>
-      <c r="C16" s="65"/>
-      <c r="D16" s="65"/>
-      <c r="E16" s="65"/>
-      <c r="F16" s="66" t="e">
+      <c r="C16" s="64"/>
+      <c r="D16" s="64"/>
+      <c r="E16" s="64"/>
+      <c r="F16" s="65" t="e">
         <f t="shared" si="0"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="G16" s="65"/>
-      <c r="H16" s="65"/>
-      <c r="I16" s="65"/>
-      <c r="J16" s="66" t="e">
+      <c r="G16" s="64"/>
+      <c r="H16" s="64"/>
+      <c r="I16" s="64"/>
+      <c r="J16" s="65" t="e">
         <f t="shared" si="1"/>
         <v>#DIV/0!</v>
       </c>
@@ -10319,17 +10261,17 @@
       <c r="B17" s="49" t="s">
         <v>142</v>
       </c>
-      <c r="C17" s="65"/>
-      <c r="D17" s="65"/>
-      <c r="E17" s="65"/>
-      <c r="F17" s="66" t="e">
+      <c r="C17" s="64"/>
+      <c r="D17" s="64"/>
+      <c r="E17" s="64"/>
+      <c r="F17" s="65" t="e">
         <f t="shared" si="0"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="G17" s="65"/>
-      <c r="H17" s="65"/>
-      <c r="I17" s="65"/>
-      <c r="J17" s="66" t="e">
+      <c r="G17" s="64"/>
+      <c r="H17" s="64"/>
+      <c r="I17" s="64"/>
+      <c r="J17" s="65" t="e">
         <f t="shared" si="1"/>
         <v>#DIV/0!</v>
       </c>
@@ -10341,55 +10283,55 @@
       <c r="B18" s="49" t="s">
         <v>143</v>
       </c>
-      <c r="C18" s="65"/>
-      <c r="D18" s="65"/>
-      <c r="E18" s="65"/>
-      <c r="F18" s="66" t="e">
+      <c r="C18" s="64"/>
+      <c r="D18" s="64"/>
+      <c r="E18" s="64"/>
+      <c r="F18" s="65" t="e">
         <f t="shared" si="0"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="G18" s="65"/>
-      <c r="H18" s="65"/>
-      <c r="I18" s="65"/>
-      <c r="J18" s="66" t="e">
+      <c r="G18" s="64"/>
+      <c r="H18" s="64"/>
+      <c r="I18" s="64"/>
+      <c r="J18" s="65" t="e">
         <f t="shared" si="1"/>
         <v>#DIV/0!</v>
       </c>
     </row>
     <row r="19" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A19" s="156" t="s">
+      <c r="A19" s="147" t="s">
         <v>42</v>
       </c>
-      <c r="B19" s="156"/>
-      <c r="C19" s="107">
+      <c r="B19" s="147"/>
+      <c r="C19" s="99">
         <f>SUM(C16:C18)</f>
         <v>0</v>
       </c>
-      <c r="D19" s="107">
+      <c r="D19" s="99">
         <f>SUM(D16:D18)</f>
         <v>0</v>
       </c>
-      <c r="E19" s="107">
+      <c r="E19" s="99">
         <f>SUM(E16:E18)</f>
         <v>0</v>
       </c>
-      <c r="F19" s="107">
+      <c r="F19" s="99">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="G19" s="107">
+      <c r="G19" s="99">
         <f>SUM(G16:G18)</f>
         <v>0</v>
       </c>
-      <c r="H19" s="107">
+      <c r="H19" s="99">
         <f>SUM(H16:H18)</f>
         <v>0</v>
       </c>
-      <c r="I19" s="107">
+      <c r="I19" s="99">
         <f>SUM(I16:I18)</f>
         <v>0</v>
       </c>
-      <c r="J19" s="107">
+      <c r="J19" s="99">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -10500,48 +10442,48 @@
       <c r="P5" s="20"/>
     </row>
     <row r="7" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="128" t="s">
+      <c r="A7" s="119" t="s">
         <v>17</v>
       </c>
-      <c r="B7" s="128" t="s">
+      <c r="B7" s="119" t="s">
         <v>145</v>
       </c>
-      <c r="C7" s="128" t="s">
+      <c r="C7" s="119" t="s">
         <v>146</v>
       </c>
-      <c r="D7" s="128" t="s">
+      <c r="D7" s="119" t="s">
         <v>147</v>
       </c>
-      <c r="E7" s="128" t="s">
+      <c r="E7" s="119" t="s">
         <v>148</v>
       </c>
-      <c r="F7" s="158" t="s">
+      <c r="F7" s="149" t="s">
         <v>367</v>
       </c>
-      <c r="G7" s="159"/>
-      <c r="H7" s="160"/>
-      <c r="I7" s="128" t="s">
+      <c r="G7" s="150"/>
+      <c r="H7" s="151"/>
+      <c r="I7" s="119" t="s">
         <v>149</v>
       </c>
-      <c r="J7" s="158" t="s">
+      <c r="J7" s="149" t="s">
         <v>150</v>
       </c>
-      <c r="K7" s="159"/>
-      <c r="L7" s="159"/>
-      <c r="M7" s="160"/>
-      <c r="N7" s="128" t="s">
+      <c r="K7" s="150"/>
+      <c r="L7" s="150"/>
+      <c r="M7" s="151"/>
+      <c r="N7" s="119" t="s">
         <v>151</v>
       </c>
-      <c r="O7" s="128" t="s">
+      <c r="O7" s="119" t="s">
         <v>152</v>
       </c>
     </row>
     <row r="8" spans="1:16" ht="55.2" x14ac:dyDescent="0.3">
-      <c r="A8" s="129"/>
-      <c r="B8" s="129"/>
-      <c r="C8" s="129"/>
-      <c r="D8" s="129"/>
-      <c r="E8" s="129"/>
+      <c r="A8" s="120"/>
+      <c r="B8" s="120"/>
+      <c r="C8" s="120"/>
+      <c r="D8" s="120"/>
+      <c r="E8" s="120"/>
       <c r="F8" s="27" t="s">
         <v>153</v>
       </c>
@@ -10551,7 +10493,7 @@
       <c r="H8" s="27" t="s">
         <v>155</v>
       </c>
-      <c r="I8" s="129"/>
+      <c r="I8" s="120"/>
       <c r="J8" s="27" t="s">
         <v>156</v>
       </c>
@@ -10564,8 +10506,8 @@
       <c r="M8" s="27" t="s">
         <v>159</v>
       </c>
-      <c r="N8" s="129"/>
-      <c r="O8" s="129"/>
+      <c r="N8" s="120"/>
+      <c r="O8" s="120"/>
     </row>
     <row r="9" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A9" s="29">
@@ -10615,346 +10557,346 @@
       </c>
     </row>
     <row r="10" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A10" s="67">
+      <c r="A10" s="66">
         <v>1</v>
       </c>
-      <c r="B10" s="68"/>
-      <c r="C10" s="69"/>
-      <c r="D10" s="70"/>
-      <c r="E10" s="69"/>
-      <c r="F10" s="69"/>
-      <c r="G10" s="69"/>
-      <c r="H10" s="69"/>
-      <c r="I10" s="68"/>
-      <c r="J10" s="68"/>
-      <c r="K10" s="68"/>
-      <c r="L10" s="68"/>
-      <c r="M10" s="68"/>
-      <c r="N10" s="68"/>
-      <c r="O10" s="71"/>
+      <c r="B10" s="67"/>
+      <c r="C10" s="68"/>
+      <c r="D10" s="69"/>
+      <c r="E10" s="68"/>
+      <c r="F10" s="68"/>
+      <c r="G10" s="68"/>
+      <c r="H10" s="68"/>
+      <c r="I10" s="67"/>
+      <c r="J10" s="67"/>
+      <c r="K10" s="67"/>
+      <c r="L10" s="67"/>
+      <c r="M10" s="67"/>
+      <c r="N10" s="67"/>
+      <c r="O10" s="70"/>
     </row>
     <row r="11" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A11" s="67">
+      <c r="A11" s="66">
         <v>2</v>
       </c>
-      <c r="B11" s="68"/>
-      <c r="C11" s="69"/>
-      <c r="D11" s="70"/>
-      <c r="E11" s="69"/>
-      <c r="F11" s="69"/>
-      <c r="G11" s="69"/>
-      <c r="H11" s="69"/>
-      <c r="I11" s="68"/>
-      <c r="J11" s="68"/>
-      <c r="K11" s="68"/>
-      <c r="L11" s="68"/>
-      <c r="M11" s="68"/>
-      <c r="N11" s="68"/>
-      <c r="O11" s="71"/>
+      <c r="B11" s="67"/>
+      <c r="C11" s="68"/>
+      <c r="D11" s="69"/>
+      <c r="E11" s="68"/>
+      <c r="F11" s="68"/>
+      <c r="G11" s="68"/>
+      <c r="H11" s="68"/>
+      <c r="I11" s="67"/>
+      <c r="J11" s="67"/>
+      <c r="K11" s="67"/>
+      <c r="L11" s="67"/>
+      <c r="M11" s="67"/>
+      <c r="N11" s="67"/>
+      <c r="O11" s="70"/>
     </row>
     <row r="12" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A12" s="67">
+      <c r="A12" s="66">
         <v>3</v>
       </c>
-      <c r="B12" s="68"/>
-      <c r="C12" s="69"/>
-      <c r="D12" s="70"/>
-      <c r="E12" s="69"/>
-      <c r="F12" s="69"/>
-      <c r="G12" s="69"/>
-      <c r="H12" s="69"/>
-      <c r="I12" s="68"/>
-      <c r="J12" s="69"/>
-      <c r="K12" s="69"/>
-      <c r="L12" s="68"/>
-      <c r="M12" s="68"/>
-      <c r="N12" s="68"/>
-      <c r="O12" s="71"/>
+      <c r="B12" s="67"/>
+      <c r="C12" s="68"/>
+      <c r="D12" s="69"/>
+      <c r="E12" s="68"/>
+      <c r="F12" s="68"/>
+      <c r="G12" s="68"/>
+      <c r="H12" s="68"/>
+      <c r="I12" s="67"/>
+      <c r="J12" s="68"/>
+      <c r="K12" s="68"/>
+      <c r="L12" s="67"/>
+      <c r="M12" s="67"/>
+      <c r="N12" s="67"/>
+      <c r="O12" s="70"/>
     </row>
     <row r="13" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A13" s="67">
+      <c r="A13" s="66">
         <v>4</v>
       </c>
-      <c r="B13" s="68"/>
-      <c r="C13" s="69"/>
-      <c r="D13" s="70"/>
-      <c r="E13" s="69"/>
-      <c r="F13" s="69"/>
-      <c r="G13" s="69"/>
-      <c r="H13" s="69"/>
-      <c r="I13" s="68"/>
-      <c r="J13" s="69"/>
-      <c r="K13" s="69"/>
-      <c r="L13" s="68"/>
-      <c r="M13" s="68"/>
-      <c r="N13" s="68"/>
-      <c r="O13" s="71"/>
+      <c r="B13" s="67"/>
+      <c r="C13" s="68"/>
+      <c r="D13" s="69"/>
+      <c r="E13" s="68"/>
+      <c r="F13" s="68"/>
+      <c r="G13" s="68"/>
+      <c r="H13" s="68"/>
+      <c r="I13" s="67"/>
+      <c r="J13" s="68"/>
+      <c r="K13" s="68"/>
+      <c r="L13" s="67"/>
+      <c r="M13" s="67"/>
+      <c r="N13" s="67"/>
+      <c r="O13" s="70"/>
     </row>
     <row r="14" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A14" s="67">
+      <c r="A14" s="66">
         <v>5</v>
       </c>
-      <c r="B14" s="68"/>
-      <c r="C14" s="69"/>
-      <c r="D14" s="70"/>
-      <c r="E14" s="69"/>
-      <c r="F14" s="69"/>
-      <c r="G14" s="69"/>
-      <c r="H14" s="69"/>
-      <c r="I14" s="68"/>
-      <c r="J14" s="69"/>
-      <c r="K14" s="69"/>
-      <c r="L14" s="68"/>
-      <c r="M14" s="68"/>
-      <c r="N14" s="68"/>
-      <c r="O14" s="71"/>
+      <c r="B14" s="67"/>
+      <c r="C14" s="68"/>
+      <c r="D14" s="69"/>
+      <c r="E14" s="68"/>
+      <c r="F14" s="68"/>
+      <c r="G14" s="68"/>
+      <c r="H14" s="68"/>
+      <c r="I14" s="67"/>
+      <c r="J14" s="68"/>
+      <c r="K14" s="68"/>
+      <c r="L14" s="67"/>
+      <c r="M14" s="67"/>
+      <c r="N14" s="67"/>
+      <c r="O14" s="70"/>
     </row>
     <row r="15" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A15" s="67">
+      <c r="A15" s="66">
         <v>6</v>
       </c>
-      <c r="B15" s="68"/>
-      <c r="C15" s="69"/>
-      <c r="D15" s="70"/>
-      <c r="E15" s="69"/>
-      <c r="F15" s="69"/>
-      <c r="G15" s="69"/>
-      <c r="H15" s="69"/>
-      <c r="I15" s="68"/>
-      <c r="J15" s="69"/>
-      <c r="K15" s="69"/>
-      <c r="L15" s="68"/>
-      <c r="M15" s="68"/>
-      <c r="N15" s="68"/>
-      <c r="O15" s="71"/>
+      <c r="B15" s="67"/>
+      <c r="C15" s="68"/>
+      <c r="D15" s="69"/>
+      <c r="E15" s="68"/>
+      <c r="F15" s="68"/>
+      <c r="G15" s="68"/>
+      <c r="H15" s="68"/>
+      <c r="I15" s="67"/>
+      <c r="J15" s="68"/>
+      <c r="K15" s="68"/>
+      <c r="L15" s="67"/>
+      <c r="M15" s="67"/>
+      <c r="N15" s="67"/>
+      <c r="O15" s="70"/>
     </row>
     <row r="16" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A16" s="67">
+      <c r="A16" s="66">
         <v>7</v>
       </c>
-      <c r="B16" s="68"/>
-      <c r="C16" s="69"/>
-      <c r="D16" s="70"/>
-      <c r="E16" s="69"/>
-      <c r="F16" s="69"/>
-      <c r="G16" s="69"/>
-      <c r="H16" s="69"/>
-      <c r="I16" s="68"/>
-      <c r="J16" s="69"/>
-      <c r="K16" s="69"/>
-      <c r="L16" s="68"/>
-      <c r="M16" s="68"/>
-      <c r="N16" s="68"/>
-      <c r="O16" s="71"/>
+      <c r="B16" s="67"/>
+      <c r="C16" s="68"/>
+      <c r="D16" s="69"/>
+      <c r="E16" s="68"/>
+      <c r="F16" s="68"/>
+      <c r="G16" s="68"/>
+      <c r="H16" s="68"/>
+      <c r="I16" s="67"/>
+      <c r="J16" s="68"/>
+      <c r="K16" s="68"/>
+      <c r="L16" s="67"/>
+      <c r="M16" s="67"/>
+      <c r="N16" s="67"/>
+      <c r="O16" s="70"/>
     </row>
     <row r="17" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A17" s="67">
+      <c r="A17" s="66">
         <v>8</v>
       </c>
-      <c r="B17" s="68"/>
-      <c r="C17" s="69"/>
-      <c r="D17" s="70"/>
-      <c r="E17" s="69"/>
-      <c r="F17" s="69"/>
-      <c r="G17" s="69"/>
-      <c r="H17" s="69"/>
-      <c r="I17" s="68"/>
-      <c r="J17" s="69"/>
-      <c r="K17" s="69"/>
-      <c r="L17" s="68"/>
-      <c r="M17" s="68"/>
-      <c r="N17" s="68"/>
-      <c r="O17" s="71"/>
+      <c r="B17" s="67"/>
+      <c r="C17" s="68"/>
+      <c r="D17" s="69"/>
+      <c r="E17" s="68"/>
+      <c r="F17" s="68"/>
+      <c r="G17" s="68"/>
+      <c r="H17" s="68"/>
+      <c r="I17" s="67"/>
+      <c r="J17" s="68"/>
+      <c r="K17" s="68"/>
+      <c r="L17" s="67"/>
+      <c r="M17" s="67"/>
+      <c r="N17" s="67"/>
+      <c r="O17" s="70"/>
     </row>
     <row r="18" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A18" s="67">
+      <c r="A18" s="66">
         <v>9</v>
       </c>
-      <c r="B18" s="68"/>
-      <c r="C18" s="69"/>
-      <c r="D18" s="70"/>
-      <c r="E18" s="69"/>
-      <c r="F18" s="69"/>
-      <c r="G18" s="69"/>
-      <c r="H18" s="69"/>
-      <c r="I18" s="68"/>
-      <c r="J18" s="69"/>
-      <c r="K18" s="69"/>
-      <c r="L18" s="68"/>
-      <c r="M18" s="68"/>
-      <c r="N18" s="68"/>
-      <c r="O18" s="71"/>
+      <c r="B18" s="67"/>
+      <c r="C18" s="68"/>
+      <c r="D18" s="69"/>
+      <c r="E18" s="68"/>
+      <c r="F18" s="68"/>
+      <c r="G18" s="68"/>
+      <c r="H18" s="68"/>
+      <c r="I18" s="67"/>
+      <c r="J18" s="68"/>
+      <c r="K18" s="68"/>
+      <c r="L18" s="67"/>
+      <c r="M18" s="67"/>
+      <c r="N18" s="67"/>
+      <c r="O18" s="70"/>
     </row>
     <row r="19" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A19" s="67">
+      <c r="A19" s="66">
         <v>10</v>
       </c>
-      <c r="B19" s="68"/>
-      <c r="C19" s="69"/>
-      <c r="D19" s="70"/>
-      <c r="E19" s="69"/>
-      <c r="F19" s="69"/>
-      <c r="G19" s="69"/>
-      <c r="H19" s="69"/>
-      <c r="I19" s="68"/>
-      <c r="J19" s="69"/>
-      <c r="K19" s="69"/>
-      <c r="L19" s="68"/>
-      <c r="M19" s="68"/>
-      <c r="N19" s="68"/>
-      <c r="O19" s="71"/>
+      <c r="B19" s="67"/>
+      <c r="C19" s="68"/>
+      <c r="D19" s="69"/>
+      <c r="E19" s="68"/>
+      <c r="F19" s="68"/>
+      <c r="G19" s="68"/>
+      <c r="H19" s="68"/>
+      <c r="I19" s="67"/>
+      <c r="J19" s="68"/>
+      <c r="K19" s="68"/>
+      <c r="L19" s="67"/>
+      <c r="M19" s="67"/>
+      <c r="N19" s="67"/>
+      <c r="O19" s="70"/>
     </row>
     <row r="20" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A20" s="67">
+      <c r="A20" s="66">
         <v>11</v>
       </c>
-      <c r="B20" s="68"/>
-      <c r="C20" s="69"/>
-      <c r="D20" s="70"/>
-      <c r="E20" s="69"/>
-      <c r="F20" s="69"/>
-      <c r="G20" s="69"/>
-      <c r="H20" s="69"/>
-      <c r="I20" s="68"/>
-      <c r="J20" s="69"/>
-      <c r="K20" s="69"/>
-      <c r="L20" s="68"/>
-      <c r="M20" s="68"/>
-      <c r="N20" s="68"/>
-      <c r="O20" s="71"/>
+      <c r="B20" s="67"/>
+      <c r="C20" s="68"/>
+      <c r="D20" s="69"/>
+      <c r="E20" s="68"/>
+      <c r="F20" s="68"/>
+      <c r="G20" s="68"/>
+      <c r="H20" s="68"/>
+      <c r="I20" s="67"/>
+      <c r="J20" s="68"/>
+      <c r="K20" s="68"/>
+      <c r="L20" s="67"/>
+      <c r="M20" s="67"/>
+      <c r="N20" s="67"/>
+      <c r="O20" s="70"/>
     </row>
     <row r="21" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A21" s="67">
+      <c r="A21" s="66">
         <v>12</v>
       </c>
-      <c r="B21" s="68"/>
-      <c r="C21" s="69"/>
-      <c r="D21" s="70"/>
-      <c r="E21" s="69"/>
-      <c r="F21" s="69"/>
-      <c r="G21" s="69"/>
-      <c r="H21" s="69"/>
-      <c r="I21" s="68"/>
-      <c r="J21" s="69"/>
-      <c r="K21" s="69"/>
-      <c r="L21" s="68"/>
-      <c r="M21" s="68"/>
-      <c r="N21" s="68"/>
-      <c r="O21" s="71"/>
+      <c r="B21" s="67"/>
+      <c r="C21" s="68"/>
+      <c r="D21" s="69"/>
+      <c r="E21" s="68"/>
+      <c r="F21" s="68"/>
+      <c r="G21" s="68"/>
+      <c r="H21" s="68"/>
+      <c r="I21" s="67"/>
+      <c r="J21" s="68"/>
+      <c r="K21" s="68"/>
+      <c r="L21" s="67"/>
+      <c r="M21" s="67"/>
+      <c r="N21" s="67"/>
+      <c r="O21" s="70"/>
     </row>
     <row r="22" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A22" s="67">
+      <c r="A22" s="66">
         <v>13</v>
       </c>
-      <c r="B22" s="68"/>
-      <c r="C22" s="69"/>
-      <c r="D22" s="70"/>
-      <c r="E22" s="69"/>
-      <c r="F22" s="69"/>
-      <c r="G22" s="69"/>
-      <c r="H22" s="69"/>
-      <c r="I22" s="68"/>
-      <c r="J22" s="69"/>
-      <c r="K22" s="69"/>
-      <c r="L22" s="68"/>
-      <c r="M22" s="68"/>
-      <c r="N22" s="68"/>
-      <c r="O22" s="71"/>
+      <c r="B22" s="67"/>
+      <c r="C22" s="68"/>
+      <c r="D22" s="69"/>
+      <c r="E22" s="68"/>
+      <c r="F22" s="68"/>
+      <c r="G22" s="68"/>
+      <c r="H22" s="68"/>
+      <c r="I22" s="67"/>
+      <c r="J22" s="68"/>
+      <c r="K22" s="68"/>
+      <c r="L22" s="67"/>
+      <c r="M22" s="67"/>
+      <c r="N22" s="67"/>
+      <c r="O22" s="70"/>
     </row>
     <row r="23" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A23" s="67">
+      <c r="A23" s="66">
         <v>14</v>
       </c>
-      <c r="B23" s="68"/>
-      <c r="C23" s="69"/>
-      <c r="D23" s="70"/>
-      <c r="E23" s="69"/>
-      <c r="F23" s="69"/>
-      <c r="G23" s="69"/>
-      <c r="H23" s="69"/>
-      <c r="I23" s="68"/>
-      <c r="J23" s="69"/>
-      <c r="K23" s="69"/>
-      <c r="L23" s="68"/>
-      <c r="M23" s="68"/>
-      <c r="N23" s="68"/>
-      <c r="O23" s="71"/>
+      <c r="B23" s="67"/>
+      <c r="C23" s="68"/>
+      <c r="D23" s="69"/>
+      <c r="E23" s="68"/>
+      <c r="F23" s="68"/>
+      <c r="G23" s="68"/>
+      <c r="H23" s="68"/>
+      <c r="I23" s="67"/>
+      <c r="J23" s="68"/>
+      <c r="K23" s="68"/>
+      <c r="L23" s="67"/>
+      <c r="M23" s="67"/>
+      <c r="N23" s="67"/>
+      <c r="O23" s="70"/>
     </row>
     <row r="24" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A24" s="67">
+      <c r="A24" s="66">
         <v>15</v>
       </c>
-      <c r="B24" s="68"/>
-      <c r="C24" s="69"/>
-      <c r="D24" s="70"/>
-      <c r="E24" s="69"/>
-      <c r="F24" s="69"/>
-      <c r="G24" s="69"/>
-      <c r="H24" s="69"/>
-      <c r="I24" s="68"/>
-      <c r="J24" s="69"/>
-      <c r="K24" s="69"/>
-      <c r="L24" s="68"/>
-      <c r="M24" s="68"/>
-      <c r="N24" s="68"/>
-      <c r="O24" s="71"/>
+      <c r="B24" s="67"/>
+      <c r="C24" s="68"/>
+      <c r="D24" s="69"/>
+      <c r="E24" s="68"/>
+      <c r="F24" s="68"/>
+      <c r="G24" s="68"/>
+      <c r="H24" s="68"/>
+      <c r="I24" s="67"/>
+      <c r="J24" s="68"/>
+      <c r="K24" s="68"/>
+      <c r="L24" s="67"/>
+      <c r="M24" s="67"/>
+      <c r="N24" s="67"/>
+      <c r="O24" s="70"/>
     </row>
     <row r="25" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A25" s="67">
+      <c r="A25" s="66">
         <v>16</v>
       </c>
-      <c r="B25" s="68"/>
-      <c r="C25" s="69"/>
-      <c r="D25" s="70"/>
-      <c r="E25" s="69"/>
-      <c r="F25" s="69"/>
-      <c r="G25" s="69"/>
-      <c r="H25" s="69"/>
-      <c r="I25" s="68"/>
-      <c r="J25" s="69"/>
-      <c r="K25" s="69"/>
-      <c r="L25" s="68"/>
-      <c r="M25" s="68"/>
-      <c r="N25" s="68"/>
-      <c r="O25" s="71"/>
+      <c r="B25" s="67"/>
+      <c r="C25" s="68"/>
+      <c r="D25" s="69"/>
+      <c r="E25" s="68"/>
+      <c r="F25" s="68"/>
+      <c r="G25" s="68"/>
+      <c r="H25" s="68"/>
+      <c r="I25" s="67"/>
+      <c r="J25" s="68"/>
+      <c r="K25" s="68"/>
+      <c r="L25" s="67"/>
+      <c r="M25" s="67"/>
+      <c r="N25" s="67"/>
+      <c r="O25" s="70"/>
     </row>
     <row r="26" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A26" s="67">
+      <c r="A26" s="66">
         <v>17</v>
       </c>
-      <c r="B26" s="68"/>
-      <c r="C26" s="69"/>
-      <c r="D26" s="70"/>
-      <c r="E26" s="69"/>
-      <c r="F26" s="69"/>
-      <c r="G26" s="69"/>
-      <c r="H26" s="69"/>
-      <c r="I26" s="68"/>
-      <c r="J26" s="69"/>
-      <c r="K26" s="69"/>
-      <c r="L26" s="68"/>
-      <c r="M26" s="68"/>
-      <c r="N26" s="68"/>
-      <c r="O26" s="71"/>
+      <c r="B26" s="67"/>
+      <c r="C26" s="68"/>
+      <c r="D26" s="69"/>
+      <c r="E26" s="68"/>
+      <c r="F26" s="68"/>
+      <c r="G26" s="68"/>
+      <c r="H26" s="68"/>
+      <c r="I26" s="67"/>
+      <c r="J26" s="68"/>
+      <c r="K26" s="68"/>
+      <c r="L26" s="67"/>
+      <c r="M26" s="67"/>
+      <c r="N26" s="67"/>
+      <c r="O26" s="70"/>
     </row>
     <row r="27" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A27" s="67" t="s">
+      <c r="A27" s="66" t="s">
         <v>89</v>
       </c>
-      <c r="B27" s="68"/>
-      <c r="C27" s="69"/>
-      <c r="D27" s="70"/>
-      <c r="E27" s="69"/>
-      <c r="F27" s="69"/>
-      <c r="G27" s="69"/>
-      <c r="H27" s="69"/>
-      <c r="I27" s="68"/>
-      <c r="J27" s="69"/>
-      <c r="K27" s="69"/>
-      <c r="L27" s="68"/>
-      <c r="M27" s="68"/>
-      <c r="N27" s="68"/>
-      <c r="O27" s="71"/>
+      <c r="B27" s="67"/>
+      <c r="C27" s="68"/>
+      <c r="D27" s="69"/>
+      <c r="E27" s="68"/>
+      <c r="F27" s="68"/>
+      <c r="G27" s="68"/>
+      <c r="H27" s="68"/>
+      <c r="I27" s="67"/>
+      <c r="J27" s="68"/>
+      <c r="K27" s="68"/>
+      <c r="L27" s="67"/>
+      <c r="M27" s="67"/>
+      <c r="N27" s="67"/>
+      <c r="O27" s="70"/>
     </row>
   </sheetData>
   <mergeCells count="10">
@@ -11013,10 +10955,10 @@
       <c r="A3" s="48" t="s">
         <v>17</v>
       </c>
-      <c r="B3" s="72" t="s">
+      <c r="B3" s="71" t="s">
         <v>160</v>
       </c>
-      <c r="C3" s="72" t="s">
+      <c r="C3" s="71" t="s">
         <v>46</v>
       </c>
       <c r="D3" s="48" t="s">
@@ -11057,7 +10999,7 @@
       <c r="C5" s="35"/>
       <c r="D5" s="25"/>
       <c r="E5" s="25"/>
-      <c r="F5" s="116"/>
+      <c r="F5" s="108"/>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A6" s="31">
@@ -11067,7 +11009,7 @@
       <c r="C6" s="35"/>
       <c r="D6" s="25"/>
       <c r="E6" s="25"/>
-      <c r="F6" s="116"/>
+      <c r="F6" s="108"/>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A7" s="31">
@@ -11077,7 +11019,7 @@
       <c r="C7" s="35"/>
       <c r="D7" s="25"/>
       <c r="E7" s="25"/>
-      <c r="F7" s="116"/>
+      <c r="F7" s="108"/>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A8" s="31">
@@ -11087,7 +11029,7 @@
       <c r="C8" s="35"/>
       <c r="D8" s="25"/>
       <c r="E8" s="25"/>
-      <c r="F8" s="116"/>
+      <c r="F8" s="108"/>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A9" s="31">
@@ -11097,7 +11039,7 @@
       <c r="C9" s="35"/>
       <c r="D9" s="25"/>
       <c r="E9" s="25"/>
-      <c r="F9" s="116"/>
+      <c r="F9" s="108"/>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A10" s="31">
@@ -11107,7 +11049,7 @@
       <c r="C10" s="35"/>
       <c r="D10" s="25"/>
       <c r="E10" s="25"/>
-      <c r="F10" s="116"/>
+      <c r="F10" s="108"/>
     </row>
   </sheetData>
   <hyperlinks>
@@ -11142,26 +11084,26 @@
       <c r="A2" s="38"/>
     </row>
     <row r="3" spans="1:8" ht="33.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="149" t="s">
+      <c r="A3" s="140" t="s">
         <v>17</v>
       </c>
-      <c r="B3" s="149" t="s">
+      <c r="B3" s="140" t="s">
         <v>165</v>
       </c>
-      <c r="C3" s="161" t="s">
+      <c r="C3" s="152" t="s">
         <v>166</v>
       </c>
-      <c r="D3" s="162"/>
-      <c r="E3" s="162"/>
-      <c r="F3" s="163"/>
-      <c r="G3" s="149" t="s">
+      <c r="D3" s="153"/>
+      <c r="E3" s="153"/>
+      <c r="F3" s="154"/>
+      <c r="G3" s="140" t="s">
         <v>167</v>
       </c>
     </row>
     <row r="4" spans="1:8" ht="21.9" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="150"/>
-      <c r="B4" s="150"/>
-      <c r="C4" s="72" t="s">
+      <c r="A4" s="141"/>
+      <c r="B4" s="141"/>
+      <c r="C4" s="71" t="s">
         <v>168</v>
       </c>
       <c r="D4" s="48" t="s">
@@ -11173,7 +11115,7 @@
       <c r="F4" s="48" t="s">
         <v>171</v>
       </c>
-      <c r="G4" s="150"/>
+      <c r="G4" s="141"/>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A5" s="22">
@@ -11264,27 +11206,27 @@
       <c r="G10" s="25"/>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A11" s="164" t="s">
+      <c r="A11" s="155" t="s">
         <v>42</v>
       </c>
-      <c r="B11" s="165"/>
-      <c r="C11" s="73">
+      <c r="B11" s="156"/>
+      <c r="C11" s="72">
         <f>SUM(C6:C10)</f>
         <v>0</v>
       </c>
-      <c r="D11" s="73">
+      <c r="D11" s="72">
         <f t="shared" ref="D11:F11" si="0">SUM(D6:D10)</f>
         <v>0</v>
       </c>
-      <c r="E11" s="73">
+      <c r="E11" s="72">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="F11" s="73">
+      <c r="F11" s="72">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="G11" s="74"/>
+      <c r="G11" s="73"/>
     </row>
   </sheetData>
   <mergeCells count="5">
@@ -11336,7 +11278,7 @@
       <c r="A4" s="48" t="s">
         <v>17</v>
       </c>
-      <c r="B4" s="72" t="s">
+      <c r="B4" s="71" t="s">
         <v>46</v>
       </c>
       <c r="C4" s="48" t="s">
@@ -11663,38 +11605,38 @@
       <c r="G13" s="3"/>
     </row>
     <row r="14" spans="1:8" ht="26.1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="128" t="s">
+      <c r="A14" s="119" t="s">
         <v>116</v>
       </c>
-      <c r="B14" s="128" t="s">
+      <c r="B14" s="119" t="s">
         <v>284</v>
       </c>
-      <c r="C14" s="128" t="s">
+      <c r="C14" s="119" t="s">
         <v>285</v>
       </c>
-      <c r="D14" s="130" t="s">
+      <c r="D14" s="121" t="s">
         <v>286</v>
       </c>
-      <c r="E14" s="131"/>
-      <c r="F14" s="132"/>
-      <c r="G14" s="128" t="s">
+      <c r="E14" s="122"/>
+      <c r="F14" s="123"/>
+      <c r="G14" s="119" t="s">
         <v>287</v>
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A15" s="129"/>
-      <c r="B15" s="129"/>
-      <c r="C15" s="129"/>
-      <c r="D15" s="84" t="s">
+      <c r="A15" s="120"/>
+      <c r="B15" s="120"/>
+      <c r="C15" s="120"/>
+      <c r="D15" s="27" t="s">
         <v>288</v>
       </c>
-      <c r="E15" s="84" t="s">
+      <c r="E15" s="27" t="s">
         <v>289</v>
       </c>
-      <c r="F15" s="84" t="s">
+      <c r="F15" s="27" t="s">
         <v>290</v>
       </c>
-      <c r="G15" s="129"/>
+      <c r="G15" s="120"/>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A16" s="29">
@@ -11827,7 +11769,7 @@
       <c r="A4" s="48" t="s">
         <v>17</v>
       </c>
-      <c r="B4" s="72" t="s">
+      <c r="B4" s="71" t="s">
         <v>46</v>
       </c>
       <c r="C4" s="48" t="s">
@@ -12003,6 +11945,9 @@
 
 <file path=xl/worksheets/sheet31.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1E00-000000000000}">
+  <sheetPr>
+    <tabColor rgb="FFFF0000"/>
+  </sheetPr>
   <dimension ref="A1:G18"/>
   <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
@@ -12013,7 +11958,9 @@
     <col min="5" max="5" width="14.44140625" style="3" customWidth="1"/>
     <col min="6" max="6" width="12.5546875" style="3" customWidth="1"/>
     <col min="7" max="7" width="14.5546875" style="3" bestFit="1" customWidth="1"/>
-    <col min="8" max="16384" width="8.88671875" style="3"/>
+    <col min="8" max="8" width="8.88671875" style="3"/>
+    <col min="9" max="9" width="60.21875" style="3" customWidth="1"/>
+    <col min="10" max="16384" width="8.88671875" style="3"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.3">
@@ -12036,7 +11983,7 @@
       <c r="A4" s="48" t="s">
         <v>17</v>
       </c>
-      <c r="B4" s="72" t="s">
+      <c r="B4" s="71" t="s">
         <v>46</v>
       </c>
       <c r="C4" s="48" t="s">
@@ -12234,25 +12181,25 @@
       <c r="A2" s="38"/>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A3" s="157" t="s">
+      <c r="A3" s="148" t="s">
         <v>17</v>
       </c>
-      <c r="B3" s="157" t="s">
+      <c r="B3" s="148" t="s">
         <v>189</v>
       </c>
-      <c r="C3" s="157" t="s">
+      <c r="C3" s="148" t="s">
         <v>190</v>
       </c>
-      <c r="D3" s="157" t="s">
+      <c r="D3" s="148" t="s">
         <v>191</v>
       </c>
-      <c r="E3" s="157"/>
-      <c r="F3" s="157"/>
+      <c r="E3" s="148"/>
+      <c r="F3" s="148"/>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A4" s="157"/>
-      <c r="B4" s="157"/>
-      <c r="C4" s="157"/>
+      <c r="A4" s="148"/>
+      <c r="B4" s="148"/>
+      <c r="C4" s="148"/>
       <c r="D4" s="27" t="s">
         <v>192</v>
       </c>
@@ -12291,9 +12238,9 @@
         <v>40</v>
       </c>
       <c r="C6" s="25"/>
-      <c r="D6" s="108"/>
-      <c r="E6" s="108"/>
-      <c r="F6" s="108"/>
+      <c r="D6" s="100"/>
+      <c r="E6" s="100"/>
+      <c r="F6" s="100"/>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A7" s="31">
@@ -12303,9 +12250,9 @@
         <v>41</v>
       </c>
       <c r="C7" s="25"/>
-      <c r="D7" s="108"/>
-      <c r="E7" s="108"/>
-      <c r="F7" s="108"/>
+      <c r="D7" s="100"/>
+      <c r="E7" s="100"/>
+      <c r="F7" s="100"/>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A8" s="31">
@@ -12315,9 +12262,9 @@
         <v>12</v>
       </c>
       <c r="C8" s="25"/>
-      <c r="D8" s="108"/>
-      <c r="E8" s="108"/>
-      <c r="F8" s="108"/>
+      <c r="D8" s="100"/>
+      <c r="E8" s="100"/>
+      <c r="F8" s="100"/>
     </row>
   </sheetData>
   <mergeCells count="4">
@@ -12344,7 +12291,7 @@
     <col min="4" max="6" width="7.5546875" style="3" customWidth="1"/>
     <col min="7" max="7" width="18.5546875" style="3" customWidth="1"/>
     <col min="8" max="8" width="14.5546875" style="3" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="8.88671875" style="75"/>
+    <col min="9" max="9" width="8.88671875" style="74"/>
     <col min="10" max="16384" width="8.88671875" style="3"/>
   </cols>
   <sheetData>
@@ -12382,28 +12329,28 @@
       <c r="A6" s="38"/>
     </row>
     <row r="7" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="157" t="s">
+      <c r="A7" s="148" t="s">
         <v>17</v>
       </c>
-      <c r="B7" s="157" t="s">
+      <c r="B7" s="148" t="s">
         <v>195</v>
       </c>
-      <c r="C7" s="157" t="s">
+      <c r="C7" s="148" t="s">
         <v>196</v>
       </c>
-      <c r="D7" s="157" t="s">
+      <c r="D7" s="148" t="s">
         <v>86</v>
       </c>
-      <c r="E7" s="157"/>
-      <c r="F7" s="157"/>
-      <c r="G7" s="157" t="s">
+      <c r="E7" s="148"/>
+      <c r="F7" s="148"/>
+      <c r="G7" s="148" t="s">
         <v>197</v>
       </c>
     </row>
     <row r="8" spans="1:9" ht="27.6" x14ac:dyDescent="0.3">
-      <c r="A8" s="157"/>
-      <c r="B8" s="157"/>
-      <c r="C8" s="157"/>
+      <c r="A8" s="148"/>
+      <c r="B8" s="148"/>
+      <c r="C8" s="148"/>
       <c r="D8" s="27" t="s">
         <v>198</v>
       </c>
@@ -12413,7 +12360,7 @@
       <c r="F8" s="27" t="s">
         <v>25</v>
       </c>
-      <c r="G8" s="157"/>
+      <c r="G8" s="148"/>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A9" s="29">
@@ -12559,7 +12506,7 @@
     <col min="4" max="6" width="7.5546875" style="3" customWidth="1"/>
     <col min="7" max="7" width="18.5546875" style="3" customWidth="1"/>
     <col min="8" max="8" width="14.5546875" style="3" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="8.88671875" style="75"/>
+    <col min="9" max="9" width="8.88671875" style="74"/>
     <col min="10" max="16384" width="8.88671875" style="3"/>
   </cols>
   <sheetData>
@@ -12573,7 +12520,7 @@
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A2" s="38"/>
-      <c r="H2" s="75"/>
+      <c r="H2" s="74"/>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A3" s="54" t="s">
@@ -12603,28 +12550,28 @@
       <c r="A7" s="38"/>
     </row>
     <row r="8" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="157" t="s">
+      <c r="A8" s="148" t="s">
         <v>17</v>
       </c>
-      <c r="B8" s="157" t="s">
+      <c r="B8" s="148" t="s">
         <v>195</v>
       </c>
-      <c r="C8" s="157" t="s">
+      <c r="C8" s="148" t="s">
         <v>196</v>
       </c>
-      <c r="D8" s="157" t="s">
+      <c r="D8" s="148" t="s">
         <v>86</v>
       </c>
-      <c r="E8" s="157"/>
-      <c r="F8" s="157"/>
-      <c r="G8" s="157" t="s">
+      <c r="E8" s="148"/>
+      <c r="F8" s="148"/>
+      <c r="G8" s="148" t="s">
         <v>197</v>
       </c>
     </row>
     <row r="9" spans="1:9" ht="27.6" x14ac:dyDescent="0.3">
-      <c r="A9" s="157"/>
-      <c r="B9" s="157"/>
-      <c r="C9" s="157"/>
+      <c r="A9" s="148"/>
+      <c r="B9" s="148"/>
+      <c r="C9" s="148"/>
       <c r="D9" s="27" t="s">
         <v>198</v>
       </c>
@@ -12634,7 +12581,7 @@
       <c r="F9" s="27" t="s">
         <v>25</v>
       </c>
-      <c r="G9" s="157"/>
+      <c r="G9" s="148"/>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A10" s="29">
@@ -12800,29 +12747,29 @@
       <c r="B3" s="38"/>
     </row>
     <row r="4" spans="1:12" ht="29.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="157" t="s">
+      <c r="A4" s="148" t="s">
         <v>204</v>
       </c>
-      <c r="B4" s="157" t="s">
+      <c r="B4" s="148" t="s">
         <v>205</v>
       </c>
-      <c r="C4" s="157" t="s">
+      <c r="C4" s="148" t="s">
         <v>206</v>
       </c>
-      <c r="D4" s="157"/>
-      <c r="E4" s="157"/>
-      <c r="F4" s="157"/>
-      <c r="G4" s="157"/>
-      <c r="H4" s="157" t="s">
+      <c r="D4" s="148"/>
+      <c r="E4" s="148"/>
+      <c r="F4" s="148"/>
+      <c r="G4" s="148"/>
+      <c r="H4" s="148" t="s">
         <v>207</v>
       </c>
-      <c r="I4" s="157" t="s">
+      <c r="I4" s="148" t="s">
         <v>208</v>
       </c>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A5" s="157"/>
-      <c r="B5" s="157"/>
+      <c r="A5" s="148"/>
+      <c r="B5" s="148"/>
       <c r="C5" s="27" t="s">
         <v>209</v>
       </c>
@@ -12838,8 +12785,8 @@
       <c r="G5" s="27" t="s">
         <v>213</v>
       </c>
-      <c r="H5" s="157"/>
-      <c r="I5" s="157"/>
+      <c r="H5" s="148"/>
+      <c r="I5" s="148"/>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A6" s="29">
@@ -12877,8 +12824,8 @@
       <c r="B7" s="31">
         <v>101</v>
       </c>
-      <c r="C7" s="76"/>
-      <c r="D7" s="76"/>
+      <c r="C7" s="75"/>
+      <c r="D7" s="75"/>
       <c r="E7" s="25"/>
       <c r="F7" s="25"/>
       <c r="G7" s="25"/>
@@ -12892,9 +12839,9 @@
       <c r="B8" s="31">
         <v>97</v>
       </c>
-      <c r="C8" s="76"/>
-      <c r="D8" s="76"/>
-      <c r="E8" s="76"/>
+      <c r="C8" s="75"/>
+      <c r="D8" s="75"/>
+      <c r="E8" s="75"/>
       <c r="F8" s="25"/>
       <c r="G8" s="25"/>
       <c r="H8" s="25"/>
@@ -12907,64 +12854,64 @@
       <c r="B9" s="31">
         <v>89</v>
       </c>
-      <c r="C9" s="76"/>
-      <c r="D9" s="76"/>
-      <c r="E9" s="76"/>
-      <c r="F9" s="76"/>
+      <c r="C9" s="75"/>
+      <c r="D9" s="75"/>
+      <c r="E9" s="75"/>
+      <c r="F9" s="75"/>
       <c r="G9" s="25"/>
       <c r="H9" s="25"/>
       <c r="I9" s="25"/>
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A10" s="77"/>
-      <c r="B10" s="77"/>
-      <c r="C10" s="77"/>
-      <c r="D10" s="77"/>
-      <c r="E10" s="77"/>
-      <c r="F10" s="77"/>
-      <c r="G10" s="77"/>
-      <c r="H10" s="77"/>
-      <c r="I10" s="77"/>
+      <c r="A10" s="76"/>
+      <c r="B10" s="76"/>
+      <c r="C10" s="76"/>
+      <c r="D10" s="76"/>
+      <c r="E10" s="76"/>
+      <c r="F10" s="76"/>
+      <c r="G10" s="76"/>
+      <c r="H10" s="76"/>
+      <c r="I10" s="76"/>
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A11" s="50" t="s">
         <v>214</v>
       </c>
-      <c r="B11" s="77"/>
-      <c r="C11" s="77"/>
-      <c r="D11" s="77"/>
-      <c r="E11" s="77"/>
-      <c r="F11" s="77"/>
-      <c r="G11" s="77"/>
-      <c r="H11" s="77"/>
-      <c r="I11" s="77"/>
+      <c r="B11" s="76"/>
+      <c r="C11" s="76"/>
+      <c r="D11" s="76"/>
+      <c r="E11" s="76"/>
+      <c r="F11" s="76"/>
+      <c r="G11" s="76"/>
+      <c r="H11" s="76"/>
+      <c r="I11" s="76"/>
     </row>
     <row r="12" spans="1:12" ht="29.1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="157" t="s">
+      <c r="A12" s="148" t="s">
         <v>204</v>
       </c>
-      <c r="B12" s="157" t="s">
+      <c r="B12" s="148" t="s">
         <v>205</v>
       </c>
-      <c r="C12" s="157" t="s">
+      <c r="C12" s="148" t="s">
         <v>206</v>
       </c>
-      <c r="D12" s="157"/>
-      <c r="E12" s="157"/>
-      <c r="F12" s="157"/>
-      <c r="G12" s="157"/>
-      <c r="H12" s="157"/>
-      <c r="I12" s="157"/>
-      <c r="J12" s="157" t="s">
+      <c r="D12" s="148"/>
+      <c r="E12" s="148"/>
+      <c r="F12" s="148"/>
+      <c r="G12" s="148"/>
+      <c r="H12" s="148"/>
+      <c r="I12" s="148"/>
+      <c r="J12" s="148" t="s">
         <v>215</v>
       </c>
-      <c r="K12" s="157" t="s">
+      <c r="K12" s="148" t="s">
         <v>208</v>
       </c>
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A13" s="157"/>
-      <c r="B13" s="157"/>
+      <c r="A13" s="148"/>
+      <c r="B13" s="148"/>
       <c r="C13" s="27" t="s">
         <v>216</v>
       </c>
@@ -12986,8 +12933,8 @@
       <c r="I13" s="27" t="s">
         <v>213</v>
       </c>
-      <c r="J13" s="157"/>
-      <c r="K13" s="157"/>
+      <c r="J13" s="148"/>
+      <c r="K13" s="148"/>
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A14" s="29">
@@ -13029,9 +12976,9 @@
       <c r="B15" s="31">
         <v>111</v>
       </c>
-      <c r="C15" s="76"/>
-      <c r="D15" s="76"/>
-      <c r="E15" s="76"/>
+      <c r="C15" s="75"/>
+      <c r="D15" s="75"/>
+      <c r="E15" s="75"/>
       <c r="F15" s="25"/>
       <c r="G15" s="25"/>
       <c r="H15" s="25"/>
@@ -13046,10 +12993,10 @@
       <c r="B16" s="31">
         <v>102</v>
       </c>
-      <c r="C16" s="76"/>
-      <c r="D16" s="76"/>
-      <c r="E16" s="76"/>
-      <c r="F16" s="76"/>
+      <c r="C16" s="75"/>
+      <c r="D16" s="75"/>
+      <c r="E16" s="75"/>
+      <c r="F16" s="75"/>
       <c r="G16" s="25"/>
       <c r="H16" s="25"/>
       <c r="I16" s="25"/>
@@ -13063,11 +13010,11 @@
       <c r="B17" s="31">
         <v>101</v>
       </c>
-      <c r="C17" s="76"/>
-      <c r="D17" s="76"/>
-      <c r="E17" s="76"/>
-      <c r="F17" s="76"/>
-      <c r="G17" s="76"/>
+      <c r="C17" s="75"/>
+      <c r="D17" s="75"/>
+      <c r="E17" s="75"/>
+      <c r="F17" s="75"/>
+      <c r="G17" s="75"/>
       <c r="H17" s="25"/>
       <c r="I17" s="25"/>
       <c r="J17" s="25"/>
@@ -13080,70 +13027,70 @@
       <c r="B18" s="31">
         <v>97</v>
       </c>
-      <c r="C18" s="76"/>
-      <c r="D18" s="76"/>
-      <c r="E18" s="76"/>
-      <c r="F18" s="76"/>
-      <c r="G18" s="76"/>
-      <c r="H18" s="76"/>
+      <c r="C18" s="75"/>
+      <c r="D18" s="75"/>
+      <c r="E18" s="75"/>
+      <c r="F18" s="75"/>
+      <c r="G18" s="75"/>
+      <c r="H18" s="75"/>
       <c r="I18" s="25"/>
       <c r="J18" s="25"/>
       <c r="K18" s="25"/>
     </row>
     <row r="19" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A19" s="77"/>
-      <c r="B19" s="77"/>
-      <c r="C19" s="77"/>
-      <c r="D19" s="77"/>
-      <c r="E19" s="77"/>
-      <c r="F19" s="77"/>
-      <c r="G19" s="77"/>
-      <c r="H19" s="77"/>
-      <c r="I19" s="77"/>
-      <c r="J19" s="77"/>
-      <c r="K19" s="77"/>
+      <c r="A19" s="76"/>
+      <c r="B19" s="76"/>
+      <c r="C19" s="76"/>
+      <c r="D19" s="76"/>
+      <c r="E19" s="76"/>
+      <c r="F19" s="76"/>
+      <c r="G19" s="76"/>
+      <c r="H19" s="76"/>
+      <c r="I19" s="76"/>
+      <c r="J19" s="76"/>
+      <c r="K19" s="76"/>
     </row>
     <row r="20" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A20" s="50" t="s">
         <v>224</v>
       </c>
-      <c r="B20" s="77"/>
-      <c r="C20" s="77"/>
-      <c r="D20" s="77"/>
-      <c r="E20" s="77"/>
-      <c r="F20" s="77"/>
-      <c r="G20" s="77"/>
-      <c r="H20" s="77"/>
-      <c r="I20" s="77"/>
-      <c r="J20" s="77"/>
-      <c r="K20" s="77"/>
+      <c r="B20" s="76"/>
+      <c r="C20" s="76"/>
+      <c r="D20" s="76"/>
+      <c r="E20" s="76"/>
+      <c r="F20" s="76"/>
+      <c r="G20" s="76"/>
+      <c r="H20" s="76"/>
+      <c r="I20" s="76"/>
+      <c r="J20" s="76"/>
+      <c r="K20" s="76"/>
     </row>
     <row r="21" spans="1:11" ht="29.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="148" t="s">
+      <c r="A21" s="139" t="s">
         <v>204</v>
       </c>
-      <c r="B21" s="157" t="s">
+      <c r="B21" s="148" t="s">
         <v>205</v>
       </c>
-      <c r="C21" s="148" t="s">
+      <c r="C21" s="139" t="s">
         <v>206</v>
       </c>
-      <c r="D21" s="148"/>
-      <c r="E21" s="148"/>
-      <c r="F21" s="148"/>
-      <c r="G21" s="149" t="s">
+      <c r="D21" s="139"/>
+      <c r="E21" s="139"/>
+      <c r="F21" s="139"/>
+      <c r="G21" s="140" t="s">
         <v>225</v>
       </c>
-      <c r="H21" s="157" t="s">
+      <c r="H21" s="148" t="s">
         <v>208</v>
       </c>
-      <c r="I21" s="77"/>
-      <c r="J21" s="77"/>
-      <c r="K21" s="77"/>
+      <c r="I21" s="76"/>
+      <c r="J21" s="76"/>
+      <c r="K21" s="76"/>
     </row>
     <row r="22" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A22" s="148"/>
-      <c r="B22" s="157"/>
+      <c r="A22" s="139"/>
+      <c r="B22" s="148"/>
       <c r="C22" s="27" t="s">
         <v>219</v>
       </c>
@@ -13156,11 +13103,11 @@
       <c r="F22" s="27" t="s">
         <v>213</v>
       </c>
-      <c r="G22" s="150"/>
-      <c r="H22" s="157"/>
-      <c r="I22" s="77"/>
-      <c r="J22" s="77"/>
-      <c r="K22" s="77"/>
+      <c r="G22" s="141"/>
+      <c r="H22" s="148"/>
+      <c r="I22" s="76"/>
+      <c r="J22" s="76"/>
+      <c r="K22" s="76"/>
     </row>
     <row r="23" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A23" s="29">
@@ -13185,9 +13132,9 @@
       <c r="H23" s="29">
         <v>7</v>
       </c>
-      <c r="I23" s="77"/>
-      <c r="J23" s="77"/>
-      <c r="K23" s="77"/>
+      <c r="I23" s="76"/>
+      <c r="J23" s="76"/>
+      <c r="K23" s="76"/>
     </row>
     <row r="24" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A24" s="31" t="s">
@@ -13196,15 +13143,15 @@
       <c r="B24" s="31">
         <v>20</v>
       </c>
-      <c r="C24" s="76"/>
+      <c r="C24" s="75"/>
       <c r="D24" s="25"/>
       <c r="E24" s="25"/>
       <c r="F24" s="25"/>
       <c r="G24" s="25"/>
       <c r="H24" s="25"/>
-      <c r="I24" s="77"/>
-      <c r="J24" s="77"/>
-      <c r="K24" s="77"/>
+      <c r="I24" s="76"/>
+      <c r="J24" s="76"/>
+      <c r="K24" s="76"/>
     </row>
     <row r="25" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A25" s="31" t="s">
@@ -13213,15 +13160,15 @@
       <c r="B25" s="31">
         <v>16</v>
       </c>
-      <c r="C25" s="76"/>
-      <c r="D25" s="76"/>
+      <c r="C25" s="75"/>
+      <c r="D25" s="75"/>
       <c r="E25" s="25"/>
       <c r="F25" s="25"/>
       <c r="G25" s="25"/>
       <c r="H25" s="25"/>
-      <c r="I25" s="77"/>
-      <c r="J25" s="77"/>
-      <c r="K25" s="77"/>
+      <c r="I25" s="76"/>
+      <c r="J25" s="76"/>
+      <c r="K25" s="76"/>
     </row>
     <row r="26" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A26" s="31" t="s">
@@ -13230,70 +13177,70 @@
       <c r="B26" s="31">
         <v>18</v>
       </c>
-      <c r="C26" s="76"/>
-      <c r="D26" s="76"/>
-      <c r="E26" s="76"/>
+      <c r="C26" s="75"/>
+      <c r="D26" s="75"/>
+      <c r="E26" s="75"/>
       <c r="F26" s="25"/>
       <c r="G26" s="25"/>
       <c r="H26" s="25"/>
-      <c r="I26" s="77"/>
-      <c r="J26" s="77"/>
-      <c r="K26" s="77"/>
+      <c r="I26" s="76"/>
+      <c r="J26" s="76"/>
+      <c r="K26" s="76"/>
     </row>
     <row r="27" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A27" s="77"/>
-      <c r="B27" s="77"/>
-      <c r="C27" s="77"/>
-      <c r="D27" s="77"/>
-      <c r="E27" s="77"/>
-      <c r="F27" s="77"/>
-      <c r="G27" s="77"/>
-      <c r="H27" s="77"/>
-      <c r="I27" s="77"/>
-      <c r="J27" s="77"/>
-      <c r="K27" s="77"/>
+      <c r="A27" s="76"/>
+      <c r="B27" s="76"/>
+      <c r="C27" s="76"/>
+      <c r="D27" s="76"/>
+      <c r="E27" s="76"/>
+      <c r="F27" s="76"/>
+      <c r="G27" s="76"/>
+      <c r="H27" s="76"/>
+      <c r="I27" s="76"/>
+      <c r="J27" s="76"/>
+      <c r="K27" s="76"/>
     </row>
     <row r="28" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A28" s="54" t="s">
         <v>226</v>
       </c>
-      <c r="B28" s="77"/>
-      <c r="C28" s="77"/>
-      <c r="D28" s="77"/>
-      <c r="E28" s="77"/>
-      <c r="F28" s="77"/>
-      <c r="G28" s="77"/>
-      <c r="H28" s="77"/>
-      <c r="I28" s="77"/>
-      <c r="J28" s="77"/>
-      <c r="K28" s="77"/>
+      <c r="B28" s="76"/>
+      <c r="C28" s="76"/>
+      <c r="D28" s="76"/>
+      <c r="E28" s="76"/>
+      <c r="F28" s="76"/>
+      <c r="G28" s="76"/>
+      <c r="H28" s="76"/>
+      <c r="I28" s="76"/>
+      <c r="J28" s="76"/>
+      <c r="K28" s="76"/>
     </row>
     <row r="29" spans="1:11" ht="29.1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A29" s="129" t="s">
+      <c r="A29" s="120" t="s">
         <v>204</v>
       </c>
-      <c r="B29" s="157" t="s">
+      <c r="B29" s="148" t="s">
         <v>205</v>
       </c>
-      <c r="C29" s="129" t="s">
+      <c r="C29" s="120" t="s">
         <v>206</v>
       </c>
-      <c r="D29" s="129"/>
-      <c r="E29" s="129"/>
-      <c r="F29" s="129"/>
-      <c r="G29" s="129"/>
-      <c r="H29" s="129"/>
-      <c r="I29" s="157"/>
-      <c r="J29" s="157" t="s">
+      <c r="D29" s="120"/>
+      <c r="E29" s="120"/>
+      <c r="F29" s="120"/>
+      <c r="G29" s="120"/>
+      <c r="H29" s="120"/>
+      <c r="I29" s="148"/>
+      <c r="J29" s="148" t="s">
         <v>225</v>
       </c>
-      <c r="K29" s="157" t="s">
+      <c r="K29" s="148" t="s">
         <v>208</v>
       </c>
     </row>
     <row r="30" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A30" s="157"/>
-      <c r="B30" s="157"/>
+      <c r="A30" s="148"/>
+      <c r="B30" s="148"/>
       <c r="C30" s="27" t="s">
         <v>216</v>
       </c>
@@ -13315,8 +13262,8 @@
       <c r="I30" s="27" t="s">
         <v>213</v>
       </c>
-      <c r="J30" s="157"/>
-      <c r="K30" s="157"/>
+      <c r="J30" s="148"/>
+      <c r="K30" s="148"/>
     </row>
     <row r="31" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A31" s="29">
@@ -13358,8 +13305,8 @@
       <c r="B32" s="31">
         <v>6</v>
       </c>
-      <c r="C32" s="76"/>
-      <c r="D32" s="76"/>
+      <c r="C32" s="75"/>
+      <c r="D32" s="75"/>
       <c r="E32" s="25"/>
       <c r="F32" s="25"/>
       <c r="G32" s="25"/>
@@ -13375,9 +13322,9 @@
       <c r="B33" s="31">
         <v>6</v>
       </c>
-      <c r="C33" s="76"/>
-      <c r="D33" s="76"/>
-      <c r="E33" s="76"/>
+      <c r="C33" s="75"/>
+      <c r="D33" s="75"/>
+      <c r="E33" s="75"/>
       <c r="F33" s="25"/>
       <c r="G33" s="25"/>
       <c r="H33" s="25"/>
@@ -13392,10 +13339,10 @@
       <c r="B34" s="31">
         <v>6</v>
       </c>
-      <c r="C34" s="76"/>
-      <c r="D34" s="76"/>
-      <c r="E34" s="76"/>
-      <c r="F34" s="76"/>
+      <c r="C34" s="75"/>
+      <c r="D34" s="75"/>
+      <c r="E34" s="75"/>
+      <c r="F34" s="75"/>
       <c r="G34" s="25"/>
       <c r="H34" s="25"/>
       <c r="I34" s="25"/>
@@ -13409,11 +13356,11 @@
       <c r="B35" s="31">
         <v>8</v>
       </c>
-      <c r="C35" s="76"/>
-      <c r="D35" s="76"/>
-      <c r="E35" s="76"/>
-      <c r="F35" s="76"/>
-      <c r="G35" s="76"/>
+      <c r="C35" s="75"/>
+      <c r="D35" s="75"/>
+      <c r="E35" s="75"/>
+      <c r="F35" s="75"/>
+      <c r="G35" s="75"/>
       <c r="H35" s="25"/>
       <c r="I35" s="25"/>
       <c r="J35" s="25"/>
@@ -13426,23 +13373,23 @@
       <c r="B36" s="31">
         <v>10</v>
       </c>
-      <c r="C36" s="76"/>
-      <c r="D36" s="76"/>
-      <c r="E36" s="76"/>
-      <c r="F36" s="76"/>
-      <c r="G36" s="76"/>
-      <c r="H36" s="76"/>
+      <c r="C36" s="75"/>
+      <c r="D36" s="75"/>
+      <c r="E36" s="75"/>
+      <c r="F36" s="75"/>
+      <c r="G36" s="75"/>
+      <c r="H36" s="75"/>
       <c r="I36" s="25"/>
       <c r="J36" s="25"/>
       <c r="K36" s="25"/>
     </row>
   </sheetData>
   <mergeCells count="20">
-    <mergeCell ref="A4:A5"/>
-    <mergeCell ref="B4:B5"/>
-    <mergeCell ref="C4:G4"/>
-    <mergeCell ref="H4:H5"/>
-    <mergeCell ref="I4:I5"/>
+    <mergeCell ref="A29:A30"/>
+    <mergeCell ref="B29:B30"/>
+    <mergeCell ref="C29:I29"/>
+    <mergeCell ref="J29:J30"/>
+    <mergeCell ref="K29:K30"/>
     <mergeCell ref="J12:J13"/>
     <mergeCell ref="K12:K13"/>
     <mergeCell ref="A21:A22"/>
@@ -13453,11 +13400,11 @@
     <mergeCell ref="A12:A13"/>
     <mergeCell ref="B12:B13"/>
     <mergeCell ref="C12:I12"/>
-    <mergeCell ref="A29:A30"/>
-    <mergeCell ref="B29:B30"/>
-    <mergeCell ref="C29:I29"/>
-    <mergeCell ref="J29:J30"/>
-    <mergeCell ref="K29:K30"/>
+    <mergeCell ref="A4:A5"/>
+    <mergeCell ref="B4:B5"/>
+    <mergeCell ref="C4:G4"/>
+    <mergeCell ref="H4:H5"/>
+    <mergeCell ref="I4:I5"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="L1" location="'Daftar Tabel'!A1" display="&lt;&lt;&lt; Daftar Tabel" xr:uid="{00000000-0004-0000-2200-000000000000}"/>
@@ -13504,29 +13451,29 @@
       <c r="D3" s="38"/>
     </row>
     <row r="4" spans="1:8" ht="31.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="157" t="s">
+      <c r="A4" s="148" t="s">
         <v>189</v>
       </c>
-      <c r="B4" s="157" t="s">
+      <c r="B4" s="148" t="s">
         <v>190</v>
       </c>
-      <c r="C4" s="157" t="s">
+      <c r="C4" s="148" t="s">
         <v>228</v>
       </c>
-      <c r="D4" s="157" t="s">
+      <c r="D4" s="148" t="s">
         <v>229</v>
       </c>
-      <c r="E4" s="157" t="s">
+      <c r="E4" s="148" t="s">
         <v>370</v>
       </c>
-      <c r="F4" s="157"/>
-      <c r="G4" s="157"/>
+      <c r="F4" s="148"/>
+      <c r="G4" s="148"/>
     </row>
     <row r="5" spans="1:8" ht="27.6" x14ac:dyDescent="0.3">
-      <c r="A5" s="157"/>
-      <c r="B5" s="157"/>
-      <c r="C5" s="157"/>
-      <c r="D5" s="157"/>
+      <c r="A5" s="148"/>
+      <c r="B5" s="148"/>
+      <c r="C5" s="148"/>
+      <c r="D5" s="148"/>
       <c r="E5" s="27" t="s">
         <v>230</v>
       </c>
@@ -13597,39 +13544,39 @@
       <c r="A10" s="33" t="s">
         <v>42</v>
       </c>
-      <c r="B10" s="117">
+      <c r="B10" s="33">
         <f>SUM(B7:B9)</f>
         <v>0</v>
       </c>
-      <c r="C10" s="117">
+      <c r="C10" s="33">
         <f t="shared" ref="C10:G10" si="0">SUM(C7:C9)</f>
         <v>0</v>
       </c>
-      <c r="D10" s="117">
+      <c r="D10" s="33">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="E10" s="117">
+      <c r="E10" s="33">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="F10" s="117">
+      <c r="F10" s="33">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="G10" s="117">
+      <c r="G10" s="33">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A11" s="77"/>
-      <c r="B11" s="77"/>
-      <c r="C11" s="77"/>
-      <c r="D11" s="77"/>
-      <c r="E11" s="78"/>
-      <c r="F11" s="78"/>
-      <c r="G11" s="78"/>
+      <c r="A11" s="76"/>
+      <c r="B11" s="76"/>
+      <c r="C11" s="76"/>
+      <c r="D11" s="76"/>
+      <c r="E11" s="77"/>
+      <c r="F11" s="77"/>
+      <c r="G11" s="77"/>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A12" s="54" t="s">
@@ -13640,25 +13587,25 @@
       <c r="D12" s="38"/>
     </row>
     <row r="13" spans="1:8" ht="33" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="157" t="s">
+      <c r="A13" s="148" t="s">
         <v>189</v>
       </c>
-      <c r="B13" s="157" t="s">
+      <c r="B13" s="148" t="s">
         <v>190</v>
       </c>
-      <c r="C13" s="157" t="s">
+      <c r="C13" s="148" t="s">
         <v>228</v>
       </c>
-      <c r="D13" s="157" t="s">
+      <c r="D13" s="148" t="s">
         <v>370</v>
       </c>
-      <c r="E13" s="157"/>
-      <c r="F13" s="157"/>
+      <c r="E13" s="148"/>
+      <c r="F13" s="148"/>
     </row>
     <row r="14" spans="1:8" ht="27.6" x14ac:dyDescent="0.3">
-      <c r="A14" s="157"/>
-      <c r="B14" s="157"/>
-      <c r="C14" s="157"/>
+      <c r="A14" s="148"/>
+      <c r="B14" s="148"/>
+      <c r="C14" s="148"/>
       <c r="D14" s="27" t="s">
         <v>234</v>
       </c>
@@ -13723,23 +13670,23 @@
       <c r="A19" s="33" t="s">
         <v>42</v>
       </c>
-      <c r="B19" s="117">
+      <c r="B19" s="33">
         <f>SUM(B16:B18)</f>
         <v>0</v>
       </c>
-      <c r="C19" s="117">
+      <c r="C19" s="33">
         <f t="shared" ref="C19:F19" si="1">SUM(C16:C18)</f>
         <v>0</v>
       </c>
-      <c r="D19" s="117">
+      <c r="D19" s="33">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="E19" s="117">
+      <c r="E19" s="33">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="F19" s="117">
+      <c r="F19" s="33">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -13753,25 +13700,25 @@
       <c r="D21" s="38"/>
     </row>
     <row r="22" spans="1:6" ht="32.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="157" t="s">
+      <c r="A22" s="148" t="s">
         <v>189</v>
       </c>
-      <c r="B22" s="157" t="s">
+      <c r="B22" s="148" t="s">
         <v>190</v>
       </c>
-      <c r="C22" s="157" t="s">
+      <c r="C22" s="148" t="s">
         <v>228</v>
       </c>
-      <c r="D22" s="157" t="s">
+      <c r="D22" s="148" t="s">
         <v>370</v>
       </c>
-      <c r="E22" s="157"/>
-      <c r="F22" s="157"/>
+      <c r="E22" s="148"/>
+      <c r="F22" s="148"/>
     </row>
     <row r="23" spans="1:6" ht="27.6" x14ac:dyDescent="0.3">
-      <c r="A23" s="157"/>
-      <c r="B23" s="157"/>
-      <c r="C23" s="157"/>
+      <c r="A23" s="148"/>
+      <c r="B23" s="148"/>
+      <c r="C23" s="148"/>
       <c r="D23" s="27" t="s">
         <v>230</v>
       </c>
@@ -13836,23 +13783,23 @@
       <c r="A28" s="33" t="s">
         <v>42</v>
       </c>
-      <c r="B28" s="117">
+      <c r="B28" s="33">
         <f>SUM(B25:B27)</f>
         <v>0</v>
       </c>
-      <c r="C28" s="117">
+      <c r="C28" s="33">
         <f t="shared" ref="C28:F28" si="2">SUM(C25:C27)</f>
         <v>0</v>
       </c>
-      <c r="D28" s="117">
+      <c r="D28" s="33">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="E28" s="117">
+      <c r="E28" s="33">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="F28" s="117">
+      <c r="F28" s="33">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -13918,25 +13865,25 @@
       <c r="D3" s="38"/>
     </row>
     <row r="4" spans="1:7" ht="31.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="157" t="s">
+      <c r="A4" s="148" t="s">
         <v>189</v>
       </c>
-      <c r="B4" s="157" t="s">
+      <c r="B4" s="148" t="s">
         <v>190</v>
       </c>
-      <c r="C4" s="157" t="s">
+      <c r="C4" s="148" t="s">
         <v>228</v>
       </c>
-      <c r="D4" s="157" t="s">
+      <c r="D4" s="148" t="s">
         <v>371</v>
       </c>
-      <c r="E4" s="157"/>
-      <c r="F4" s="157"/>
+      <c r="E4" s="148"/>
+      <c r="F4" s="148"/>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A5" s="157"/>
-      <c r="B5" s="157"/>
-      <c r="C5" s="157"/>
+      <c r="A5" s="148"/>
+      <c r="B5" s="148"/>
+      <c r="C5" s="148"/>
       <c r="D5" s="27" t="s">
         <v>240</v>
       </c>
@@ -14001,27 +13948,27 @@
       <c r="A10" s="33" t="s">
         <v>42</v>
       </c>
-      <c r="B10" s="117">
+      <c r="B10" s="33">
         <f>SUM(B7:B9)</f>
         <v>0</v>
       </c>
-      <c r="C10" s="117">
+      <c r="C10" s="33">
         <f t="shared" ref="C10:F10" si="0">SUM(C7:C9)</f>
         <v>0</v>
       </c>
-      <c r="D10" s="117">
+      <c r="D10" s="33">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="E10" s="117">
+      <c r="E10" s="33">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="F10" s="117">
+      <c r="F10" s="33">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="G10" s="78"/>
+      <c r="G10" s="77"/>
     </row>
   </sheetData>
   <mergeCells count="4">
@@ -14066,25 +14013,25 @@
       </c>
     </row>
     <row r="4" spans="1:7" ht="45.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="157" t="s">
+      <c r="A4" s="148" t="s">
         <v>189</v>
       </c>
-      <c r="B4" s="157" t="s">
+      <c r="B4" s="148" t="s">
         <v>190</v>
       </c>
-      <c r="C4" s="157" t="s">
+      <c r="C4" s="148" t="s">
         <v>228</v>
       </c>
-      <c r="D4" s="157" t="s">
+      <c r="D4" s="148" t="s">
         <v>369</v>
       </c>
-      <c r="E4" s="157"/>
-      <c r="F4" s="157"/>
+      <c r="E4" s="148"/>
+      <c r="F4" s="148"/>
     </row>
     <row r="5" spans="1:7" ht="41.4" x14ac:dyDescent="0.3">
-      <c r="A5" s="157"/>
-      <c r="B5" s="157"/>
-      <c r="C5" s="157"/>
+      <c r="A5" s="148"/>
+      <c r="B5" s="148"/>
+      <c r="C5" s="148"/>
       <c r="D5" s="27" t="s">
         <v>244</v>
       </c>
@@ -14149,34 +14096,34 @@
       <c r="A10" s="33" t="s">
         <v>42</v>
       </c>
-      <c r="B10" s="117">
+      <c r="B10" s="33">
         <f>SUM(B7:B9)</f>
         <v>0</v>
       </c>
-      <c r="C10" s="117">
+      <c r="C10" s="33">
         <f t="shared" ref="C10:F10" si="0">SUM(C7:C9)</f>
         <v>0</v>
       </c>
-      <c r="D10" s="117">
+      <c r="D10" s="33">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="E10" s="117">
+      <c r="E10" s="33">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="F10" s="117">
+      <c r="F10" s="33">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A11" s="77"/>
-      <c r="B11" s="78"/>
-      <c r="C11" s="77"/>
-      <c r="D11" s="77"/>
-      <c r="E11" s="77"/>
-      <c r="F11" s="77"/>
+      <c r="A11" s="76"/>
+      <c r="B11" s="77"/>
+      <c r="C11" s="76"/>
+      <c r="D11" s="76"/>
+      <c r="E11" s="76"/>
+      <c r="F11" s="76"/>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A12" s="41"/>
@@ -14234,20 +14181,20 @@
       </c>
     </row>
     <row r="4" spans="1:4" ht="24.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="157" t="s">
+      <c r="A4" s="148" t="s">
         <v>189</v>
       </c>
-      <c r="B4" s="157" t="s">
+      <c r="B4" s="148" t="s">
         <v>190</v>
       </c>
-      <c r="C4" s="157" t="s">
+      <c r="C4" s="148" t="s">
         <v>248</v>
       </c>
     </row>
     <row r="5" spans="1:4" ht="24.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="157"/>
-      <c r="B5" s="157"/>
-      <c r="C5" s="157"/>
+      <c r="A5" s="148"/>
+      <c r="B5" s="148"/>
+      <c r="C5" s="148"/>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A6" s="29">
@@ -14349,36 +14296,36 @@
     </row>
     <row r="8" spans="1:11" hidden="1" x14ac:dyDescent="0.3"/>
     <row r="9" spans="1:11" ht="23.1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="135" t="s">
+      <c r="A9" s="126" t="s">
         <v>17</v>
       </c>
-      <c r="B9" s="135" t="s">
+      <c r="B9" s="126" t="s">
         <v>18</v>
       </c>
-      <c r="C9" s="135" t="s">
+      <c r="C9" s="126" t="s">
         <v>19</v>
       </c>
-      <c r="D9" s="135"/>
-      <c r="E9" s="135"/>
-      <c r="F9" s="135" t="s">
+      <c r="D9" s="126"/>
+      <c r="E9" s="126"/>
+      <c r="F9" s="126" t="s">
         <v>20</v>
       </c>
-      <c r="G9" s="135" t="s">
+      <c r="G9" s="126" t="s">
         <v>21</v>
       </c>
-      <c r="H9" s="135" t="s">
+      <c r="H9" s="126" t="s">
         <v>22</v>
       </c>
-      <c r="I9" s="135" t="s">
+      <c r="I9" s="126" t="s">
         <v>23</v>
       </c>
-      <c r="J9" s="133" t="s">
+      <c r="J9" s="124" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="10" spans="1:11" ht="38.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="135"/>
-      <c r="B10" s="135"/>
+      <c r="A10" s="126"/>
+      <c r="B10" s="126"/>
       <c r="C10" s="21" t="s">
         <v>25</v>
       </c>
@@ -14388,11 +14335,11 @@
       <c r="E10" s="21" t="s">
         <v>27</v>
       </c>
-      <c r="F10" s="135"/>
-      <c r="G10" s="135"/>
-      <c r="H10" s="135"/>
-      <c r="I10" s="135"/>
-      <c r="J10" s="134"/>
+      <c r="F10" s="126"/>
+      <c r="G10" s="126"/>
+      <c r="H10" s="126"/>
+      <c r="I10" s="126"/>
+      <c r="J10" s="125"/>
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A11" s="22">
@@ -14565,7 +14512,7 @@
       <c r="H21" s="24"/>
       <c r="I21" s="24"/>
       <c r="J21" s="26"/>
-      <c r="K21" s="115"/>
+      <c r="K21" s="107"/>
     </row>
     <row r="22" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A22" s="23" t="s">
@@ -14604,26 +14551,26 @@
   <conditionalFormatting sqref="C15:E15">
     <cfRule type="duplicateValues" dxfId="41" priority="9"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C22:E22">
-    <cfRule type="duplicateValues" dxfId="40" priority="7"/>
-  </conditionalFormatting>
   <conditionalFormatting sqref="C16:E16">
-    <cfRule type="duplicateValues" dxfId="39" priority="6"/>
+    <cfRule type="duplicateValues" dxfId="40" priority="6"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C17:E17">
-    <cfRule type="duplicateValues" dxfId="38" priority="5"/>
+    <cfRule type="duplicateValues" dxfId="39" priority="5"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C21:E21">
-    <cfRule type="duplicateValues" dxfId="37" priority="4"/>
+  <conditionalFormatting sqref="C18:E18">
+    <cfRule type="duplicateValues" dxfId="38" priority="1"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C19:E19">
+    <cfRule type="duplicateValues" dxfId="37" priority="2"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C20:E20">
     <cfRule type="duplicateValues" dxfId="36" priority="3"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C19:E19">
-    <cfRule type="duplicateValues" dxfId="35" priority="2"/>
+  <conditionalFormatting sqref="C21:E21">
+    <cfRule type="duplicateValues" dxfId="35" priority="4"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C18:E18">
-    <cfRule type="duplicateValues" dxfId="34" priority="1"/>
+  <conditionalFormatting sqref="C22:E22">
+    <cfRule type="duplicateValues" dxfId="34" priority="7"/>
   </conditionalFormatting>
   <dataValidations count="1">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C12:E22" xr:uid="{00000000-0002-0000-0300-000000000000}">
@@ -14669,25 +14616,25 @@
       </c>
     </row>
     <row r="4" spans="1:8" ht="29.1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="157" t="s">
+      <c r="A4" s="148" t="s">
         <v>116</v>
       </c>
-      <c r="B4" s="157" t="s">
+      <c r="B4" s="148" t="s">
         <v>250</v>
       </c>
-      <c r="C4" s="157" t="s">
+      <c r="C4" s="148" t="s">
         <v>251</v>
       </c>
-      <c r="D4" s="157"/>
-      <c r="E4" s="157"/>
-      <c r="F4" s="157"/>
-      <c r="G4" s="157" t="s">
+      <c r="D4" s="148"/>
+      <c r="E4" s="148"/>
+      <c r="F4" s="148"/>
+      <c r="G4" s="148" t="s">
         <v>167</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A5" s="157"/>
-      <c r="B5" s="157"/>
+      <c r="A5" s="148"/>
+      <c r="B5" s="148"/>
       <c r="C5" s="27" t="s">
         <v>168</v>
       </c>
@@ -14700,7 +14647,7 @@
       <c r="F5" s="27" t="s">
         <v>171</v>
       </c>
-      <c r="G5" s="157"/>
+      <c r="G5" s="148"/>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A6" s="29">
@@ -14732,10 +14679,10 @@
       <c r="B7" s="49" t="s">
         <v>4</v>
       </c>
-      <c r="C7" s="79"/>
-      <c r="D7" s="79"/>
-      <c r="E7" s="79"/>
-      <c r="F7" s="79"/>
+      <c r="C7" s="78"/>
+      <c r="D7" s="78"/>
+      <c r="E7" s="78"/>
+      <c r="F7" s="78"/>
       <c r="G7" s="34"/>
     </row>
     <row r="8" spans="1:8" ht="27.6" x14ac:dyDescent="0.3">
@@ -14745,10 +14692,10 @@
       <c r="B8" s="49" t="s">
         <v>252</v>
       </c>
-      <c r="C8" s="79"/>
-      <c r="D8" s="79"/>
-      <c r="E8" s="79"/>
-      <c r="F8" s="79"/>
+      <c r="C8" s="78"/>
+      <c r="D8" s="78"/>
+      <c r="E8" s="78"/>
+      <c r="F8" s="78"/>
       <c r="G8" s="34"/>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.3">
@@ -14758,10 +14705,10 @@
       <c r="B9" s="49" t="s">
         <v>253</v>
       </c>
-      <c r="C9" s="79"/>
-      <c r="D9" s="79"/>
-      <c r="E9" s="79"/>
-      <c r="F9" s="79"/>
+      <c r="C9" s="78"/>
+      <c r="D9" s="78"/>
+      <c r="E9" s="78"/>
+      <c r="F9" s="78"/>
       <c r="G9" s="34"/>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.3">
@@ -14771,10 +14718,10 @@
       <c r="B10" s="49" t="s">
         <v>254</v>
       </c>
-      <c r="C10" s="79"/>
-      <c r="D10" s="79"/>
-      <c r="E10" s="79"/>
-      <c r="F10" s="79"/>
+      <c r="C10" s="78"/>
+      <c r="D10" s="78"/>
+      <c r="E10" s="78"/>
+      <c r="F10" s="78"/>
       <c r="G10" s="34"/>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.3">
@@ -14784,10 +14731,10 @@
       <c r="B11" s="49" t="s">
         <v>255</v>
       </c>
-      <c r="C11" s="79"/>
-      <c r="D11" s="79"/>
-      <c r="E11" s="79"/>
-      <c r="F11" s="79"/>
+      <c r="C11" s="78"/>
+      <c r="D11" s="78"/>
+      <c r="E11" s="78"/>
+      <c r="F11" s="78"/>
       <c r="G11" s="34"/>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.3">
@@ -14797,10 +14744,10 @@
       <c r="B12" s="49" t="s">
         <v>5</v>
       </c>
-      <c r="C12" s="79"/>
-      <c r="D12" s="79"/>
-      <c r="E12" s="79"/>
-      <c r="F12" s="79"/>
+      <c r="C12" s="78"/>
+      <c r="D12" s="78"/>
+      <c r="E12" s="78"/>
+      <c r="F12" s="78"/>
       <c r="G12" s="34"/>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.3">
@@ -14810,22 +14757,22 @@
       <c r="B13" s="49" t="s">
         <v>256</v>
       </c>
-      <c r="C13" s="79"/>
-      <c r="D13" s="79"/>
-      <c r="E13" s="79"/>
-      <c r="F13" s="79"/>
+      <c r="C13" s="78"/>
+      <c r="D13" s="78"/>
+      <c r="E13" s="78"/>
+      <c r="F13" s="78"/>
       <c r="G13" s="34"/>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A14" s="166" t="s">
+      <c r="A14" s="157" t="s">
         <v>42</v>
       </c>
-      <c r="B14" s="166"/>
-      <c r="C14" s="80"/>
-      <c r="D14" s="80"/>
-      <c r="E14" s="80"/>
-      <c r="F14" s="80"/>
-      <c r="G14" s="74"/>
+      <c r="B14" s="157"/>
+      <c r="C14" s="79"/>
+      <c r="D14" s="79"/>
+      <c r="E14" s="79"/>
+      <c r="F14" s="79"/>
+      <c r="G14" s="73"/>
     </row>
   </sheetData>
   <mergeCells count="5">
@@ -14871,34 +14818,34 @@
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A4" s="148" t="s">
+      <c r="A4" s="139" t="s">
         <v>17</v>
       </c>
-      <c r="B4" s="148" t="s">
+      <c r="B4" s="139" t="s">
         <v>100</v>
       </c>
-      <c r="C4" s="148" t="s">
+      <c r="C4" s="139" t="s">
         <v>101</v>
       </c>
-      <c r="D4" s="148"/>
-      <c r="E4" s="148"/>
-      <c r="F4" s="148" t="s">
+      <c r="D4" s="139"/>
+      <c r="E4" s="139"/>
+      <c r="F4" s="139" t="s">
         <v>42</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A5" s="148"/>
-      <c r="B5" s="148"/>
-      <c r="C5" s="82" t="s">
+      <c r="A5" s="139"/>
+      <c r="B5" s="139"/>
+      <c r="C5" s="48" t="s">
         <v>40</v>
       </c>
-      <c r="D5" s="82" t="s">
+      <c r="D5" s="48" t="s">
         <v>41</v>
       </c>
-      <c r="E5" s="82" t="s">
+      <c r="E5" s="48" t="s">
         <v>12</v>
       </c>
-      <c r="F5" s="148"/>
+      <c r="F5" s="139"/>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A6" s="22">
@@ -15071,23 +15018,23 @@
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A17" s="151" t="s">
+      <c r="A17" s="142" t="s">
         <v>42</v>
       </c>
-      <c r="B17" s="152"/>
-      <c r="C17" s="83">
+      <c r="B17" s="143"/>
+      <c r="C17" s="33">
         <f>SUM(C7:C16)</f>
         <v>0</v>
       </c>
-      <c r="D17" s="83">
+      <c r="D17" s="33">
         <f>SUM(D7:D16)</f>
         <v>0</v>
       </c>
-      <c r="E17" s="83">
+      <c r="E17" s="33">
         <f>SUM(E7:E16)</f>
         <v>0</v>
       </c>
-      <c r="F17" s="83">
+      <c r="F17" s="33">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
@@ -15136,24 +15083,24 @@
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A4" s="148" t="s">
+      <c r="A4" s="139" t="s">
         <v>17</v>
       </c>
-      <c r="B4" s="148" t="s">
+      <c r="B4" s="139" t="s">
         <v>100</v>
       </c>
-      <c r="C4" s="148" t="s">
+      <c r="C4" s="139" t="s">
         <v>101</v>
       </c>
-      <c r="D4" s="148"/>
-      <c r="E4" s="148"/>
-      <c r="F4" s="148" t="s">
+      <c r="D4" s="139"/>
+      <c r="E4" s="139"/>
+      <c r="F4" s="139" t="s">
         <v>42</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A5" s="148"/>
-      <c r="B5" s="148"/>
+      <c r="A5" s="139"/>
+      <c r="B5" s="139"/>
       <c r="C5" s="48" t="s">
         <v>40</v>
       </c>
@@ -15163,7 +15110,7 @@
       <c r="E5" s="48" t="s">
         <v>12</v>
       </c>
-      <c r="F5" s="148"/>
+      <c r="F5" s="139"/>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A6" s="22">
@@ -15336,10 +15283,10 @@
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A17" s="151" t="s">
+      <c r="A17" s="142" t="s">
         <v>42</v>
       </c>
-      <c r="B17" s="152"/>
+      <c r="B17" s="143"/>
       <c r="C17" s="33">
         <f>SUM(C7:C16)</f>
         <v>0</v>
@@ -15530,7 +15477,7 @@
       <c r="E4" s="48" t="s">
         <v>131</v>
       </c>
-      <c r="F4" s="87" t="s">
+      <c r="F4" s="48" t="s">
         <v>423</v>
       </c>
     </row>
@@ -15562,7 +15509,7 @@
       <c r="C6" s="60"/>
       <c r="D6" s="25"/>
       <c r="E6" s="25"/>
-      <c r="F6" s="116"/>
+      <c r="F6" s="108"/>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A7" s="31">
@@ -15572,7 +15519,7 @@
       <c r="C7" s="60"/>
       <c r="D7" s="25"/>
       <c r="E7" s="25"/>
-      <c r="F7" s="116"/>
+      <c r="F7" s="108"/>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A8" s="31">
@@ -15582,7 +15529,7 @@
       <c r="C8" s="60"/>
       <c r="D8" s="25"/>
       <c r="E8" s="25"/>
-      <c r="F8" s="116"/>
+      <c r="F8" s="108"/>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A9" s="31">
@@ -15592,7 +15539,7 @@
       <c r="C9" s="60"/>
       <c r="D9" s="25"/>
       <c r="E9" s="25"/>
-      <c r="F9" s="116"/>
+      <c r="F9" s="108"/>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A10" s="31">
@@ -15602,7 +15549,7 @@
       <c r="C10" s="60"/>
       <c r="D10" s="25"/>
       <c r="E10" s="25"/>
-      <c r="F10" s="116"/>
+      <c r="F10" s="108"/>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A11" s="31" t="s">
@@ -15612,7 +15559,7 @@
       <c r="C11" s="60"/>
       <c r="D11" s="25"/>
       <c r="E11" s="25"/>
-      <c r="F11" s="116"/>
+      <c r="F11" s="108"/>
     </row>
   </sheetData>
   <hyperlinks>
@@ -15645,7 +15592,7 @@
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2" s="41"/>
-      <c r="E2" s="109"/>
+      <c r="E2" s="101"/>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A3" s="54" t="s">
@@ -15690,11 +15637,11 @@
       <c r="A7" s="58" t="s">
         <v>58</v>
       </c>
-      <c r="B7" s="153" t="s">
+      <c r="B7" s="144" t="s">
         <v>119</v>
       </c>
-      <c r="C7" s="154"/>
-      <c r="D7" s="155"/>
+      <c r="C7" s="145"/>
+      <c r="D7" s="146"/>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A8" s="59">
@@ -15778,7 +15725,7 @@
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2" s="41"/>
-      <c r="E2" s="109"/>
+      <c r="E2" s="101"/>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A3" s="54" t="s">
@@ -15823,11 +15770,11 @@
       <c r="A7" s="58" t="s">
         <v>120</v>
       </c>
-      <c r="B7" s="153" t="s">
+      <c r="B7" s="144" t="s">
         <v>121</v>
       </c>
-      <c r="C7" s="154"/>
-      <c r="D7" s="155"/>
+      <c r="C7" s="145"/>
+      <c r="D7" s="146"/>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A8" s="59">
@@ -15964,11 +15911,11 @@
       <c r="A7" s="58" t="s">
         <v>122</v>
       </c>
-      <c r="B7" s="153" t="s">
+      <c r="B7" s="144" t="s">
         <v>123</v>
       </c>
-      <c r="C7" s="154"/>
-      <c r="D7" s="155"/>
+      <c r="C7" s="145"/>
+      <c r="D7" s="146"/>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A8" s="59">
@@ -16105,11 +16052,11 @@
       <c r="A7" s="58" t="s">
         <v>124</v>
       </c>
-      <c r="B7" s="153" t="s">
+      <c r="B7" s="144" t="s">
         <v>125</v>
       </c>
-      <c r="C7" s="154"/>
-      <c r="D7" s="155"/>
+      <c r="C7" s="145"/>
+      <c r="D7" s="146"/>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A8" s="59">
@@ -16168,6 +16115,15 @@
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet49.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1DDAA0F1-0EE2-4FE4-8136-6F3F7D2F9753}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
@@ -16213,36 +16169,36 @@
     </row>
     <row r="8" spans="1:11" hidden="1" x14ac:dyDescent="0.3"/>
     <row r="9" spans="1:11" ht="23.1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="135" t="s">
+      <c r="A9" s="126" t="s">
         <v>17</v>
       </c>
-      <c r="B9" s="135" t="s">
+      <c r="B9" s="126" t="s">
         <v>18</v>
       </c>
-      <c r="C9" s="135" t="s">
+      <c r="C9" s="126" t="s">
         <v>19</v>
       </c>
-      <c r="D9" s="135"/>
-      <c r="E9" s="135"/>
-      <c r="F9" s="135" t="s">
+      <c r="D9" s="126"/>
+      <c r="E9" s="126"/>
+      <c r="F9" s="126" t="s">
         <v>20</v>
       </c>
-      <c r="G9" s="135" t="s">
+      <c r="G9" s="126" t="s">
         <v>21</v>
       </c>
-      <c r="H9" s="135" t="s">
+      <c r="H9" s="126" t="s">
         <v>22</v>
       </c>
-      <c r="I9" s="135" t="s">
+      <c r="I9" s="126" t="s">
         <v>23</v>
       </c>
-      <c r="J9" s="135" t="s">
+      <c r="J9" s="126" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="10" spans="1:11" ht="38.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="135"/>
-      <c r="B10" s="135"/>
+      <c r="A10" s="126"/>
+      <c r="B10" s="126"/>
       <c r="C10" s="21" t="s">
         <v>25</v>
       </c>
@@ -16252,11 +16208,11 @@
       <c r="E10" s="21" t="s">
         <v>27</v>
       </c>
-      <c r="F10" s="135"/>
-      <c r="G10" s="135"/>
-      <c r="H10" s="135"/>
-      <c r="I10" s="135"/>
-      <c r="J10" s="135"/>
+      <c r="F10" s="126"/>
+      <c r="G10" s="126"/>
+      <c r="H10" s="126"/>
+      <c r="I10" s="126"/>
+      <c r="J10" s="126"/>
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A11" s="22">
@@ -16461,32 +16417,32 @@
   <conditionalFormatting sqref="C13:E13">
     <cfRule type="duplicateValues" dxfId="32" priority="10"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C19:E19">
-    <cfRule type="duplicateValues" dxfId="31" priority="9"/>
+  <conditionalFormatting sqref="C14:E14">
+    <cfRule type="duplicateValues" dxfId="31" priority="1"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C20:E20">
-    <cfRule type="duplicateValues" dxfId="30" priority="8"/>
+  <conditionalFormatting sqref="C15:E15">
+    <cfRule type="duplicateValues" dxfId="30" priority="2"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C21:E21">
-    <cfRule type="duplicateValues" dxfId="29" priority="7"/>
+  <conditionalFormatting sqref="C16:E16">
+    <cfRule type="duplicateValues" dxfId="29" priority="3"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C22:E22">
-    <cfRule type="duplicateValues" dxfId="28" priority="6"/>
+  <conditionalFormatting sqref="C17:E17">
+    <cfRule type="duplicateValues" dxfId="28" priority="4"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C18:E18">
     <cfRule type="duplicateValues" dxfId="27" priority="5"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C17:E17">
-    <cfRule type="duplicateValues" dxfId="26" priority="4"/>
+  <conditionalFormatting sqref="C19:E19">
+    <cfRule type="duplicateValues" dxfId="26" priority="9"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C16:E16">
-    <cfRule type="duplicateValues" dxfId="25" priority="3"/>
+  <conditionalFormatting sqref="C20:E20">
+    <cfRule type="duplicateValues" dxfId="25" priority="8"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C15:E15">
-    <cfRule type="duplicateValues" dxfId="24" priority="2"/>
+  <conditionalFormatting sqref="C21:E21">
+    <cfRule type="duplicateValues" dxfId="24" priority="7"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C14:E14">
-    <cfRule type="duplicateValues" dxfId="23" priority="1"/>
+  <conditionalFormatting sqref="C22:E22">
+    <cfRule type="duplicateValues" dxfId="23" priority="6"/>
   </conditionalFormatting>
   <dataValidations count="1">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C12:E22" xr:uid="{00000000-0002-0000-0400-000000000000}">
@@ -16544,36 +16500,36 @@
     </row>
     <row r="8" spans="1:11" hidden="1" x14ac:dyDescent="0.3"/>
     <row r="9" spans="1:11" ht="23.1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="135" t="s">
+      <c r="A9" s="126" t="s">
         <v>17</v>
       </c>
-      <c r="B9" s="135" t="s">
+      <c r="B9" s="126" t="s">
         <v>18</v>
       </c>
-      <c r="C9" s="135" t="s">
+      <c r="C9" s="126" t="s">
         <v>19</v>
       </c>
-      <c r="D9" s="135"/>
-      <c r="E9" s="135"/>
-      <c r="F9" s="135" t="s">
+      <c r="D9" s="126"/>
+      <c r="E9" s="126"/>
+      <c r="F9" s="126" t="s">
         <v>20</v>
       </c>
-      <c r="G9" s="135" t="s">
+      <c r="G9" s="126" t="s">
         <v>21</v>
       </c>
-      <c r="H9" s="135" t="s">
+      <c r="H9" s="126" t="s">
         <v>22</v>
       </c>
-      <c r="I9" s="135" t="s">
+      <c r="I9" s="126" t="s">
         <v>23</v>
       </c>
-      <c r="J9" s="135" t="s">
+      <c r="J9" s="126" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="10" spans="1:11" ht="38.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="135"/>
-      <c r="B10" s="135"/>
+      <c r="A10" s="126"/>
+      <c r="B10" s="126"/>
       <c r="C10" s="21" t="s">
         <v>25</v>
       </c>
@@ -16583,11 +16539,11 @@
       <c r="E10" s="21" t="s">
         <v>27</v>
       </c>
-      <c r="F10" s="135"/>
-      <c r="G10" s="135"/>
-      <c r="H10" s="135"/>
-      <c r="I10" s="135"/>
-      <c r="J10" s="135"/>
+      <c r="F10" s="126"/>
+      <c r="G10" s="126"/>
+      <c r="H10" s="126"/>
+      <c r="I10" s="126"/>
+      <c r="J10" s="126"/>
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A11" s="22">
@@ -16795,29 +16751,29 @@
   <conditionalFormatting sqref="C14:E14">
     <cfRule type="duplicateValues" dxfId="20" priority="9"/>
   </conditionalFormatting>
+  <conditionalFormatting sqref="C15:E15">
+    <cfRule type="duplicateValues" dxfId="19" priority="1"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C16:E16">
+    <cfRule type="duplicateValues" dxfId="18" priority="2"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C17:E17">
+    <cfRule type="duplicateValues" dxfId="17" priority="3"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C18:E18">
+    <cfRule type="duplicateValues" dxfId="16" priority="4"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C19:E19">
+    <cfRule type="duplicateValues" dxfId="15" priority="5"/>
+  </conditionalFormatting>
   <conditionalFormatting sqref="C20:E20">
-    <cfRule type="duplicateValues" dxfId="19" priority="8"/>
+    <cfRule type="duplicateValues" dxfId="14" priority="8"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C21:E21">
-    <cfRule type="duplicateValues" dxfId="18" priority="7"/>
+    <cfRule type="duplicateValues" dxfId="13" priority="7"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C22:E22">
-    <cfRule type="duplicateValues" dxfId="17" priority="6"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C19:E19">
-    <cfRule type="duplicateValues" dxfId="16" priority="5"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C18:E18">
-    <cfRule type="duplicateValues" dxfId="15" priority="4"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C17:E17">
-    <cfRule type="duplicateValues" dxfId="14" priority="3"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C16:E16">
-    <cfRule type="duplicateValues" dxfId="13" priority="2"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C15:E15">
-    <cfRule type="duplicateValues" dxfId="12" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="12" priority="6"/>
   </conditionalFormatting>
   <dataValidations count="1">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C12:E22" xr:uid="{00000000-0002-0000-0500-000000000000}">
@@ -16854,28 +16810,28 @@
       </c>
     </row>
     <row r="3" spans="1:9" ht="29.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="128" t="s">
+      <c r="A3" s="119" t="s">
         <v>29</v>
       </c>
-      <c r="B3" s="128" t="s">
+      <c r="B3" s="119" t="s">
         <v>30</v>
       </c>
-      <c r="C3" s="130" t="s">
+      <c r="C3" s="121" t="s">
         <v>31</v>
       </c>
-      <c r="D3" s="132"/>
-      <c r="E3" s="130" t="s">
+      <c r="D3" s="123"/>
+      <c r="E3" s="121" t="s">
         <v>32</v>
       </c>
-      <c r="F3" s="132"/>
-      <c r="G3" s="130" t="s">
+      <c r="F3" s="123"/>
+      <c r="G3" s="121" t="s">
         <v>33</v>
       </c>
-      <c r="H3" s="132"/>
+      <c r="H3" s="123"/>
     </row>
     <row r="4" spans="1:9" ht="27.6" x14ac:dyDescent="0.3">
-      <c r="A4" s="129"/>
-      <c r="B4" s="129"/>
+      <c r="A4" s="120"/>
+      <c r="B4" s="120"/>
       <c r="C4" s="27" t="s">
         <v>34</v>
       </c>
@@ -16982,10 +16938,10 @@
       <c r="H10" s="25"/>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A11" s="136" t="s">
+      <c r="A11" s="127" t="s">
         <v>42</v>
       </c>
-      <c r="B11" s="137"/>
+      <c r="B11" s="128"/>
       <c r="C11" s="33">
         <f t="shared" ref="C11:F11" si="0">SUM(C6:C10)</f>
         <v>0</v>
@@ -17002,11 +16958,11 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="G11" s="136">
+      <c r="G11" s="127">
         <f>SUM(G10:H10)</f>
         <v>0</v>
       </c>
-      <c r="H11" s="137"/>
+      <c r="H11" s="128"/>
     </row>
   </sheetData>
   <mergeCells count="7">
@@ -17031,18 +16987,17 @@
   <dimension ref="A1:L17"/>
   <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="5.88671875" style="101" customWidth="1"/>
-    <col min="2" max="2" width="22.44140625" style="101" customWidth="1"/>
-    <col min="3" max="11" width="9.88671875" style="101" customWidth="1"/>
-    <col min="12" max="12" width="14.5546875" style="101" bestFit="1" customWidth="1"/>
-    <col min="13" max="16384" width="8.88671875" style="101"/>
+    <col min="1" max="1" width="5.88671875" customWidth="1"/>
+    <col min="2" max="2" width="22.44140625" customWidth="1"/>
+    <col min="3" max="11" width="9.88671875" customWidth="1"/>
+    <col min="12" max="12" width="14.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" s="99" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="99" t="s">
+    <row r="1" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="3" t="s">
         <v>298</v>
       </c>
-      <c r="L1" s="100" t="s">
+      <c r="L1" s="20" t="s">
         <v>14</v>
       </c>
     </row>
@@ -17052,91 +17007,91 @@
       </c>
     </row>
     <row r="4" spans="1:12" ht="26.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="128" t="s">
+      <c r="A4" s="119" t="s">
         <v>17</v>
       </c>
-      <c r="B4" s="138" t="s">
+      <c r="B4" s="129" t="s">
         <v>354</v>
       </c>
-      <c r="C4" s="140" t="s">
+      <c r="C4" s="131" t="s">
         <v>33</v>
       </c>
-      <c r="D4" s="141"/>
-      <c r="E4" s="142"/>
-      <c r="F4" s="140" t="s">
+      <c r="D4" s="132"/>
+      <c r="E4" s="133"/>
+      <c r="F4" s="131" t="s">
         <v>355</v>
       </c>
-      <c r="G4" s="141"/>
-      <c r="H4" s="142"/>
-      <c r="I4" s="140" t="s">
+      <c r="G4" s="132"/>
+      <c r="H4" s="133"/>
+      <c r="I4" s="131" t="s">
         <v>356</v>
       </c>
-      <c r="J4" s="141"/>
-      <c r="K4" s="142"/>
+      <c r="J4" s="132"/>
+      <c r="K4" s="133"/>
     </row>
     <row r="5" spans="1:12" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="129"/>
-      <c r="B5" s="139"/>
-      <c r="C5" s="102" t="s">
+      <c r="A5" s="120"/>
+      <c r="B5" s="130"/>
+      <c r="C5" s="94" t="s">
         <v>40</v>
       </c>
-      <c r="D5" s="102" t="s">
+      <c r="D5" s="94" t="s">
         <v>41</v>
       </c>
-      <c r="E5" s="102" t="s">
+      <c r="E5" s="94" t="s">
         <v>12</v>
       </c>
-      <c r="F5" s="102" t="s">
+      <c r="F5" s="94" t="s">
         <v>40</v>
       </c>
-      <c r="G5" s="102" t="s">
+      <c r="G5" s="94" t="s">
         <v>41</v>
       </c>
-      <c r="H5" s="102" t="s">
+      <c r="H5" s="94" t="s">
         <v>12</v>
       </c>
-      <c r="I5" s="102" t="s">
+      <c r="I5" s="94" t="s">
         <v>40</v>
       </c>
-      <c r="J5" s="102" t="s">
+      <c r="J5" s="94" t="s">
         <v>41</v>
       </c>
-      <c r="K5" s="102" t="s">
+      <c r="K5" s="94" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A6" s="103">
+      <c r="A6" s="95">
         <v>1</v>
       </c>
-      <c r="B6" s="103">
+      <c r="B6" s="95">
         <v>2</v>
       </c>
-      <c r="C6" s="103">
+      <c r="C6" s="95">
         <v>3</v>
       </c>
-      <c r="D6" s="103">
+      <c r="D6" s="95">
         <v>4</v>
       </c>
-      <c r="E6" s="103">
+      <c r="E6" s="95">
         <v>5</v>
       </c>
-      <c r="F6" s="103">
+      <c r="F6" s="95">
         <v>6</v>
       </c>
-      <c r="G6" s="103">
+      <c r="G6" s="95">
         <v>7</v>
       </c>
-      <c r="H6" s="103">
+      <c r="H6" s="95">
         <v>8</v>
       </c>
-      <c r="I6" s="103">
+      <c r="I6" s="95">
         <v>9</v>
       </c>
-      <c r="J6" s="103">
+      <c r="J6" s="95">
         <v>10</v>
       </c>
-      <c r="K6" s="103">
+      <c r="K6" s="95">
         <v>11</v>
       </c>
     </row>
@@ -17387,62 +17342,62 @@
     </row>
     <row r="10" spans="1:14" hidden="1" x14ac:dyDescent="0.3"/>
     <row r="11" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A11" s="128" t="s">
+      <c r="A11" s="119" t="s">
         <v>17</v>
       </c>
-      <c r="B11" s="128" t="s">
+      <c r="B11" s="119" t="s">
         <v>46</v>
       </c>
-      <c r="C11" s="128" t="s">
+      <c r="C11" s="119" t="s">
         <v>358</v>
       </c>
-      <c r="D11" s="130" t="s">
+      <c r="D11" s="121" t="s">
         <v>47</v>
       </c>
-      <c r="E11" s="145"/>
-      <c r="F11" s="128" t="s">
+      <c r="E11" s="136"/>
+      <c r="F11" s="119" t="s">
         <v>48</v>
       </c>
-      <c r="G11" s="128" t="s">
+      <c r="G11" s="119" t="s">
         <v>49</v>
       </c>
-      <c r="H11" s="128" t="s">
+      <c r="H11" s="119" t="s">
         <v>50</v>
       </c>
-      <c r="I11" s="128" t="s">
+      <c r="I11" s="119" t="s">
         <v>51</v>
       </c>
-      <c r="J11" s="128" t="s">
+      <c r="J11" s="119" t="s">
         <v>52</v>
       </c>
-      <c r="K11" s="128" t="s">
+      <c r="K11" s="119" t="s">
         <v>53</v>
       </c>
-      <c r="L11" s="128" t="s">
+      <c r="L11" s="119" t="s">
         <v>54</v>
       </c>
-      <c r="M11" s="128" t="s">
+      <c r="M11" s="119" t="s">
         <v>55</v>
       </c>
     </row>
     <row r="12" spans="1:14" ht="55.2" x14ac:dyDescent="0.3">
-      <c r="A12" s="129"/>
-      <c r="B12" s="129"/>
-      <c r="C12" s="129"/>
+      <c r="A12" s="120"/>
+      <c r="B12" s="120"/>
+      <c r="C12" s="120"/>
       <c r="D12" s="27" t="s">
         <v>265</v>
       </c>
       <c r="E12" s="27" t="s">
         <v>266</v>
       </c>
-      <c r="F12" s="129"/>
-      <c r="G12" s="129"/>
-      <c r="H12" s="129"/>
-      <c r="I12" s="129"/>
-      <c r="J12" s="129"/>
-      <c r="K12" s="129"/>
-      <c r="L12" s="129"/>
-      <c r="M12" s="129"/>
+      <c r="F12" s="120"/>
+      <c r="G12" s="120"/>
+      <c r="H12" s="120"/>
+      <c r="I12" s="120"/>
+      <c r="J12" s="120"/>
+      <c r="K12" s="120"/>
+      <c r="L12" s="120"/>
+      <c r="M12" s="120"/>
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A13" s="29">
@@ -17454,10 +17409,10 @@
       <c r="C13" s="29">
         <v>3</v>
       </c>
-      <c r="D13" s="143">
+      <c r="D13" s="134">
         <v>4</v>
       </c>
-      <c r="E13" s="144"/>
+      <c r="E13" s="135"/>
       <c r="F13" s="29">
         <v>5</v>
       </c>
@@ -17842,11 +17797,6 @@
     </row>
   </sheetData>
   <mergeCells count="13">
-    <mergeCell ref="D13:E13"/>
-    <mergeCell ref="D11:E11"/>
-    <mergeCell ref="A11:A12"/>
-    <mergeCell ref="B11:B12"/>
-    <mergeCell ref="C11:C12"/>
     <mergeCell ref="L11:L12"/>
     <mergeCell ref="M11:M12"/>
     <mergeCell ref="F11:F12"/>
@@ -17855,6 +17805,11 @@
     <mergeCell ref="I11:I12"/>
     <mergeCell ref="J11:J12"/>
     <mergeCell ref="K11:K12"/>
+    <mergeCell ref="D13:E13"/>
+    <mergeCell ref="D11:E11"/>
+    <mergeCell ref="A11:A12"/>
+    <mergeCell ref="B11:B12"/>
+    <mergeCell ref="C11:C12"/>
   </mergeCells>
   <dataValidations count="2">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="L14:L34 G14:G34" xr:uid="{00000000-0002-0000-0800-000000000000}">
